--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -954,35 +954,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MAPLE LEAF</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>092F  039</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kakawis</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>16.7</v>
+        <v>10.8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -993,54 +993,54 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3 t</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 15.1g/t</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>$307k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>2023</v>
+        <v>1987</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="V6" t="n">
-        <v>49.27111</v>
+        <v>50.53139</v>
       </c>
       <c r="W6" t="n">
-        <v>-125.73167</v>
+        <v>-125.2025</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>31.5</v>
+        <v>6.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,33 +1089,33 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1126,17 +1126,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="V7" t="n">
-        <v>58.90944</v>
+        <v>49.73278</v>
       </c>
       <c r="W7" t="n">
-        <v>-129.09278</v>
+        <v>-125.21139</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1146,21 +1146,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10.8</v>
+        <v>7.4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,54 +1185,54 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>1987</v>
+        <v>2012</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U8" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V8" t="n">
-        <v>50.53139</v>
+        <v>54.94444</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.2025</v>
+        <v>-126.15722</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1242,35 +1242,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6.8</v>
+        <v>36</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,33 +1281,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P9" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1318,17 +1318,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="V9" t="n">
-        <v>49.73278</v>
+        <v>58.185</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.21139</v>
+        <v>-125.30611</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1338,21 +1338,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.4</v>
+        <v>39.3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1377,54 +1377,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V10" t="n">
-        <v>54.94444</v>
+        <v>58.15222</v>
       </c>
       <c r="W10" t="n">
-        <v>-126.15722</v>
+        <v>-125.27778</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -1434,30 +1434,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MAGNET</t>
+          <t>DALEY WEST</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092L  097</t>
+          <t>093M  053</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nimpkish</t>
+          <t>New Hazelton</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8.4</v>
+        <v>2.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Magnetite, Iron, Copper</t>
+          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1478,49 +1478,49 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 15.40%</t>
+          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
+          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$780k</t>
+          <t>$193k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
+          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V11" t="n">
-        <v>50.40806</v>
+        <v>55.22278</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.96167</v>
+        <v>-127.56333</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
         </is>
       </c>
     </row>
@@ -1530,21 +1530,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ORMOND 3 (L.353)</t>
+          <t>MAGNOLIA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>092E  012</t>
+          <t>092F  274</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Marshall School Junction</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Gold, Silver, Lead, Zinc, Magnetite, Iron</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1574,49 +1574,49 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ag 127g/t, Cu 6.07%</t>
+          <t>Au 9.9g/t, Ag 231g/t, Cu 4.60%, Pb 16.00%, Zn 15.00%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
+          <t>Grab samples of dump material around a shaft that was sunk on the lens assayed up to 4.6 per cent copper, 18.51 grams per tonne gold and 17.14 grams per tonne silver (Assessment Report 5749). Seven hundred metres to the northwest from the Cap Sheaf shaft, grab samples from a showing on the Milner claim (Lot 77) assayed 4 to 16 per cent lead, 5 to 15 per cent zinc, 0.68 to 1.37 grams per tonne gold and 171.4 to 445.64 grams per tonne silver (Assessment 5749).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$750k</t>
+          <t>$104k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="P12" t="n">
-        <v>1988</v>
+        <v>2006</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Parallax Development Corp.</t>
+          <t>CanQuest Resource Corporation, Greenlite Ventures Inc., Longbar Minerals Limited</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V12" t="n">
-        <v>49.29972</v>
+        <v>49.70361</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.09722</v>
+        <v>-124.48639</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++274</t>
         </is>
       </c>
     </row>
@@ -1626,30 +1626,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RED CAP - SLOPE ZONE</t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>104K  010</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>5.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1670,28 +1670,28 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$666k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>2007</v>
+        <v>2019</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -1702,17 +1702,17 @@
         <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V13" t="n">
-        <v>58.73611</v>
+        <v>50.16611</v>
       </c>
       <c r="W13" t="n">
-        <v>-133.27</v>
+        <v>-125.39944</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -1722,30 +1722,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>20.1</v>
+        <v>11.4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1761,54 +1761,54 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$74k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>2019</v>
+        <v>1999</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U14" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V14" t="n">
-        <v>57.94639</v>
+        <v>52.85806</v>
       </c>
       <c r="W14" t="n">
-        <v>-131.66722</v>
+        <v>-132.15722</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -1818,35 +1818,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1857,54 +1857,54 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>2010</v>
+        <v>1986</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T15" t="n">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="U15" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="V15" t="n">
-        <v>49.47472</v>
+        <v>49.30889</v>
       </c>
       <c r="W15" t="n">
-        <v>-121.51417</v>
+        <v>-120.00417</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -1914,35 +1914,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RED CAP - EAST CIRQUE</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>104K  141</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>21</v>
+        <v>37.4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1953,33 +1953,29 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Au 3.7g/t, Ag 26.0g/t</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$208k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>2007</v>
+        <v>1966</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1990,17 +1986,17 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V16" t="n">
-        <v>58.73639</v>
+        <v>58.88222</v>
       </c>
       <c r="W16" t="n">
-        <v>-133.24944</v>
+        <v>-132.1175</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2010,30 +2006,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DALEY WEST</t>
+          <t>AVON</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>093M  053</t>
+          <t>092F  350</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>New Hazelton</t>
+          <t>Chetarpe</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.7</v>
+        <v>24.6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
+          <t>Gold, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2054,49 +2050,49 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
+          <t>Au 47.3g/t, Ag 53.1g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
+          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$193k</t>
+          <t>$33k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>2019</v>
+        <v>1985</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
+          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U17" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="V17" t="n">
-        <v>55.22278</v>
+        <v>49.40417</v>
       </c>
       <c r="W17" t="n">
-        <v>-127.56333</v>
+        <v>-125.75833</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
         </is>
       </c>
     </row>
@@ -2106,30 +2102,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>092B  060</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6.1</v>
+        <v>3.6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2150,30 +2146,20 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>$170k</t>
-        </is>
-      </c>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>3</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2023</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
         <v>13</v>
@@ -2182,17 +2168,17 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>50.37417</v>
+        <v>48.6075</v>
       </c>
       <c r="W18" t="n">
-        <v>-116.36167</v>
+        <v>-123.57111</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
         </is>
       </c>
     </row>
@@ -2202,17 +2188,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MAGNOLIA</t>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>092F  274</t>
+          <t>092B  056</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Marshall School Junction</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2220,12 +2206,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Lead, Zinc, Magnetite, Iron</t>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2241,54 +2227,44 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 9.9g/t, Ag 231g/t, Cu 4.60%, Pb 16.00%, Zn 15.00%</t>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Grab samples of dump material around a shaft that was sunk on the lens assayed up to 4.6 per cent copper, 18.51 grams per tonne gold and 17.14 grams per tonne silver (Assessment Report 5749). Seven hundred metres to the northwest from the Cap Sheaf shaft, grab samples from a showing on the Milner claim (Lot 77) assayed 4 to 16 per cent lead, 5 to 15 per cent zinc, 0.68 to 1.37 grams per tonne gold and 171.4 to 445.64 grams per tonne silver (Assessment 5749).</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>$104k</t>
-        </is>
-      </c>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>13</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2006</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>CanQuest Resource Corporation, Greenlite Ventures Inc., Longbar Minerals Limited</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>300</v>
       </c>
       <c r="U19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>49.70361</v>
+        <v>48.61472</v>
       </c>
       <c r="W19" t="n">
-        <v>-124.48639</v>
+        <v>-123.59222</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++274</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
         </is>
       </c>
     </row>
@@ -2298,30 +2274,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HAIDA GOLD</t>
+          <t>KING GEORGE (L.159)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>103C  002</t>
+          <t>092B  011</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sewell Inlet</t>
+          <t>East Sooke</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>11.4</v>
+        <v>0.8</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2337,54 +2313,44 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>544 t</t>
+          <t>13 t</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 8.7g/t</t>
+          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>$74k</t>
-        </is>
-      </c>
+          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>4</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1999</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U20" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>52.85806</v>
+        <v>48.36806</v>
       </c>
       <c r="W20" t="n">
-        <v>-132.15722</v>
+        <v>-123.69528</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
         </is>
       </c>
     </row>
@@ -2394,35 +2360,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">SILVER BELL                   </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>093M  076</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Kispiox</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>37.4</v>
+        <v>1.6</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Gold, Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I21" t="b">
@@ -2433,31 +2399,25 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>$2k</t>
-        </is>
-      </c>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1966</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
         <v>13</v>
@@ -2466,17 +2426,17 @@
         <v>325</v>
       </c>
       <c r="U21" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>58.88222</v>
+        <v>55.33556</v>
       </c>
       <c r="W21" t="n">
-        <v>-132.1175</v>
+        <v>-127.69194</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
         </is>
       </c>
     </row>
@@ -2486,30 +2446,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KATANGA</t>
+          <t xml:space="preserve">CORMORANT                     </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>092GNE009</t>
+          <t>092K  098</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Williams Landing</t>
+          <t>Granite Bay</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>9.5</v>
+        <v>5.3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2525,54 +2485,44 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 62.0g/t</t>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>$4k</t>
-        </is>
-      </c>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>2</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Black Swan Gold Mines Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T22" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U22" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>49.51111</v>
+        <v>50.18694</v>
       </c>
       <c r="W22" t="n">
-        <v>-122.57306</v>
+        <v>-125.28056</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
         </is>
       </c>
     </row>
@@ -2582,21 +2532,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FISH CREEK</t>
+          <t xml:space="preserve">ROANAN                        </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>103O  005</t>
+          <t>104B  164</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Premier</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2621,17 +2571,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2651,272 +2601,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>55.99139</v>
+        <v>56.00194</v>
       </c>
       <c r="W23" t="n">
-        <v>-130.03694</v>
+        <v>-130.04972</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>SIXMILE</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>103O  002</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>13</v>
-      </c>
-      <c r="T24" t="n">
-        <v>325</v>
-      </c>
-      <c r="U24" t="n">
-        <v>55</v>
-      </c>
-      <c r="V24" t="n">
-        <v>55.98833</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-130.06194</v>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CORMORANT                     </t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>092K  098</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Granite Bay</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="n">
-        <v>250</v>
-      </c>
-      <c r="U25" t="n">
-        <v>55</v>
-      </c>
-      <c r="V25" t="n">
-        <v>50.18694</v>
-      </c>
-      <c r="W25" t="n">
-        <v>-125.28056</v>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>093M  076</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Kispiox</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Zinc, Lead</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="n">
-        <v>13</v>
-      </c>
-      <c r="T26" t="n">
-        <v>325</v>
-      </c>
-      <c r="U26" t="n">
-        <v>55</v>
-      </c>
-      <c r="V26" t="n">
-        <v>55.33556</v>
-      </c>
-      <c r="W26" t="n">
-        <v>-127.69194</v>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -954,35 +954,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>MAPLE LEAF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>092F  039</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Kakawis</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>10.8</v>
+        <v>16.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -993,54 +993,54 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>3 t</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 15.1g/t</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$307k</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>1987</v>
+        <v>2023</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="V6" t="n">
-        <v>50.53139</v>
+        <v>49.27111</v>
       </c>
       <c r="W6" t="n">
-        <v>-125.2025</v>
+        <v>-125.73167</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
         </is>
       </c>
     </row>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>104I  098</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>McDame</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6.8</v>
+        <v>31.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,33 +1089,33 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1126,17 +1126,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V7" t="n">
-        <v>49.73278</v>
+        <v>58.90944</v>
       </c>
       <c r="W7" t="n">
-        <v>-125.21139</v>
+        <v>-129.09278</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
         </is>
       </c>
     </row>
@@ -1146,21 +1146,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7.4</v>
+        <v>10.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,54 +1185,54 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>2012</v>
+        <v>1987</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V8" t="n">
-        <v>54.94444</v>
+        <v>50.53139</v>
       </c>
       <c r="W8" t="n">
-        <v>-126.15722</v>
+        <v>-125.2025</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1242,35 +1242,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>36</v>
+        <v>6.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,33 +1281,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1318,17 +1318,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>58.185</v>
+        <v>49.73278</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.30611</v>
+        <v>-125.21139</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1338,21 +1338,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>39.3</v>
+        <v>7.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1377,54 +1377,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U10" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>58.15222</v>
+        <v>54.94444</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.27778</v>
+        <v>-126.15722</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1434,30 +1434,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DALEY WEST</t>
+          <t>MAGNET</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>093M  053</t>
+          <t>092L  097</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>New Hazelton</t>
+          <t>Nimpkish</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2.7</v>
+        <v>8.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
+          <t>Magnetite, Iron, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1478,49 +1478,49 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
+          <t>Cu 15.40%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
+          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$193k</t>
+          <t>$780k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="P11" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
+          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U11" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>55.22278</v>
+        <v>50.40806</v>
       </c>
       <c r="W11" t="n">
-        <v>-127.56333</v>
+        <v>-126.96167</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
         </is>
       </c>
     </row>
@@ -1530,21 +1530,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MAGNOLIA</t>
+          <t>ORMOND 3 (L.353)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>092F  274</t>
+          <t>092E  012</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Marshall School Junction</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Lead, Zinc, Magnetite, Iron</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1574,49 +1574,49 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 9.9g/t, Ag 231g/t, Cu 4.60%, Pb 16.00%, Zn 15.00%</t>
+          <t>Ag 127g/t, Cu 6.07%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Grab samples of dump material around a shaft that was sunk on the lens assayed up to 4.6 per cent copper, 18.51 grams per tonne gold and 17.14 grams per tonne silver (Assessment Report 5749). Seven hundred metres to the northwest from the Cap Sheaf shaft, grab samples from a showing on the Milner claim (Lot 77) assayed 4 to 16 per cent lead, 5 to 15 per cent zinc, 0.68 to 1.37 grams per tonne gold and 171.4 to 445.64 grams per tonne silver (Assessment 5749).</t>
+          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$104k</t>
+          <t>$750k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2006</v>
+        <v>1988</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>CanQuest Resource Corporation, Greenlite Ventures Inc., Longbar Minerals Limited</t>
+          <t>Parallax Development Corp.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T12" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="U12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>49.70361</v>
+        <v>49.29972</v>
       </c>
       <c r="W12" t="n">
-        <v>-124.48639</v>
+        <v>-126.09722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++274</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
         </is>
       </c>
     </row>
@@ -1626,30 +1626,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t>RED CAP - SLOPE ZONE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>104K  010</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5.6</v>
+        <v>20</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1670,28 +1670,28 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$666k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="P13" t="n">
-        <v>2019</v>
+        <v>2007</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -1702,17 +1702,17 @@
         <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>50.16611</v>
+        <v>58.73611</v>
       </c>
       <c r="W13" t="n">
-        <v>-125.39944</v>
+        <v>-133.27</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
         </is>
       </c>
     </row>
@@ -1722,30 +1722,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HAIDA GOLD</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>103C  002</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sewell Inlet</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>11.4</v>
+        <v>20.1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1761,54 +1761,54 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>544 t</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 8.7g/t</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$74k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>1999</v>
+        <v>2019</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>52.85806</v>
+        <v>57.94639</v>
       </c>
       <c r="W14" t="n">
-        <v>-132.15722</v>
+        <v>-131.66722</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1818,35 +1818,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1857,54 +1857,54 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$234k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>1986</v>
+        <v>2010</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T15" t="n">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="U15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="V15" t="n">
-        <v>49.30889</v>
+        <v>49.47472</v>
       </c>
       <c r="W15" t="n">
-        <v>-120.00417</v>
+        <v>-121.51417</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -1914,35 +1914,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>37.4</v>
+        <v>21</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1953,29 +1953,33 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>1966</v>
+        <v>2007</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1986,17 +1990,17 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V16" t="n">
-        <v>58.88222</v>
+        <v>58.73639</v>
       </c>
       <c r="W16" t="n">
-        <v>-132.1175</v>
+        <v>-133.24944</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -2006,30 +2010,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AVON</t>
+          <t>DALEY WEST</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>092F  350</t>
+          <t>093M  053</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Chetarpe</t>
+          <t>New Hazelton</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>24.6</v>
+        <v>2.7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead</t>
+          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2050,49 +2054,49 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 47.3g/t, Ag 53.1g/t</t>
+          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
+          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$33k</t>
+          <t>$193k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>1985</v>
+        <v>2019</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
+          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>49.40417</v>
+        <v>55.22278</v>
       </c>
       <c r="W17" t="n">
-        <v>-125.75833</v>
+        <v>-127.56333</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
         </is>
       </c>
     </row>
@@ -2102,30 +2106,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>092B  060</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3.6</v>
+        <v>6.1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2146,20 +2150,30 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>$170k</t>
+        </is>
+      </c>
       <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2023</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
         <v>13</v>
@@ -2168,17 +2182,17 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>48.6075</v>
+        <v>50.37417</v>
       </c>
       <c r="W18" t="n">
-        <v>-123.57111</v>
+        <v>-116.36167</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -2188,17 +2202,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+          <t>MAGNOLIA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>092B  056</t>
+          <t>092F  274</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Marshall School Junction</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2206,12 +2220,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+          <t>Copper, Gold, Silver, Lead, Zinc, Magnetite, Iron</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2227,44 +2241,54 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+          <t>Au 9.9g/t, Ag 231g/t, Cu 4.60%, Pb 16.00%, Zn 15.00%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>Grab samples of dump material around a shaft that was sunk on the lens assayed up to 4.6 per cent copper, 18.51 grams per tonne gold and 17.14 grams per tonne silver (Assessment Report 5749). Seven hundred metres to the northwest from the Cap Sheaf shaft, grab samples from a showing on the Milner claim (Lot 77) assayed 4 to 16 per cent lead, 5 to 15 per cent zinc, 0.68 to 1.37 grams per tonne gold and 171.4 to 445.64 grams per tonne silver (Assessment 5749).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>$104k</t>
+        </is>
+      </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2006</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>CanQuest Resource Corporation, Greenlite Ventures Inc., Longbar Minerals Limited</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>300</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V19" t="n">
-        <v>48.61472</v>
+        <v>49.70361</v>
       </c>
       <c r="W19" t="n">
-        <v>-123.59222</v>
+        <v>-124.48639</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++274</t>
         </is>
       </c>
     </row>
@@ -2274,30 +2298,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KING GEORGE (L.159)</t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>092B  011</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>East Sooke</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.8</v>
+        <v>11.4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2313,44 +2337,54 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>13 t</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>$74k</t>
+        </is>
+      </c>
       <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1999</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U20" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V20" t="n">
-        <v>48.36806</v>
+        <v>52.85806</v>
       </c>
       <c r="W20" t="n">
-        <v>-123.69528</v>
+        <v>-132.15722</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -2360,35 +2394,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>093M  076</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kispiox</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.6</v>
+        <v>37.4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I21" t="b">
@@ -2399,25 +2433,31 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>$2k</t>
+        </is>
+      </c>
       <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
         <v>13</v>
@@ -2426,17 +2466,17 @@
         <v>325</v>
       </c>
       <c r="U21" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="V21" t="n">
-        <v>55.33556</v>
+        <v>58.88222</v>
       </c>
       <c r="W21" t="n">
-        <v>-127.69194</v>
+        <v>-132.1175</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2446,30 +2486,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORMORANT                     </t>
+          <t>KATANGA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>092K  098</t>
+          <t>092GNE009</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Granite Bay</t>
+          <t>Williams Landing</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5.3</v>
+        <v>9.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2485,44 +2525,54 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+          <t>Au 62.0g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>$4k</t>
+        </is>
+      </c>
       <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Black Swan Gold Mines Ltd.</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T22" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U22" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V22" t="n">
-        <v>50.18694</v>
+        <v>49.51111</v>
       </c>
       <c r="W22" t="n">
-        <v>-125.28056</v>
+        <v>-122.57306</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
         </is>
       </c>
     </row>
@@ -2532,21 +2582,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROANAN                        </t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>104B  164</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Premier</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2571,17 +2621,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2601,14 +2651,272 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>56.00194</v>
+        <v>55.99139</v>
       </c>
       <c r="W23" t="n">
-        <v>-130.04972</v>
+        <v>-130.03694</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SIXMILE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>103O  002</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>13</v>
+      </c>
+      <c r="T24" t="n">
+        <v>325</v>
+      </c>
+      <c r="U24" t="n">
+        <v>55</v>
+      </c>
+      <c r="V24" t="n">
+        <v>55.98833</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-130.06194</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CORMORANT                     </t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>092K  098</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Granite Bay</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="n">
+        <v>250</v>
+      </c>
+      <c r="U25" t="n">
+        <v>55</v>
+      </c>
+      <c r="V25" t="n">
+        <v>50.18694</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-125.28056</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILVER BELL                   </t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>093M  076</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Kispiox</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Zinc, Lead</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>13</v>
+      </c>
+      <c r="T26" t="n">
+        <v>325</v>
+      </c>
+      <c r="U26" t="n">
+        <v>55</v>
+      </c>
+      <c r="V26" t="n">
+        <v>55.33556</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-127.69194</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:X27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1050,30 +1050,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t>WINCO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>104I  019</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>Boulder City</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>31.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Silver, Copper, Lead, Gold, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1094,28 +1094,28 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
+          <t>Ag 487g/t, Cu 9.85%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
+          <t>chip sample results include maximum values over 1 metre of 9.85 per cent copper and 486.86 grams per tonne silver;</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$3.2M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P7" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>Quartz Mountain Resources Ltd., Wyn Development Inc., Horseshoe Gold Mining Inc.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1129,14 +1129,14 @@
         <v>70</v>
       </c>
       <c r="V7" t="n">
-        <v>58.90944</v>
+        <v>58.78</v>
       </c>
       <c r="W7" t="n">
-        <v>-129.09278</v>
+        <v>-128.12222</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++019</t>
         </is>
       </c>
     </row>
@@ -1146,30 +1146,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>104I  098</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>McDame</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10.8</v>
+        <v>31.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1185,33 +1185,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>1987</v>
+        <v>2022</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1222,17 +1222,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V8" t="n">
-        <v>50.53139</v>
+        <v>58.90944</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.2025</v>
+        <v>-129.09278</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
         </is>
       </c>
     </row>
@@ -1242,35 +1242,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6.8</v>
+        <v>10.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,33 +1281,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2018</v>
+        <v>1987</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1321,14 +1321,14 @@
         <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>49.73278</v>
+        <v>50.53139</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.21139</v>
+        <v>-125.2025</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1338,35 +1338,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1377,54 +1377,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>54.94444</v>
+        <v>49.73278</v>
       </c>
       <c r="W10" t="n">
-        <v>-126.15722</v>
+        <v>-125.21139</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1434,35 +1434,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MAGNET</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092L  097</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nimpkish</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Magnetite, Iron, Copper</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1473,54 +1473,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 15.40%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$780k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2025</v>
+        <v>2012</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="U11" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>50.40806</v>
+        <v>54.94444</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.96167</v>
+        <v>-126.15722</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1530,30 +1530,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ORMOND 3 (L.353)</t>
+          <t>MAGNET</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>092E  012</t>
+          <t>092L  097</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Nimpkish</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.8</v>
+        <v>8.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Magnetite, Iron, Copper</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1574,49 +1574,49 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ag 127g/t, Cu 6.07%</t>
+          <t>Cu 15.40%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
+          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$750k</t>
+          <t>$780k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="P12" t="n">
-        <v>1988</v>
+        <v>2025</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Parallax Development Corp.</t>
+          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T12" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="U12" t="n">
         <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>49.29972</v>
+        <v>50.40806</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.09722</v>
+        <v>-126.96167</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
         </is>
       </c>
     </row>
@@ -1626,30 +1626,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RED CAP - SLOPE ZONE</t>
+          <t>ORMOND 3 (L.353)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>104K  010</t>
+          <t>092E  012</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>2.8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1670,49 +1670,49 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
+          <t>Ag 127g/t, Cu 6.07%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
+          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$666k</t>
+          <t>$750k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>2007</v>
+        <v>1988</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Parallax Development Corp.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U13" t="n">
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>58.73611</v>
+        <v>49.29972</v>
       </c>
       <c r="W13" t="n">
-        <v>-133.27</v>
+        <v>-126.09722</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
         </is>
       </c>
     </row>
@@ -1722,30 +1722,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>RED CAP - SLOPE ZONE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>104K  010</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1766,28 +1766,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$666k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P14" t="n">
-        <v>2019</v>
+        <v>2007</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1801,14 +1801,14 @@
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>57.94639</v>
+        <v>58.73611</v>
       </c>
       <c r="W14" t="n">
-        <v>-131.66722</v>
+        <v>-133.27</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
         </is>
       </c>
     </row>
@@ -1818,35 +1818,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.9</v>
+        <v>20.1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1857,54 +1857,54 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>2010</v>
+        <v>2019</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="V15" t="n">
-        <v>49.47472</v>
+        <v>57.94639</v>
       </c>
       <c r="W15" t="n">
-        <v>-121.51417</v>
+        <v>-131.66722</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1914,35 +1914,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RED CAP - EAST CIRQUE</t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>104K  141</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>21</v>
+        <v>6.9</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1953,54 +1953,54 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 3.7g/t, Ag 26.0g/t</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$208k</t>
+          <t>$234k</t>
         </is>
       </c>
       <c r="O16" t="n">
         <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U16" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="V16" t="n">
-        <v>58.73639</v>
+        <v>49.47472</v>
       </c>
       <c r="W16" t="n">
-        <v>-133.24944</v>
+        <v>-121.51417</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -2010,30 +2010,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DALEY WEST</t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>093M  053</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>New Hazelton</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.7</v>
+        <v>21</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2054,28 +2054,28 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$193k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>2019</v>
+        <v>2007</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -2089,14 +2089,14 @@
         <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>55.22278</v>
+        <v>58.73639</v>
       </c>
       <c r="W17" t="n">
-        <v>-127.56333</v>
+        <v>-133.24944</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -2106,21 +2106,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t>DALEY WEST</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>093M  053</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>New Hazelton</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6.1</v>
+        <v>2.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2145,33 +2145,33 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$193k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
@@ -2185,14 +2185,14 @@
         <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>50.37417</v>
+        <v>55.22278</v>
       </c>
       <c r="W18" t="n">
-        <v>-116.36167</v>
+        <v>-127.56333</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
         </is>
       </c>
     </row>
@@ -2202,21 +2202,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MAGNOLIA</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>092F  274</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Marshall School Junction</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.9</v>
+        <v>6.1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Lead, Zinc, Magnetite, Iron</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2241,54 +2241,54 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 9.9g/t, Ag 231g/t, Cu 4.60%, Pb 16.00%, Zn 15.00%</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Grab samples of dump material around a shaft that was sunk on the lens assayed up to 4.6 per cent copper, 18.51 grams per tonne gold and 17.14 grams per tonne silver (Assessment Report 5749). Seven hundred metres to the northwest from the Cap Sheaf shaft, grab samples from a showing on the Milner claim (Lot 77) assayed 4 to 16 per cent lead, 5 to 15 per cent zinc, 0.68 to 1.37 grams per tonne gold and 171.4 to 445.64 grams per tonne silver (Assessment 5749).</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>$104k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>2006</v>
+        <v>2023</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>CanQuest Resource Corporation, Greenlite Ventures Inc., Longbar Minerals Limited</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>325</v>
       </c>
       <c r="U19" t="n">
         <v>61</v>
       </c>
       <c r="V19" t="n">
-        <v>49.70361</v>
+        <v>50.37417</v>
       </c>
       <c r="W19" t="n">
-        <v>-124.48639</v>
+        <v>-116.36167</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++274</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -2298,30 +2298,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HAIDA GOLD</t>
+          <t>MAGNOLIA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>103C  002</t>
+          <t>092F  274</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sewell Inlet</t>
+          <t>Marshall School Junction</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>11.4</v>
+        <v>1.9</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Gold, Silver, Lead, Zinc, Magnetite, Iron</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2337,54 +2337,54 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>544 t</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 8.7g/t</t>
+          <t>Au 9.9g/t, Ag 231g/t, Cu 4.60%, Pb 16.00%, Zn 15.00%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+          <t>Grab samples of dump material around a shaft that was sunk on the lens assayed up to 4.6 per cent copper, 18.51 grams per tonne gold and 17.14 grams per tonne silver (Assessment Report 5749). Seven hundred metres to the northwest from the Cap Sheaf shaft, grab samples from a showing on the Milner claim (Lot 77) assayed 4 to 16 per cent lead, 5 to 15 per cent zinc, 0.68 to 1.37 grams per tonne gold and 171.4 to 445.64 grams per tonne silver (Assessment 5749).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>$74k</t>
+          <t>$104k</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="P20" t="n">
-        <v>1999</v>
+        <v>2006</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+          <t>CanQuest Resource Corporation, Greenlite Ventures Inc., Longbar Minerals Limited</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>325</v>
+        <v>75</v>
       </c>
       <c r="U20" t="n">
         <v>61</v>
       </c>
       <c r="V20" t="n">
-        <v>52.85806</v>
+        <v>49.70361</v>
       </c>
       <c r="W20" t="n">
-        <v>-132.15722</v>
+        <v>-124.48639</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++274</t>
         </is>
       </c>
     </row>
@@ -2394,35 +2394,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>37.4</v>
+        <v>11.4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I21" t="b">
@@ -2433,29 +2433,33 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>544 t</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Au 8.7g/t</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$74k</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>1966</v>
+        <v>1999</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
@@ -2466,17 +2470,17 @@
         <v>325</v>
       </c>
       <c r="U21" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V21" t="n">
-        <v>58.88222</v>
+        <v>52.85806</v>
       </c>
       <c r="W21" t="n">
-        <v>-132.1175</v>
+        <v>-132.15722</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -2486,35 +2490,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KATANGA</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>092GNE009</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Williams Landing</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>9.5</v>
+        <v>37.4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I22" t="b">
@@ -2525,33 +2529,29 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Au 62.0g/t</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>$4k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P22" t="n">
-        <v>1985</v>
+        <v>1966</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Black Swan Gold Mines Ltd.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
@@ -2562,17 +2562,17 @@
         <v>325</v>
       </c>
       <c r="U22" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="V22" t="n">
-        <v>49.51111</v>
+        <v>58.88222</v>
       </c>
       <c r="W22" t="n">
-        <v>-122.57306</v>
+        <v>-132.1175</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2582,21 +2582,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FISH CREEK</t>
+          <t>KATANGA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>103O  005</t>
+          <t>092GNE009</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Williams Landing</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6.6</v>
+        <v>9.5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2626,20 +2626,30 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+          <t>Au 62.0g/t</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>$4k</t>
+        </is>
+      </c>
       <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Black Swan Gold Mines Ltd.</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
         <v>13</v>
@@ -2648,17 +2658,17 @@
         <v>325</v>
       </c>
       <c r="U23" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V23" t="n">
-        <v>55.99139</v>
+        <v>49.51111</v>
       </c>
       <c r="W23" t="n">
-        <v>-130.03694</v>
+        <v>-122.57306</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2678,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SIXMILE</t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>103O  002</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2682,7 +2692,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2691,7 +2701,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2712,12 +2722,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2737,14 +2747,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>55.98833</v>
+        <v>55.99139</v>
       </c>
       <c r="W24" t="n">
-        <v>-130.06194</v>
+        <v>-130.03694</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
         </is>
       </c>
     </row>
@@ -2754,30 +2764,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORMORANT                     </t>
+          <t>SIXMILE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>092K  098</t>
+          <t>103O  002</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Granite Bay</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2793,17 +2803,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2814,23 +2824,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T25" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U25" t="n">
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>50.18694</v>
+        <v>55.98833</v>
       </c>
       <c r="W25" t="n">
-        <v>-125.28056</v>
+        <v>-130.06194</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
         </is>
       </c>
     </row>
@@ -2840,30 +2850,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
+          <t xml:space="preserve">CORMORANT                     </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>093M  076</t>
+          <t>092K  098</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Kispiox</t>
+          <t>Granite Bay</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2884,12 +2894,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -2900,21 +2910,107 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T26" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U26" t="n">
         <v>55</v>
       </c>
       <c r="V26" t="n">
+        <v>50.18694</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-125.28056</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILVER BELL                   </t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>093M  076</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Kispiox</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Zinc, Lead</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>13</v>
+      </c>
+      <c r="T27" t="n">
+        <v>325</v>
+      </c>
+      <c r="U27" t="n">
+        <v>55</v>
+      </c>
+      <c r="V27" t="n">
         <v>55.33556</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W27" t="n">
         <v>-127.69194</v>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
         </is>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:X20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -954,35 +954,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MAPLE LEAF</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>092F  039</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kakawis</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>16.7</v>
+        <v>10.8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -993,54 +993,54 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3 t</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 15.1g/t</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>$307k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>2023</v>
+        <v>1987</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="V6" t="n">
-        <v>49.27111</v>
+        <v>50.53139</v>
       </c>
       <c r="W6" t="n">
-        <v>-125.73167</v>
+        <v>-125.2025</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WINCO</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>104I  019</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Boulder City</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>66.40000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Gold, Zinc</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,33 +1089,33 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ag 487g/t, Cu 9.85%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>chip sample results include maximum values over 1 metre of 9.85 per cent copper and 486.86 grams per tonne silver;</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$3.2M</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Quartz Mountain Resources Ltd., Wyn Development Inc., Horseshoe Gold Mining Inc.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1126,17 +1126,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="V7" t="n">
-        <v>58.78</v>
+        <v>49.73278</v>
       </c>
       <c r="W7" t="n">
-        <v>-128.12222</v>
+        <v>-125.21139</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++019</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1146,35 +1146,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>31.5</v>
+        <v>7.4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,54 +1185,54 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U8" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="V8" t="n">
-        <v>58.90944</v>
+        <v>54.94444</v>
       </c>
       <c r="W8" t="n">
-        <v>-129.09278</v>
+        <v>-126.15722</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1242,21 +1242,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>ORMOND 3 (L.353)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>092E  012</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10.8</v>
+        <v>2.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1281,54 +1281,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Ag 127g/t, Cu 6.07%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$750k</t>
         </is>
       </c>
       <c r="O9" t="n">
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Parallax Development Corp.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U9" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="V9" t="n">
-        <v>50.53139</v>
+        <v>49.29972</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.2025</v>
+        <v>-126.09722</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
         </is>
       </c>
     </row>
@@ -1338,35 +1338,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.8</v>
+        <v>20.1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1377,33 +1377,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1414,17 +1414,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="V10" t="n">
-        <v>49.73278</v>
+        <v>57.94639</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.21139</v>
+        <v>-131.66722</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1434,30 +1434,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1473,54 +1473,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$234k</t>
         </is>
       </c>
       <c r="O11" t="n">
         <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T11" t="n">
-        <v>275</v>
+        <v>175</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="V11" t="n">
-        <v>54.94444</v>
+        <v>49.47472</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.15722</v>
+        <v>-121.51417</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -1530,30 +1530,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MAGNET</t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>092L  097</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nimpkish</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8.4</v>
+        <v>21</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Magnetite, Iron, Copper</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1574,49 +1574,49 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 15.40%</t>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$780k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>2025</v>
+        <v>2007</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V12" t="n">
-        <v>50.40806</v>
+        <v>58.73639</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.96167</v>
+        <v>-133.24944</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -1626,21 +1626,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORMOND 3 (L.353)</t>
+          <t>DALEY WEST</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092E  012</t>
+          <t>093M  053</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>New Hazelton</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1670,49 +1670,49 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ag 127g/t, Cu 6.07%</t>
+          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
+          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$750k</t>
+          <t>$193k</t>
         </is>
       </c>
       <c r="O13" t="n">
         <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>1988</v>
+        <v>2019</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Parallax Development Corp.</t>
+          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V13" t="n">
-        <v>49.29972</v>
+        <v>55.22278</v>
       </c>
       <c r="W13" t="n">
-        <v>-126.09722</v>
+        <v>-127.56333</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
         </is>
       </c>
     </row>
@@ -1722,30 +1722,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RED CAP - SLOPE ZONE</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>104K  010</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>6.1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1761,33 +1761,33 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$666k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2007</v>
+        <v>2023</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1798,17 +1798,17 @@
         <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V14" t="n">
-        <v>58.73611</v>
+        <v>50.37417</v>
       </c>
       <c r="W14" t="n">
-        <v>-133.27</v>
+        <v>-116.36167</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -1818,35 +1818,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>20.1</v>
+        <v>37.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1857,33 +1857,29 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>2019</v>
+        <v>1966</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1894,17 +1890,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="V15" t="n">
-        <v>57.94639</v>
+        <v>58.88222</v>
       </c>
       <c r="W15" t="n">
-        <v>-131.66722</v>
+        <v>-132.1175</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -1914,35 +1910,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t xml:space="preserve">MIDNIGHT NAILS 1-2            </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>082LSE063</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Cherryville</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6.9</v>
+        <v>8.1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1953,54 +1949,54 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Au 11.1g/t, Ag 76.0g/t, Pb 1.05%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>In 1983, samples from the Cherry shear assayed up to 158 grams per tonne gold and 1251 grams per tonne silver, while a sample of the altered dike or sill assayed 4.2 per cent lead, 1.86 per cent zinc, 42.2 grams per tonne gold and 212.5 grams per tonne silver (Assessment Report 11892). In 1987, a sample (R-7) wall rock adjacent to the vein assayed 75.3 grams per tonne gold, 147 grams per tonne silver and 1.96 per cent lead over 0.6 metre (Assessment Report 17386). In 1988, samples from the vein in the Cherry shear assayed up to 2.16 grams per tonne gold and 0.9 gram per tonne silver over 1 metre, while samples from areas with no quartz veining assayed up to 20 grams per tonne gold, 1.05 per cent lead and 76 grams per tonne silver over 90 metres (Assessment Report 18706). Samples from disco</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$47k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P16" t="n">
-        <v>2010</v>
+        <v>2026</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>Mohawk Oil Co. Ltd., Howard, Lennie Lee</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T16" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="U16" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="V16" t="n">
-        <v>49.47472</v>
+        <v>50.17861</v>
       </c>
       <c r="W16" t="n">
-        <v>-121.51417</v>
+        <v>-118.54</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSE063</t>
         </is>
       </c>
     </row>
@@ -2010,30 +2006,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RED CAP - EAST CIRQUE</t>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>104K  141</t>
+          <t>092B  056</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>21</v>
+        <v>1.9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2049,35 +2045,25 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 3.7g/t, Ag 26.0g/t</t>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>$208k</t>
-        </is>
-      </c>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>4</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2007</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
         <v>13</v>
@@ -2086,17 +2072,17 @@
         <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>58.73639</v>
+        <v>48.61472</v>
       </c>
       <c r="W17" t="n">
-        <v>-133.24944</v>
+        <v>-123.59222</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
         </is>
       </c>
     </row>
@@ -2106,30 +2092,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DALEY WEST</t>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>093M  053</t>
+          <t>092B  060</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>New Hazelton</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2145,35 +2131,25 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>$193k</t>
-        </is>
-      </c>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>2</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2019</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
         <v>13</v>
@@ -2182,17 +2158,17 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>55.22278</v>
+        <v>48.6075</v>
       </c>
       <c r="W18" t="n">
-        <v>-127.56333</v>
+        <v>-123.57111</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
         </is>
       </c>
     </row>
@@ -2202,21 +2178,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t>KING GEORGE (L.159)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>092B  011</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>East Sooke</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6.1</v>
+        <v>0.8</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2225,7 +2201,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2241,54 +2217,44 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>13 t</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>$170k</t>
-        </is>
-      </c>
+          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>3</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2023</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T19" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>50.37417</v>
+        <v>48.36806</v>
       </c>
       <c r="W19" t="n">
-        <v>-116.36167</v>
+        <v>-123.69528</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
         </is>
       </c>
     </row>
@@ -2298,30 +2264,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MAGNOLIA</t>
+          <t xml:space="preserve">SILVER BELL                   </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>092F  274</t>
+          <t>093M  076</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Marshall School Junction</t>
+          <t>Kispiox</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Lead, Zinc, Magnetite, Iron</t>
+          <t>Gold, Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2337,680 +2303,42 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 9.9g/t, Ag 231g/t, Cu 4.60%, Pb 16.00%, Zn 15.00%</t>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Grab samples of dump material around a shaft that was sunk on the lens assayed up to 4.6 per cent copper, 18.51 grams per tonne gold and 17.14 grams per tonne silver (Assessment Report 5749). Seven hundred metres to the northwest from the Cap Sheaf shaft, grab samples from a showing on the Milner claim (Lot 77) assayed 4 to 16 per cent lead, 5 to 15 per cent zinc, 0.68 to 1.37 grams per tonne gold and 171.4 to 445.64 grams per tonne silver (Assessment 5749).</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>$104k</t>
-        </is>
-      </c>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>13</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2006</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>CanQuest Resource Corporation, Greenlite Ventures Inc., Longbar Minerals Limited</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>75</v>
+        <v>325</v>
       </c>
       <c r="U20" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>49.70361</v>
+        <v>55.33556</v>
       </c>
       <c r="W20" t="n">
-        <v>-124.48639</v>
+        <v>-127.69194</v>
       </c>
       <c r="X20" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++274</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>HAIDA GOLD</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>103C  002</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Sewell Inlet</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>544 t</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Au 8.7g/t</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>$74k</t>
-        </is>
-      </c>
-      <c r="O21" t="n">
-        <v>4</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1999</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>13</v>
-      </c>
-      <c r="T21" t="n">
-        <v>325</v>
-      </c>
-      <c r="U21" t="n">
-        <v>61</v>
-      </c>
-      <c r="V21" t="n">
-        <v>52.85806</v>
-      </c>
-      <c r="W21" t="n">
-        <v>-132.15722</v>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACE                           </t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>104K  025</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Callison Ranch</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Asbestos</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Developed Prospect  </t>
-        </is>
-      </c>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>$2k</t>
-        </is>
-      </c>
-      <c r="O22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1966</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>13</v>
-      </c>
-      <c r="T22" t="n">
-        <v>325</v>
-      </c>
-      <c r="U22" t="n">
-        <v>60</v>
-      </c>
-      <c r="V22" t="n">
-        <v>58.88222</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-132.1175</v>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>KATANGA</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>092GNE009</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Williams Landing</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Au 62.0g/t</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>$4k</t>
-        </is>
-      </c>
-      <c r="O23" t="n">
-        <v>2</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Black Swan Gold Mines Ltd.</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>13</v>
-      </c>
-      <c r="T23" t="n">
-        <v>325</v>
-      </c>
-      <c r="U23" t="n">
-        <v>57</v>
-      </c>
-      <c r="V23" t="n">
-        <v>49.51111</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-122.57306</v>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>FISH CREEK</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>103O  005</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>13</v>
-      </c>
-      <c r="T24" t="n">
-        <v>325</v>
-      </c>
-      <c r="U24" t="n">
-        <v>55</v>
-      </c>
-      <c r="V24" t="n">
-        <v>55.99139</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-130.03694</v>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>SIXMILE</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>103O  002</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>13</v>
-      </c>
-      <c r="T25" t="n">
-        <v>325</v>
-      </c>
-      <c r="U25" t="n">
-        <v>55</v>
-      </c>
-      <c r="V25" t="n">
-        <v>55.98833</v>
-      </c>
-      <c r="W25" t="n">
-        <v>-130.06194</v>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CORMORANT                     </t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>092K  098</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Granite Bay</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="n">
-        <v>250</v>
-      </c>
-      <c r="U26" t="n">
-        <v>55</v>
-      </c>
-      <c r="V26" t="n">
-        <v>50.18694</v>
-      </c>
-      <c r="W26" t="n">
-        <v>-125.28056</v>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>093M  076</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Kispiox</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Zinc, Lead</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I27" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="n">
-        <v>13</v>
-      </c>
-      <c r="T27" t="n">
-        <v>325</v>
-      </c>
-      <c r="U27" t="n">
-        <v>55</v>
-      </c>
-      <c r="V27" t="n">
-        <v>55.33556</v>
-      </c>
-      <c r="W27" t="n">
-        <v>-127.69194</v>
-      </c>
-      <c r="X27" t="inlineStr">
         <is>
           <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
         </is>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X20"/>
+  <dimension ref="A1:X27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -762,35 +762,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ERICKSEN-ASHBY</t>
+          <t>CHARLIE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>104K  009</t>
+          <t>092O  043</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Nemaiah Valley</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5.3</v>
+        <v>36.9</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold, Rhodonite</t>
+          <t>Gold, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -801,54 +801,54 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>907 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 0.9g/t, Ag 567g/t, Pb 5.68%, Zn 5.21%</t>
+          <t>Au 16.0g/t, Ag 224g/t</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3 intersected 20.2 metres which assayed 567.1 grams per tonne silver, 4.94 per cent lead and 4.22 per cent zinc; 4 intersected 5.1 metres which assayed 627.4 grams per tonne silver, 6.42 per cent lead and 6.2 per cent zinc (Assessment Report 10026). In 1981, a 15.1 metre drill intersection in mineralized cherts in Zone 8 assayed 173.1 grams per tonne silver, 1.2 per cent lead and 1.37 per cent zinc (Assessment Report 10026). Identified over an 8 metre width, some samples yielded high assays of 1203 grams per tonne silver, 23.23 per cent zinc, 20.24 per cent lead and 0.69 gram per tonne gold. Grab samples from the mineralized zone, 5 to 7 metres wide, of fine-grained pyrite, sphalerite, galena and quartz were assayed yielding 1.13 grams per tonne gold, 144.0 grams per tonne silver, 2.14 per</t>
+          <t>A chip sample assayed 279.9 grams per tonne silver, 10.6 grams per tonne gold and 13.68 per cent copper (Bulletin 81). The following year, samples from the East vein area assayed up to 0.48 per cent copper, 1.0 gram per tonne gold and 14.3 grams per tonne silver (Assessment Report 12105). In 1987, chip samples from the Charlie vein, taken over a length of 20 metres and width of 20 centimetres, averaged 22.1 grams per tonne gold and 224.0 grams per tonne silver, while a sample (AB 245B) of the DK vein assayed 9.9 grams per tonne gold, 95.8 grams per tonne silver and 0.14 per cent lead (Assessment Report 17038). A 20- centimetre sample of massive sulphide from the Big vein assayed 8.2 grams per tonne gold, 8557 grams per tonne silver and 26.0 per cent copper (Assessment Report 17038). In 199</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>$286k</t>
+          <t>$6.3M</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="P4" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Optima Minerals Inc., Northwind Ventures, Terratest</t>
+          <t>Galore Resources Inc., Suncor, Galore Resources Inc.; Zelon Enterprises Ltd.</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U4" t="n">
         <v>75</v>
       </c>
       <c r="V4" t="n">
-        <v>58.65806</v>
+        <v>51.18028</v>
       </c>
       <c r="W4" t="n">
-        <v>-133.475</v>
+        <v>-123.67083</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++009</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092O++043</t>
         </is>
       </c>
     </row>
@@ -858,30 +858,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DRIFTPILE CREEK</t>
+          <t>ERICKSEN-ASHBY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>094K  066</t>
+          <t>104K  009</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>5.3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Barite</t>
+          <t>Silver, Lead, Zinc, Gold, Rhodonite</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -897,54 +897,54 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>18.1 Mt</t>
+          <t>907 kt</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Pb 1.18%, Zn 10.00%</t>
+          <t>Au 0.9g/t, Ag 567g/t, Pb 5.68%, Zn 5.21%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>In 1980, it was reported that shallow drilling in 11 areas indicated reserves of approximately 18,145,000 tonnes averaging 2.38 per cent combined lead-zinc (Canadian Mines Handbook 1980-81, pages 280-281). In 1978, the best drill intersection from the North Trench zone (hole 78-07) was 11.7 metres grading 7.45 per cent combined lead and zinc, whereas drilling on the Ridge zone yielded 3 per cent combined lead and zinc over 26.2 metres and 4.14 per cent zinc over 7.5 metres in drillhole 78-09 (Assessment Report 7149 and 24609). In 1993, drilling on the Main zone intersected a 12-metre zone grading 10 per cent zinc and 1 per cent lead, including a zone of 6.02 metres grading 12.26 per cent zinc and 1.36 per cent lead in hole 93-56 (Assessment Report 23109). Several narrow high-grade intercep</t>
+          <t>3 intersected 20.2 metres which assayed 567.1 grams per tonne silver, 4.94 per cent lead and 4.22 per cent zinc; 4 intersected 5.1 metres which assayed 627.4 grams per tonne silver, 6.42 per cent lead and 6.2 per cent zinc (Assessment Report 10026). In 1981, a 15.1 metre drill intersection in mineralized cherts in Zone 8 assayed 173.1 grams per tonne silver, 1.2 per cent lead and 1.37 per cent zinc (Assessment Report 10026). Identified over an 8 metre width, some samples yielded high assays of 1203 grams per tonne silver, 23.23 per cent zinc, 20.24 per cent lead and 0.69 gram per tonne gold. Grab samples from the mineralized zone, 5 to 7 metres wide, of fine-grained pyrite, sphalerite, galena and quartz were assayed yielding 1.13 grams per tonne gold, 144.0 grams per tonne silver, 2.14 per</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>$1.4M</t>
+          <t>$286k</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Teck Exploration Ltd., Welcome North Mines Limited, Teck Corporation</t>
+          <t>Optima Minerals Inc., Northwind Ventures, Terratest</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V5" t="n">
-        <v>58.06639</v>
+        <v>58.65806</v>
       </c>
       <c r="W5" t="n">
-        <v>-125.90972</v>
+        <v>-133.475</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++066</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++009</t>
         </is>
       </c>
     </row>
@@ -954,35 +954,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>DRIFTPILE CREEK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>094K  066</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>10.8</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Zinc, Lead, Barite</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -993,54 +993,54 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>18.1 Mt</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Pb 1.18%, Zn 10.00%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>In 1980, it was reported that shallow drilling in 11 areas indicated reserves of approximately 18,145,000 tonnes averaging 2.38 per cent combined lead-zinc (Canadian Mines Handbook 1980-81, pages 280-281). In 1978, the best drill intersection from the North Trench zone (hole 78-07) was 11.7 metres grading 7.45 per cent combined lead and zinc, whereas drilling on the Ridge zone yielded 3 per cent combined lead and zinc over 26.2 metres and 4.14 per cent zinc over 7.5 metres in drillhole 78-09 (Assessment Report 7149 and 24609). In 1993, drilling on the Main zone intersected a 12-metre zone grading 10 per cent zinc and 1 per cent lead, including a zone of 6.02 metres grading 12.26 per cent zinc and 1.36 per cent lead in hole 93-56 (Assessment Report 23109). Several narrow high-grade intercep</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$1.4M</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="P6" t="n">
-        <v>1987</v>
+        <v>2016</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Teck Exploration Ltd., Welcome North Mines Limited, Teck Corporation</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U6" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="V6" t="n">
-        <v>50.53139</v>
+        <v>58.06639</v>
       </c>
       <c r="W6" t="n">
-        <v>-125.2025</v>
+        <v>-125.90972</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++066</t>
         </is>
       </c>
     </row>
@@ -1050,21 +1050,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>MAPLE LEAF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>092F  039</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Kakawis</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6.8</v>
+        <v>16.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,54 +1089,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>3 t</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Au 15.1g/t</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$307k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="P7" t="n">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="V7" t="n">
-        <v>49.73278</v>
+        <v>49.27111</v>
       </c>
       <c r="W7" t="n">
-        <v>-125.21139</v>
+        <v>-125.73167</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
         </is>
       </c>
     </row>
@@ -1146,35 +1146,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>104I  098</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>McDame</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7.4</v>
+        <v>31.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,54 +1185,54 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="V8" t="n">
-        <v>54.94444</v>
+        <v>58.90944</v>
       </c>
       <c r="W8" t="n">
-        <v>-126.15722</v>
+        <v>-129.09278</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
         </is>
       </c>
     </row>
@@ -1242,21 +1242,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ORMOND 3 (L.353)</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092E  012</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2.8</v>
+        <v>10.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1281,54 +1281,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ag 127g/t, Cu 6.07%</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$750k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O9" t="n">
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Parallax Development Corp.</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>49.29972</v>
+        <v>50.53139</v>
       </c>
       <c r="W9" t="n">
-        <v>-126.09722</v>
+        <v>-125.2025</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1338,35 +1338,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>20.1</v>
+        <v>6.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1377,33 +1377,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1414,17 +1414,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>57.94639</v>
+        <v>49.73278</v>
       </c>
       <c r="W10" t="n">
-        <v>-131.66722</v>
+        <v>-125.21139</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1434,30 +1434,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1473,54 +1473,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O11" t="n">
         <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="U11" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>49.47472</v>
+        <v>54.94444</v>
       </c>
       <c r="W11" t="n">
-        <v>-121.51417</v>
+        <v>-126.15722</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1530,21 +1530,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RED CAP - EAST CIRQUE</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>104K  141</t>
+          <t>092E  088</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>21</v>
+        <v>1.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Gold, Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1574,49 +1574,49 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 3.7g/t, Ag 26.0g/t</t>
+          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
+          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$208k</t>
+          <t>$766k</t>
         </is>
       </c>
       <c r="O12" t="n">
         <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>2007</v>
+        <v>1988</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>58.73639</v>
+        <v>49.29694</v>
       </c>
       <c r="W12" t="n">
-        <v>-133.24944</v>
+        <v>-126.08111</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
         </is>
       </c>
     </row>
@@ -1626,21 +1626,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DALEY WEST</t>
+          <t>ORMOND 3 (L.353)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>093M  053</t>
+          <t>092E  012</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>New Hazelton</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1670,49 +1670,49 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
+          <t>Ag 127g/t, Cu 6.07%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
+          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$193k</t>
+          <t>$750k</t>
         </is>
       </c>
       <c r="O13" t="n">
         <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>2019</v>
+        <v>1988</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
+          <t>Parallax Development Corp.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U13" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>55.22278</v>
+        <v>49.29972</v>
       </c>
       <c r="W13" t="n">
-        <v>-127.56333</v>
+        <v>-126.09722</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
         </is>
       </c>
     </row>
@@ -1722,21 +1722,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.1</v>
+        <v>20.1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1761,33 +1761,33 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1798,17 +1798,17 @@
         <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>50.37417</v>
+        <v>57.94639</v>
       </c>
       <c r="W14" t="n">
-        <v>-116.36167</v>
+        <v>-131.66722</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1818,35 +1818,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>37.4</v>
+        <v>36</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1857,29 +1857,33 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Au 5.8g/t, Cu 7.88%</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>1966</v>
+        <v>2022</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1890,17 +1894,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="V15" t="n">
-        <v>58.88222</v>
+        <v>58.185</v>
       </c>
       <c r="W15" t="n">
-        <v>-132.1175</v>
+        <v>-125.30611</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1910,30 +1914,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIDNIGHT NAILS 1-2            </t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>082LSE063</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cherryville</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8.1</v>
+        <v>39.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1954,49 +1958,49 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 11.1g/t, Ag 76.0g/t, Pb 1.05%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>In 1983, samples from the Cherry shear assayed up to 158 grams per tonne gold and 1251 grams per tonne silver, while a sample of the altered dike or sill assayed 4.2 per cent lead, 1.86 per cent zinc, 42.2 grams per tonne gold and 212.5 grams per tonne silver (Assessment Report 11892). In 1987, a sample (R-7) wall rock adjacent to the vein assayed 75.3 grams per tonne gold, 147 grams per tonne silver and 1.96 per cent lead over 0.6 metre (Assessment Report 17386). In 1988, samples from the vein in the Cherry shear assayed up to 2.16 grams per tonne gold and 0.9 gram per tonne silver over 1 metre, while samples from areas with no quartz veining assayed up to 20 grams per tonne gold, 1.05 per cent lead and 76 grams per tonne silver over 90 metres (Assessment Report 18706). Samples from disco</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$47k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P16" t="n">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Mohawk Oil Co. Ltd., Howard, Lennie Lee</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="V16" t="n">
-        <v>50.17861</v>
+        <v>58.15222</v>
       </c>
       <c r="W16" t="n">
-        <v>-118.54</v>
+        <v>-125.27778</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSE063</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -2006,35 +2010,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>092B  056</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2045,44 +2049,54 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>$234k</t>
+        </is>
+      </c>
       <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2010</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U17" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="V17" t="n">
-        <v>48.61472</v>
+        <v>49.47472</v>
       </c>
       <c r="W17" t="n">
-        <v>-123.59222</v>
+        <v>-121.51417</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -2092,30 +2106,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>092B  060</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3.6</v>
+        <v>21</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2131,25 +2145,35 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>$208k</t>
+        </is>
+      </c>
       <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2007</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
         <v>13</v>
@@ -2158,17 +2182,17 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>48.6075</v>
+        <v>58.73639</v>
       </c>
       <c r="W18" t="n">
-        <v>-123.57111</v>
+        <v>-133.24944</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -2178,21 +2202,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KING GEORGE (L.159)</t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>092B  011</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>East Sooke</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2201,7 +2225,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2217,44 +2241,54 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>13 t</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>$102k</t>
+        </is>
+      </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2019</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Volatus Capital Corp., Osborne, T.</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T19" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V19" t="n">
-        <v>48.36806</v>
+        <v>50.16611</v>
       </c>
       <c r="W19" t="n">
-        <v>-123.69528</v>
+        <v>-125.39944</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -2264,21 +2298,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>093M  076</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Kispiox</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.6</v>
+        <v>11.4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2287,7 +2321,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2303,44 +2337,682 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>$74k</t>
+        </is>
+      </c>
       <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1999</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
+        <v>12</v>
+      </c>
+      <c r="T20" t="n">
+        <v>300</v>
+      </c>
+      <c r="U20" t="n">
+        <v>61</v>
+      </c>
+      <c r="V20" t="n">
+        <v>52.85806</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-132.15722</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>092HSE058</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Hedley</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Copper</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Ag 10g/t, Au 9.6g/t</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>$64k</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1986</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>9</v>
+      </c>
+      <c r="T21" t="n">
+        <v>225</v>
+      </c>
+      <c r="U21" t="n">
+        <v>61</v>
+      </c>
+      <c r="V21" t="n">
+        <v>49.30889</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-120.00417</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACE                           </t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>104K  025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Callison Ranch</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Asbestos</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Prospect  </t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>$2k</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
         <v>13</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T22" t="n">
         <v>325</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U22" t="n">
+        <v>60</v>
+      </c>
+      <c r="V22" t="n">
+        <v>58.88222</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-132.1175</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>KATANGA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>092GNE009</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Williams Landing</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Gold, Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Au 62.0g/t</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>$4k</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>2</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Black Swan Gold Mines Ltd.</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>13</v>
+      </c>
+      <c r="T23" t="n">
+        <v>325</v>
+      </c>
+      <c r="U23" t="n">
+        <v>57</v>
+      </c>
+      <c r="V23" t="n">
+        <v>49.51111</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-122.57306</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>092B  060</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Cliffside</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>13</v>
+      </c>
+      <c r="T24" t="n">
+        <v>325</v>
+      </c>
+      <c r="U24" t="n">
         <v>55</v>
       </c>
-      <c r="V20" t="n">
-        <v>55.33556</v>
-      </c>
-      <c r="W20" t="n">
-        <v>-127.69194</v>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+      <c r="V24" t="n">
+        <v>48.6075</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-123.57111</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>092B  056</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Cliffside</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>13</v>
+      </c>
+      <c r="T25" t="n">
+        <v>325</v>
+      </c>
+      <c r="U25" t="n">
+        <v>55</v>
+      </c>
+      <c r="V25" t="n">
+        <v>48.61472</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-123.59222</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>KING GEORGE (L.159)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>092B  011</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>East Sooke</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>13 t</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>7</v>
+      </c>
+      <c r="T26" t="n">
+        <v>175</v>
+      </c>
+      <c r="U26" t="n">
+        <v>55</v>
+      </c>
+      <c r="V26" t="n">
+        <v>48.36806</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-123.69528</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROANAN                        </t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>104B  164</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Premier</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>13</v>
+      </c>
+      <c r="T27" t="n">
+        <v>325</v>
+      </c>
+      <c r="U27" t="n">
+        <v>55</v>
+      </c>
+      <c r="V27" t="n">
+        <v>56.00194</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-130.04972</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:X22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -762,35 +762,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CHARLIE</t>
+          <t>ERICKSEN-ASHBY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>092O  043</t>
+          <t>104K  009</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nemaiah Valley</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36.9</v>
+        <v>5.3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead</t>
+          <t>Silver, Lead, Zinc, Gold, Rhodonite</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -801,54 +801,54 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>907 kt</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 16.0g/t, Ag 224g/t</t>
+          <t>Au 0.9g/t, Ag 567g/t, Pb 5.68%, Zn 5.21%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>A chip sample assayed 279.9 grams per tonne silver, 10.6 grams per tonne gold and 13.68 per cent copper (Bulletin 81). The following year, samples from the East vein area assayed up to 0.48 per cent copper, 1.0 gram per tonne gold and 14.3 grams per tonne silver (Assessment Report 12105). In 1987, chip samples from the Charlie vein, taken over a length of 20 metres and width of 20 centimetres, averaged 22.1 grams per tonne gold and 224.0 grams per tonne silver, while a sample (AB 245B) of the DK vein assayed 9.9 grams per tonne gold, 95.8 grams per tonne silver and 0.14 per cent lead (Assessment Report 17038). A 20- centimetre sample of massive sulphide from the Big vein assayed 8.2 grams per tonne gold, 8557 grams per tonne silver and 26.0 per cent copper (Assessment Report 17038). In 199</t>
+          <t>3 intersected 20.2 metres which assayed 567.1 grams per tonne silver, 4.94 per cent lead and 4.22 per cent zinc; 4 intersected 5.1 metres which assayed 627.4 grams per tonne silver, 6.42 per cent lead and 6.2 per cent zinc (Assessment Report 10026). In 1981, a 15.1 metre drill intersection in mineralized cherts in Zone 8 assayed 173.1 grams per tonne silver, 1.2 per cent lead and 1.37 per cent zinc (Assessment Report 10026). Identified over an 8 metre width, some samples yielded high assays of 1203 grams per tonne silver, 23.23 per cent zinc, 20.24 per cent lead and 0.69 gram per tonne gold. Grab samples from the mineralized zone, 5 to 7 metres wide, of fine-grained pyrite, sphalerite, galena and quartz were assayed yielding 1.13 grams per tonne gold, 144.0 grams per tonne silver, 2.14 per</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>$6.3M</t>
+          <t>$286k</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="P4" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Galore Resources Inc., Suncor, Galore Resources Inc.; Zelon Enterprises Ltd.</t>
+          <t>Optima Minerals Inc., Northwind Ventures, Terratest</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
         <v>75</v>
       </c>
       <c r="V4" t="n">
-        <v>51.18028</v>
+        <v>58.65806</v>
       </c>
       <c r="W4" t="n">
-        <v>-123.67083</v>
+        <v>-133.475</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092O++043</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++009</t>
         </is>
       </c>
     </row>
@@ -858,30 +858,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ERICKSEN-ASHBY</t>
+          <t>DRIFTPILE CREEK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>104K  009</t>
+          <t>094K  066</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5.3</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold, Rhodonite</t>
+          <t>Zinc, Lead, Barite</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -897,54 +897,54 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>907 kt</t>
+          <t>18.1 Mt</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Au 0.9g/t, Ag 567g/t, Pb 5.68%, Zn 5.21%</t>
+          <t>Pb 1.18%, Zn 10.00%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3 intersected 20.2 metres which assayed 567.1 grams per tonne silver, 4.94 per cent lead and 4.22 per cent zinc; 4 intersected 5.1 metres which assayed 627.4 grams per tonne silver, 6.42 per cent lead and 6.2 per cent zinc (Assessment Report 10026). In 1981, a 15.1 metre drill intersection in mineralized cherts in Zone 8 assayed 173.1 grams per tonne silver, 1.2 per cent lead and 1.37 per cent zinc (Assessment Report 10026). Identified over an 8 metre width, some samples yielded high assays of 1203 grams per tonne silver, 23.23 per cent zinc, 20.24 per cent lead and 0.69 gram per tonne gold. Grab samples from the mineralized zone, 5 to 7 metres wide, of fine-grained pyrite, sphalerite, galena and quartz were assayed yielding 1.13 grams per tonne gold, 144.0 grams per tonne silver, 2.14 per</t>
+          <t>In 1980, it was reported that shallow drilling in 11 areas indicated reserves of approximately 18,145,000 tonnes averaging 2.38 per cent combined lead-zinc (Canadian Mines Handbook 1980-81, pages 280-281). In 1978, the best drill intersection from the North Trench zone (hole 78-07) was 11.7 metres grading 7.45 per cent combined lead and zinc, whereas drilling on the Ridge zone yielded 3 per cent combined lead and zinc over 26.2 metres and 4.14 per cent zinc over 7.5 metres in drillhole 78-09 (Assessment Report 7149 and 24609). In 1993, drilling on the Main zone intersected a 12-metre zone grading 10 per cent zinc and 1 per cent lead, including a zone of 6.02 metres grading 12.26 per cent zinc and 1.36 per cent lead in hole 93-56 (Assessment Report 23109). Several narrow high-grade intercep</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>$286k</t>
+          <t>$1.4M</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P5" t="n">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Optima Minerals Inc., Northwind Ventures, Terratest</t>
+          <t>Teck Exploration Ltd., Welcome North Mines Limited, Teck Corporation</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U5" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="V5" t="n">
-        <v>58.65806</v>
+        <v>58.06639</v>
       </c>
       <c r="W5" t="n">
-        <v>-133.475</v>
+        <v>-125.90972</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++009</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++066</t>
         </is>
       </c>
     </row>
@@ -954,30 +954,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DRIFTPILE CREEK</t>
+          <t>MAPLE LEAF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>094K  066</t>
+          <t>092F  039</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Kakawis</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>16.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Barite</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -993,54 +993,54 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>18.1 Mt</t>
+          <t>3 t</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Pb 1.18%, Zn 10.00%</t>
+          <t>Au 15.1g/t</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>In 1980, it was reported that shallow drilling in 11 areas indicated reserves of approximately 18,145,000 tonnes averaging 2.38 per cent combined lead-zinc (Canadian Mines Handbook 1980-81, pages 280-281). In 1978, the best drill intersection from the North Trench zone (hole 78-07) was 11.7 metres grading 7.45 per cent combined lead and zinc, whereas drilling on the Ridge zone yielded 3 per cent combined lead and zinc over 26.2 metres and 4.14 per cent zinc over 7.5 metres in drillhole 78-09 (Assessment Report 7149 and 24609). In 1993, drilling on the Main zone intersected a 12-metre zone grading 10 per cent zinc and 1 per cent lead, including a zone of 6.02 metres grading 12.26 per cent zinc and 1.36 per cent lead in hole 93-56 (Assessment Report 23109). Several narrow high-grade intercep</t>
+          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>$1.4M</t>
+          <t>$307k</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Teck Exploration Ltd., Welcome North Mines Limited, Teck Corporation</t>
+          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="V6" t="n">
-        <v>58.06639</v>
+        <v>49.27111</v>
       </c>
       <c r="W6" t="n">
-        <v>-125.90972</v>
+        <v>-125.73167</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++066</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
         </is>
       </c>
     </row>
@@ -1050,21 +1050,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MAPLE LEAF</t>
+          <t xml:space="preserve">EDYE PASS                     </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>092F  039</t>
+          <t>103J  015</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kakawis</t>
+          <t>Hunts Inlet</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.7</v>
+        <v>10.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,54 +1089,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3 t</t>
+          <t>226 kt</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 15.1g/t</t>
+          <t>Au 29.0g/t, Ag 10.0g/t</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
+          <t>Assays of a 1-metre wide vein yielded 29 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1935). The highest rock sample sample #780401 with 45g/t Au gold over a 45 centimetre width was located 60 m west of the drill pad where earlier exploration was conducted on the Cedar Vein system 200 m east of the historic Dawson workings in the area of the lineament of the Edye Shear zone.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$307k</t>
+          <t>$1.8M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P7" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
+          <t>Porcher Island Gold Corporation, Cathedral Gold Corp., Tombill Mines</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U7" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="V7" t="n">
-        <v>49.27111</v>
+        <v>54.0275</v>
       </c>
       <c r="W7" t="n">
-        <v>-125.73167</v>
+        <v>-130.585</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103J++015</t>
         </is>
       </c>
     </row>
@@ -1146,21 +1146,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>31.5</v>
+        <v>2.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,33 +1185,25 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P8" t="n">
-        <v>2022</v>
+        <v>1986</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1222,17 +1214,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V8" t="n">
-        <v>58.90944</v>
+        <v>49.7075</v>
       </c>
       <c r="W8" t="n">
-        <v>-129.09278</v>
+        <v>-116.00528</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1696,10 +1688,10 @@
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T13" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="U13" t="n">
         <v>65</v>
@@ -2106,30 +2098,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RED CAP - EAST CIRQUE</t>
+          <t>DALEY WEST</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>104K  141</t>
+          <t>093M  053</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>New Hazelton</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>21</v>
+        <v>2.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2150,28 +2142,28 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 3.7g/t, Ag 26.0g/t</t>
+          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
+          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$208k</t>
+          <t>$193k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>2007</v>
+        <v>2019</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
@@ -2185,14 +2177,14 @@
         <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>58.73639</v>
+        <v>55.22278</v>
       </c>
       <c r="W18" t="n">
-        <v>-133.24944</v>
+        <v>-127.56333</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
         </is>
       </c>
     </row>
@@ -2202,30 +2194,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5.6</v>
+        <v>7.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2241,54 +2233,54 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
-        <v>2019</v>
+        <v>1986</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T19" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U19" t="n">
         <v>61</v>
       </c>
       <c r="V19" t="n">
-        <v>50.16611</v>
+        <v>49.30889</v>
       </c>
       <c r="W19" t="n">
-        <v>-125.39944</v>
+        <v>-120.00417</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -2298,35 +2290,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HAIDA GOLD</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>103C  002</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sewell Inlet</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>11.4</v>
+        <v>37.4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2337,54 +2329,50 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>544 t</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Au 8.7g/t</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>$74k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>1999</v>
+        <v>1966</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U20" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V20" t="n">
-        <v>52.85806</v>
+        <v>58.88222</v>
       </c>
       <c r="W20" t="n">
-        <v>-132.15722</v>
+        <v>-132.1175</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2394,30 +2382,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>092B  060</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2438,49 +2426,39 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>$64k</t>
-        </is>
-      </c>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>2</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1986</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T21" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U21" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>49.30889</v>
+        <v>48.6075</v>
       </c>
       <c r="W21" t="n">
-        <v>-120.00417</v>
+        <v>-123.57111</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
         </is>
       </c>
     </row>
@@ -2490,35 +2468,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">SILVER BELL                   </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>093M  076</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Kispiox</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>37.4</v>
+        <v>1.6</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Gold, Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I22" t="b">
@@ -2529,31 +2507,25 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>$2k</t>
-        </is>
-      </c>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1966</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
         <v>13</v>
@@ -2562,457 +2534,17 @@
         <v>325</v>
       </c>
       <c r="U22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>58.88222</v>
+        <v>55.33556</v>
       </c>
       <c r="W22" t="n">
-        <v>-132.1175</v>
+        <v>-127.69194</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>KATANGA</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>092GNE009</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Williams Landing</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Au 62.0g/t</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>$4k</t>
-        </is>
-      </c>
-      <c r="O23" t="n">
-        <v>2</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Black Swan Gold Mines Ltd.</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>13</v>
-      </c>
-      <c r="T23" t="n">
-        <v>325</v>
-      </c>
-      <c r="U23" t="n">
-        <v>57</v>
-      </c>
-      <c r="V23" t="n">
-        <v>49.51111</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-122.57306</v>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>092B  060</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Cliffside</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>13</v>
-      </c>
-      <c r="T24" t="n">
-        <v>325</v>
-      </c>
-      <c r="U24" t="n">
-        <v>55</v>
-      </c>
-      <c r="V24" t="n">
-        <v>48.6075</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-123.57111</v>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>092B  056</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Cliffside</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>13</v>
-      </c>
-      <c r="T25" t="n">
-        <v>325</v>
-      </c>
-      <c r="U25" t="n">
-        <v>55</v>
-      </c>
-      <c r="V25" t="n">
-        <v>48.61472</v>
-      </c>
-      <c r="W25" t="n">
-        <v>-123.59222</v>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>KING GEORGE (L.159)</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>092B  011</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>East Sooke</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>13 t</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="n">
-        <v>7</v>
-      </c>
-      <c r="T26" t="n">
-        <v>175</v>
-      </c>
-      <c r="U26" t="n">
-        <v>55</v>
-      </c>
-      <c r="V26" t="n">
-        <v>48.36806</v>
-      </c>
-      <c r="W26" t="n">
-        <v>-123.69528</v>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ROANAN                        </t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>104B  164</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Premier</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I27" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="n">
-        <v>13</v>
-      </c>
-      <c r="T27" t="n">
-        <v>325</v>
-      </c>
-      <c r="U27" t="n">
-        <v>55</v>
-      </c>
-      <c r="V27" t="n">
-        <v>56.00194</v>
-      </c>
-      <c r="W27" t="n">
-        <v>-130.04972</v>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:X30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDYE PASS                     </t>
+          <t>WINCO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>103J  015</t>
+          <t>104I  019</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hunts Inlet</t>
+          <t>Boulder City</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10.7</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Silver, Copper, Lead, Gold, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,54 +1089,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>226 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 29.0g/t, Ag 10.0g/t</t>
+          <t>Ag 487g/t, Cu 9.85%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Assays of a 1-metre wide vein yielded 29 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1935). The highest rock sample sample #780401 with 45g/t Au gold over a 45 centimetre width was located 60 m west of the drill pad where earlier exploration was conducted on the Cedar Vein system 200 m east of the historic Dawson workings in the area of the lineament of the Edye Shear zone.</t>
+          <t>chip sample results include maximum values over 1 metre of 9.85 per cent copper and 486.86 grams per tonne silver;</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$1.8M</t>
+          <t>$3.2M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="P7" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Porcher Island Gold Corporation, Cathedral Gold Corp., Tombill Mines</t>
+          <t>Quartz Mountain Resources Ltd., Wyn Development Inc., Horseshoe Gold Mining Inc.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
         <v>70</v>
       </c>
       <c r="V7" t="n">
-        <v>54.0275</v>
+        <v>58.78</v>
       </c>
       <c r="W7" t="n">
-        <v>-130.585</v>
+        <v>-128.12222</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103J++015</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++019</t>
         </is>
       </c>
     </row>
@@ -1146,21 +1146,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>104I  098</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>McDame</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.2</v>
+        <v>31.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,25 +1185,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>1986</v>
+        <v>2022</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1214,17 +1222,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V8" t="n">
-        <v>49.7075</v>
+        <v>58.90944</v>
       </c>
       <c r="W8" t="n">
-        <v>-116.00528</v>
+        <v>-129.09278</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
         </is>
       </c>
     </row>
@@ -1234,35 +1242,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10.8</v>
+        <v>2.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1273,33 +1281,25 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P9" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1310,17 +1310,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="V9" t="n">
-        <v>50.53139</v>
+        <v>49.7075</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.2025</v>
+        <v>-116.00528</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1330,35 +1330,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.8</v>
+        <v>10.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,33 +1369,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>2018</v>
+        <v>1987</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1409,14 +1409,14 @@
         <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>49.73278</v>
+        <v>50.53139</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.21139</v>
+        <v>-125.2025</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1426,35 +1426,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V11" t="n">
-        <v>54.94444</v>
+        <v>49.73278</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.15722</v>
+        <v>-125.21139</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1522,35 +1522,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MAIN</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>092E  088</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.8</v>
+        <v>7.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Zinc</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1561,54 +1561,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$766k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O12" t="n">
         <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>1988</v>
+        <v>2012</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T12" t="n">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="U12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V12" t="n">
-        <v>49.29694</v>
+        <v>54.94444</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.08111</v>
+        <v>-126.15722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1618,30 +1618,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORMOND 3 (L.353)</t>
+          <t>MAGNET</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092E  012</t>
+          <t>092L  097</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Nimpkish</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.8</v>
+        <v>8.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Magnetite, Iron, Copper</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,49 +1662,49 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ag 127g/t, Cu 6.07%</t>
+          <t>Cu 15.40%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
+          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$750k</t>
+          <t>$780k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="P13" t="n">
-        <v>1988</v>
+        <v>2025</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Parallax Development Corp.</t>
+          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="U13" t="n">
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>49.29972</v>
+        <v>50.40806</v>
       </c>
       <c r="W13" t="n">
-        <v>-126.09722</v>
+        <v>-126.96167</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
         </is>
       </c>
     </row>
@@ -1714,30 +1714,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>092E  088</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>20.1</v>
+        <v>1.8</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1758,49 +1758,49 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$766k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>2019</v>
+        <v>1988</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U14" t="n">
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>57.94639</v>
+        <v>49.29694</v>
       </c>
       <c r="W14" t="n">
-        <v>-131.66722</v>
+        <v>-126.08111</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
         </is>
       </c>
     </row>
@@ -1810,21 +1810,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>ORMOND 3 (L.353)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>092E  012</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>36</v>
+        <v>2.8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1854,49 +1854,49 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Ag 127g/t, Cu 6.07%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$750k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>2022</v>
+        <v>1988</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>Parallax Development Corp.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U15" t="n">
         <v>65</v>
       </c>
       <c r="V15" t="n">
-        <v>58.185</v>
+        <v>49.29972</v>
       </c>
       <c r="W15" t="n">
-        <v>-125.30611</v>
+        <v>-126.09722</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
         </is>
       </c>
     </row>
@@ -1906,30 +1906,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t>RED CAP - SLOPE ZONE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>104K  010</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>39.3</v>
+        <v>20</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1950,28 +1950,28 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
+          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$666k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P16" t="n">
-        <v>2022</v>
+        <v>2007</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1985,14 +1985,14 @@
         <v>65</v>
       </c>
       <c r="V16" t="n">
-        <v>58.15222</v>
+        <v>58.73611</v>
       </c>
       <c r="W16" t="n">
-        <v>-125.27778</v>
+        <v>-133.27</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
         </is>
       </c>
     </row>
@@ -2002,35 +2002,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6.9</v>
+        <v>20.1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2041,54 +2041,54 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>2010</v>
+        <v>2019</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="V17" t="n">
-        <v>49.47472</v>
+        <v>57.94639</v>
       </c>
       <c r="W17" t="n">
-        <v>-121.51417</v>
+        <v>-131.66722</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -2098,35 +2098,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DALEY WEST</t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>093M  053</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>New Hazelton</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.7</v>
+        <v>6.9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -2137,54 +2137,54 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$193k</t>
+          <t>$234k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T18" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U18" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="V18" t="n">
-        <v>55.22278</v>
+        <v>49.47472</v>
       </c>
       <c r="W18" t="n">
-        <v>-127.56333</v>
+        <v>-121.51417</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -2194,21 +2194,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>7.5</v>
+        <v>21</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2233,54 +2233,54 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>1986</v>
+        <v>2007</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T19" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U19" t="n">
         <v>61</v>
       </c>
       <c r="V19" t="n">
-        <v>49.30889</v>
+        <v>58.73639</v>
       </c>
       <c r="W19" t="n">
-        <v>-120.00417</v>
+        <v>-133.24944</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -2290,35 +2290,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>DALEY WEST</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>093M  053</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>New Hazelton</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>37.4</v>
+        <v>2.7</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2329,29 +2329,33 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$193k</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>1966</v>
+        <v>2019</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
@@ -2362,17 +2366,17 @@
         <v>325</v>
       </c>
       <c r="U20" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V20" t="n">
-        <v>58.88222</v>
+        <v>55.22278</v>
       </c>
       <c r="W20" t="n">
-        <v>-132.1175</v>
+        <v>-127.56333</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
         </is>
       </c>
     </row>
@@ -2382,30 +2386,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>092B  060</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3.6</v>
+        <v>6.1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2426,20 +2430,30 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>$170k</t>
+        </is>
+      </c>
       <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
         <v>13</v>
@@ -2448,17 +2462,17 @@
         <v>325</v>
       </c>
       <c r="U21" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V21" t="n">
-        <v>48.6075</v>
+        <v>50.37417</v>
       </c>
       <c r="W21" t="n">
-        <v>-123.57111</v>
+        <v>-116.36167</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -2468,21 +2482,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>093M  076</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Kispiox</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.6</v>
+        <v>7.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2491,7 +2505,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2512,39 +2526,743 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>$64k</t>
+        </is>
+      </c>
       <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1986</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
+        <v>9</v>
+      </c>
+      <c r="T22" t="n">
+        <v>225</v>
+      </c>
+      <c r="U22" t="n">
+        <v>61</v>
+      </c>
+      <c r="V22" t="n">
+        <v>49.30889</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-120.00417</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACE                           </t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>104K  025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Callison Ranch</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Asbestos</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Prospect  </t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>$2k</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
         <v>13</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>325</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U23" t="n">
+        <v>60</v>
+      </c>
+      <c r="V23" t="n">
+        <v>58.88222</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-132.1175</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>092B  060</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Cliffside</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>13</v>
+      </c>
+      <c r="T24" t="n">
+        <v>325</v>
+      </c>
+      <c r="U24" t="n">
         <v>55</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V24" t="n">
+        <v>48.6075</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-123.57111</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>KING GEORGE (L.159)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>092B  011</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>East Sooke</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>13 t</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>7</v>
+      </c>
+      <c r="T25" t="n">
+        <v>175</v>
+      </c>
+      <c r="U25" t="n">
+        <v>55</v>
+      </c>
+      <c r="V25" t="n">
+        <v>48.36806</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-123.69528</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>092B  056</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Cliffside</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>13</v>
+      </c>
+      <c r="T26" t="n">
+        <v>325</v>
+      </c>
+      <c r="U26" t="n">
+        <v>55</v>
+      </c>
+      <c r="V26" t="n">
+        <v>48.61472</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-123.59222</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FISH CREEK</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>103O  005</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>13</v>
+      </c>
+      <c r="T27" t="n">
+        <v>325</v>
+      </c>
+      <c r="U27" t="n">
+        <v>55</v>
+      </c>
+      <c r="V27" t="n">
+        <v>55.99139</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-130.03694</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILVER BELL                   </t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>093M  076</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Kispiox</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Zinc, Lead</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>13</v>
+      </c>
+      <c r="T28" t="n">
+        <v>325</v>
+      </c>
+      <c r="U28" t="n">
+        <v>55</v>
+      </c>
+      <c r="V28" t="n">
         <v>55.33556</v>
       </c>
-      <c r="W22" t="n">
+      <c r="W28" t="n">
         <v>-127.69194</v>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SIXMILE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>103O  002</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>13</v>
+      </c>
+      <c r="T29" t="n">
+        <v>325</v>
+      </c>
+      <c r="U29" t="n">
+        <v>55</v>
+      </c>
+      <c r="V29" t="n">
+        <v>55.98833</v>
+      </c>
+      <c r="W29" t="n">
+        <v>-130.06194</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROANAN                        </t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>104B  164</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Premier</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>13</v>
+      </c>
+      <c r="T30" t="n">
+        <v>325</v>
+      </c>
+      <c r="U30" t="n">
+        <v>55</v>
+      </c>
+      <c r="V30" t="n">
+        <v>56.00194</v>
+      </c>
+      <c r="W30" t="n">
+        <v>-130.04972</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X30"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -1618,30 +1618,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MAGNET</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092L  097</t>
+          <t>092E  088</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nimpkish</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>8.4</v>
+        <v>1.8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Magnetite, Iron, Copper</t>
+          <t>Gold, Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,49 +1662,49 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Cu 15.40%</t>
+          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
+          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$780k</t>
+          <t>$766k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>2025</v>
+        <v>1988</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
+          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T13" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="U13" t="n">
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>50.40806</v>
+        <v>49.29694</v>
       </c>
       <c r="W13" t="n">
-        <v>-126.96167</v>
+        <v>-126.08111</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
         </is>
       </c>
     </row>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MAIN</t>
+          <t>ORMOND 3 (L.353)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>092E  088</t>
+          <t>092E  012</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1728,16 +1728,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Zinc</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1758,49 +1758,49 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
+          <t>Ag 127g/t, Cu 6.07%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
+          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$766k</t>
+          <t>$750k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
         <v>1988</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
+          <t>Parallax Development Corp.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T14" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="U14" t="n">
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>49.29694</v>
+        <v>49.29972</v>
       </c>
       <c r="W14" t="n">
-        <v>-126.08111</v>
+        <v>-126.09722</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
         </is>
       </c>
     </row>
@@ -1810,30 +1810,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ORMOND 3 (L.353)</t>
+          <t>RED CAP - SLOPE ZONE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>092E  012</t>
+          <t>104K  010</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2.8</v>
+        <v>20</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1854,49 +1854,49 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ag 127g/t, Cu 6.07%</t>
+          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
+          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$750k</t>
+          <t>$666k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="P15" t="n">
-        <v>1988</v>
+        <v>2007</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Parallax Development Corp.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>65</v>
       </c>
       <c r="V15" t="n">
-        <v>49.29972</v>
+        <v>58.73611</v>
       </c>
       <c r="W15" t="n">
-        <v>-126.09722</v>
+        <v>-133.27</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
         </is>
       </c>
     </row>
@@ -1906,30 +1906,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RED CAP - SLOPE ZONE</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>104K  010</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1950,28 +1950,28 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$666k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P16" t="n">
-        <v>2007</v>
+        <v>2019</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1985,14 +1985,14 @@
         <v>65</v>
       </c>
       <c r="V16" t="n">
-        <v>58.73611</v>
+        <v>57.94639</v>
       </c>
       <c r="W16" t="n">
-        <v>-133.27</v>
+        <v>-131.66722</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -2002,35 +2002,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>20.1</v>
+        <v>6.9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2041,54 +2041,54 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$234k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U17" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="V17" t="n">
-        <v>57.94639</v>
+        <v>49.47472</v>
       </c>
       <c r="W17" t="n">
-        <v>-131.66722</v>
+        <v>-121.51417</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -2098,35 +2098,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t>DALEY WEST</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>093M  053</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>New Hazelton</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6.9</v>
+        <v>2.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -2137,54 +2137,54 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$193k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>2010</v>
+        <v>2019</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>49.47472</v>
+        <v>55.22278</v>
       </c>
       <c r="W18" t="n">
-        <v>-121.51417</v>
+        <v>-127.56333</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
         </is>
       </c>
     </row>
@@ -2194,30 +2194,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RED CAP - EAST CIRQUE</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>104K  141</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>21</v>
+        <v>6.1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2233,33 +2233,33 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 3.7g/t, Ag 26.0g/t</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>$208k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>2007</v>
+        <v>2023</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
@@ -2273,14 +2273,14 @@
         <v>61</v>
       </c>
       <c r="V19" t="n">
-        <v>58.73639</v>
+        <v>50.37417</v>
       </c>
       <c r="W19" t="n">
-        <v>-133.24944</v>
+        <v>-116.36167</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -2290,21 +2290,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DALEY WEST</t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>093M  053</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>New Hazelton</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2334,28 +2334,28 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>$193k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
         <v>2019</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
@@ -2369,14 +2369,14 @@
         <v>61</v>
       </c>
       <c r="V20" t="n">
-        <v>55.22278</v>
+        <v>50.16611</v>
       </c>
       <c r="W20" t="n">
-        <v>-127.56333</v>
+        <v>-125.39944</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -2386,30 +2386,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6.1</v>
+        <v>7.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2430,49 +2430,49 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>2023</v>
+        <v>1986</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T21" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U21" t="n">
         <v>61</v>
       </c>
       <c r="V21" t="n">
-        <v>50.37417</v>
+        <v>49.30889</v>
       </c>
       <c r="W21" t="n">
-        <v>-116.36167</v>
+        <v>-120.00417</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -2482,35 +2482,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7.5</v>
+        <v>37.4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I22" t="b">
@@ -2521,54 +2521,50 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P22" t="n">
-        <v>1986</v>
+        <v>1966</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T22" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U22" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V22" t="n">
-        <v>49.30889</v>
+        <v>58.88222</v>
       </c>
       <c r="W22" t="n">
-        <v>-120.00417</v>
+        <v>-132.1175</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2578,35 +2574,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">SILVER BELL                   </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>093M  076</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Kispiox</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>37.4</v>
+        <v>1.6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Gold, Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I23" t="b">
@@ -2617,31 +2613,25 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>$2k</t>
-        </is>
-      </c>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
-        <v>1</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1966</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
         <v>13</v>
@@ -2650,619 +2640,17 @@
         <v>325</v>
       </c>
       <c r="U23" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>58.88222</v>
+        <v>55.33556</v>
       </c>
       <c r="W23" t="n">
-        <v>-132.1175</v>
+        <v>-127.69194</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>092B  060</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Cliffside</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>13</v>
-      </c>
-      <c r="T24" t="n">
-        <v>325</v>
-      </c>
-      <c r="U24" t="n">
-        <v>55</v>
-      </c>
-      <c r="V24" t="n">
-        <v>48.6075</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-123.57111</v>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>KING GEORGE (L.159)</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>092B  011</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>East Sooke</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>13 t</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>7</v>
-      </c>
-      <c r="T25" t="n">
-        <v>175</v>
-      </c>
-      <c r="U25" t="n">
-        <v>55</v>
-      </c>
-      <c r="V25" t="n">
-        <v>48.36806</v>
-      </c>
-      <c r="W25" t="n">
-        <v>-123.69528</v>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>092B  056</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Cliffside</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="n">
-        <v>13</v>
-      </c>
-      <c r="T26" t="n">
-        <v>325</v>
-      </c>
-      <c r="U26" t="n">
-        <v>55</v>
-      </c>
-      <c r="V26" t="n">
-        <v>48.61472</v>
-      </c>
-      <c r="W26" t="n">
-        <v>-123.59222</v>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>FISH CREEK</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>103O  005</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I27" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="n">
-        <v>13</v>
-      </c>
-      <c r="T27" t="n">
-        <v>325</v>
-      </c>
-      <c r="U27" t="n">
-        <v>55</v>
-      </c>
-      <c r="V27" t="n">
-        <v>55.99139</v>
-      </c>
-      <c r="W27" t="n">
-        <v>-130.03694</v>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>093M  076</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Kispiox</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Zinc, Lead</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I28" t="b">
-        <v>1</v>
-      </c>
-      <c r="J28" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="n">
-        <v>13</v>
-      </c>
-      <c r="T28" t="n">
-        <v>325</v>
-      </c>
-      <c r="U28" t="n">
-        <v>55</v>
-      </c>
-      <c r="V28" t="n">
-        <v>55.33556</v>
-      </c>
-      <c r="W28" t="n">
-        <v>-127.69194</v>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
           <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>SIXMILE</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>103O  002</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I29" t="b">
-        <v>1</v>
-      </c>
-      <c r="J29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="n">
-        <v>13</v>
-      </c>
-      <c r="T29" t="n">
-        <v>325</v>
-      </c>
-      <c r="U29" t="n">
-        <v>55</v>
-      </c>
-      <c r="V29" t="n">
-        <v>55.98833</v>
-      </c>
-      <c r="W29" t="n">
-        <v>-130.06194</v>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ROANAN                        </t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>104B  164</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Premier</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I30" t="b">
-        <v>1</v>
-      </c>
-      <c r="J30" t="b">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="n">
-        <v>13</v>
-      </c>
-      <c r="T30" t="n">
-        <v>325</v>
-      </c>
-      <c r="U30" t="n">
-        <v>55</v>
-      </c>
-      <c r="V30" t="n">
-        <v>56.00194</v>
-      </c>
-      <c r="W30" t="n">
-        <v>-130.04972</v>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:X24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1050,30 +1050,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WINCO</t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>104I  019</t>
+          <t>104I  098</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Boulder City</t>
+          <t>McDame</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>66.40000000000001</v>
+        <v>31.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Gold, Zinc</t>
+          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1094,28 +1094,28 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ag 487g/t, Cu 9.85%</t>
+          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>chip sample results include maximum values over 1 metre of 9.85 per cent copper and 486.86 grams per tonne silver;</t>
+          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$3.2M</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Quartz Mountain Resources Ltd., Wyn Development Inc., Horseshoe Gold Mining Inc.</t>
+          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1129,14 +1129,14 @@
         <v>70</v>
       </c>
       <c r="V7" t="n">
-        <v>58.78</v>
+        <v>58.90944</v>
       </c>
       <c r="W7" t="n">
-        <v>-128.12222</v>
+        <v>-129.09278</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++019</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
         </is>
       </c>
     </row>
@@ -1146,21 +1146,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>31.5</v>
+        <v>2.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,33 +1185,25 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P8" t="n">
-        <v>2022</v>
+        <v>1986</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1222,17 +1214,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V8" t="n">
-        <v>58.90944</v>
+        <v>49.7075</v>
       </c>
       <c r="W8" t="n">
-        <v>-129.09278</v>
+        <v>-116.00528</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1242,35 +1234,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2.2</v>
+        <v>10.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,25 +1273,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+          <t>118 kt (assay)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1310,17 +1310,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>49.7075</v>
+        <v>50.53139</v>
       </c>
       <c r="W9" t="n">
-        <v>-116.00528</v>
+        <v>-125.2025</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1330,35 +1330,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10.8</v>
+        <v>6.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,33 +1369,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>1987</v>
+        <v>2018</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1409,14 +1409,14 @@
         <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>50.53139</v>
+        <v>49.73278</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.2025</v>
+        <v>-125.21139</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1426,35 +1426,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U11" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>49.73278</v>
+        <v>54.94444</v>
       </c>
       <c r="W11" t="n">
-        <v>-125.21139</v>
+        <v>-126.15722</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1522,35 +1522,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>MAGNET</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092L  097</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Nimpkish</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Magnetite, Iron, Copper</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1561,54 +1561,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Cu 15.40%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$780k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P12" t="n">
-        <v>2012</v>
+        <v>2025</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T12" t="n">
-        <v>275</v>
+        <v>175</v>
       </c>
       <c r="U12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>54.94444</v>
+        <v>50.40806</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.15722</v>
+        <v>-126.96167</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
         </is>
       </c>
     </row>
@@ -1618,30 +1618,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MAIN</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092E  088</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.8</v>
+        <v>20.1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Zinc</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,49 +1662,49 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$766k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>1988</v>
+        <v>2019</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>49.29694</v>
+        <v>57.94639</v>
       </c>
       <c r="W13" t="n">
-        <v>-126.08111</v>
+        <v>-131.66722</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1714,21 +1714,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ORMOND 3 (L.353)</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>092E  012</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2.8</v>
+        <v>36</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1758,49 +1758,49 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 127g/t, Cu 6.07%</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$750k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P14" t="n">
-        <v>1988</v>
+        <v>2022</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Parallax Development Corp.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>49.29972</v>
+        <v>58.185</v>
       </c>
       <c r="W14" t="n">
-        <v>-126.09722</v>
+        <v>-125.30611</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RED CAP - SLOPE ZONE</t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>104K  010</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1824,16 +1824,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1854,21 +1854,21 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$666k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
         <v>2007</v>
@@ -1886,17 +1886,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V15" t="n">
-        <v>58.73611</v>
+        <v>58.73639</v>
       </c>
       <c r="W15" t="n">
-        <v>-133.27</v>
+        <v>-133.24944</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -1906,21 +1906,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>DALEY WEST</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>093M  053</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>New Hazelton</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>20.1</v>
+        <v>2.7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1950,28 +1950,28 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$193k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
         <v>2019</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1982,17 +1982,17 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V16" t="n">
-        <v>57.94639</v>
+        <v>55.22278</v>
       </c>
       <c r="W16" t="n">
-        <v>-131.66722</v>
+        <v>-127.56333</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
         </is>
       </c>
     </row>
@@ -2002,35 +2002,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6.9</v>
+        <v>6.1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2041,54 +2041,54 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>2010</v>
+        <v>2023</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>49.47472</v>
+        <v>50.37417</v>
       </c>
       <c r="W17" t="n">
-        <v>-121.51417</v>
+        <v>-116.36167</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -2098,21 +2098,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DALEY WEST</t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>093M  053</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>New Hazelton</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2142,28 +2142,28 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$193k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
         <v>2019</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
@@ -2177,14 +2177,14 @@
         <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>55.22278</v>
+        <v>50.16611</v>
       </c>
       <c r="W18" t="n">
-        <v>-127.56333</v>
+        <v>-125.39944</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -2194,35 +2194,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6.1</v>
+        <v>37.4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2233,33 +2233,29 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>2023</v>
+        <v>1966</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
@@ -2270,17 +2266,17 @@
         <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V19" t="n">
-        <v>50.37417</v>
+        <v>58.88222</v>
       </c>
       <c r="W19" t="n">
-        <v>-116.36167</v>
+        <v>-132.1175</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2290,30 +2286,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t>AVON</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>092F  350</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Chetarpe</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5.6</v>
+        <v>24.6</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2334,49 +2330,49 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Au 47.3g/t, Ag 53.1g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$33k</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>2019</v>
+        <v>1985</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U20" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="V20" t="n">
-        <v>50.16611</v>
+        <v>49.40417</v>
       </c>
       <c r="W20" t="n">
-        <v>-125.39944</v>
+        <v>-125.75833</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
         </is>
       </c>
     </row>
@@ -2386,21 +2382,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t>KATANGA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>092GNE009</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Williams Landing</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2409,7 +2405,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2425,54 +2421,54 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Au 62.0g/t</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$4k</t>
         </is>
       </c>
       <c r="O21" t="n">
         <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>Black Swan Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T21" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U21" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="V21" t="n">
-        <v>49.30889</v>
+        <v>49.51111</v>
       </c>
       <c r="W21" t="n">
-        <v>-120.00417</v>
+        <v>-122.57306</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
         </is>
       </c>
     </row>
@@ -2482,35 +2478,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">SILVER BELL                   </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>093M  076</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Kispiox</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>37.4</v>
+        <v>1.6</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Gold, Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I22" t="b">
@@ -2521,31 +2517,25 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>$2k</t>
-        </is>
-      </c>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1966</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
         <v>13</v>
@@ -2554,17 +2544,17 @@
         <v>325</v>
       </c>
       <c r="U22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>58.88222</v>
+        <v>55.33556</v>
       </c>
       <c r="W22" t="n">
-        <v>-132.1175</v>
+        <v>-127.69194</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
         </is>
       </c>
     </row>
@@ -2574,30 +2564,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>093M  076</t>
+          <t>092B  060</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Kispiox</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead</t>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2618,12 +2608,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2643,14 +2633,100 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>55.33556</v>
+        <v>48.6075</v>
       </c>
       <c r="W23" t="n">
-        <v>-127.69194</v>
+        <v>-123.57111</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROANAN                        </t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>104B  164</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Premier</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>13</v>
+      </c>
+      <c r="T24" t="n">
+        <v>325</v>
+      </c>
+      <c r="U24" t="n">
+        <v>55</v>
+      </c>
+      <c r="V24" t="n">
+        <v>56.00194</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-130.04972</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:X25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1050,30 +1050,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t>WINCO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>104I  019</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>Boulder City</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>31.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Silver, Copper, Lead, Gold, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1094,28 +1094,28 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
+          <t>Ag 487g/t, Cu 9.85%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
+          <t>chip sample results include maximum values over 1 metre of 9.85 per cent copper and 486.86 grams per tonne silver;</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$3.2M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P7" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>Quartz Mountain Resources Ltd., Wyn Development Inc., Horseshoe Gold Mining Inc.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1129,14 +1129,14 @@
         <v>70</v>
       </c>
       <c r="V7" t="n">
-        <v>58.90944</v>
+        <v>58.78</v>
       </c>
       <c r="W7" t="n">
-        <v>-129.09278</v>
+        <v>-128.12222</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++019</t>
         </is>
       </c>
     </row>
@@ -1146,21 +1146,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>104I  098</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>McDame</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.2</v>
+        <v>31.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,25 +1185,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>1986</v>
+        <v>2022</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1214,17 +1222,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V8" t="n">
-        <v>49.7075</v>
+        <v>58.90944</v>
       </c>
       <c r="W8" t="n">
-        <v>-116.00528</v>
+        <v>-129.09278</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
         </is>
       </c>
     </row>
@@ -1234,35 +1242,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10.8</v>
+        <v>2.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1273,33 +1281,25 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P9" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1310,17 +1310,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="V9" t="n">
-        <v>50.53139</v>
+        <v>49.7075</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.2025</v>
+        <v>-116.00528</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1330,35 +1330,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.8</v>
+        <v>10.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,33 +1369,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>2018</v>
+        <v>1987</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1409,14 +1409,14 @@
         <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>49.73278</v>
+        <v>50.53139</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.21139</v>
+        <v>-125.2025</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1426,35 +1426,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V11" t="n">
-        <v>54.94444</v>
+        <v>49.73278</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.15722</v>
+        <v>-125.21139</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1522,35 +1522,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MAGNET</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>092L  097</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nimpkish</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Magnetite, Iron, Copper</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1561,54 +1561,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 15.40%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$780k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>2025</v>
+        <v>2012</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T12" t="n">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="U12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V12" t="n">
-        <v>50.40806</v>
+        <v>54.94444</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.96167</v>
+        <v>-126.15722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1618,30 +1618,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>092E  088</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>20.1</v>
+        <v>1.8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,49 +1662,49 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$766k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>2019</v>
+        <v>1988</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U13" t="n">
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>57.94639</v>
+        <v>49.29694</v>
       </c>
       <c r="W13" t="n">
-        <v>-131.66722</v>
+        <v>-126.08111</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
         </is>
       </c>
     </row>
@@ -1714,30 +1714,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>RED CAP - SLOPE ZONE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>104K  010</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1758,28 +1758,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$666k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P14" t="n">
-        <v>2022</v>
+        <v>2007</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1793,14 +1793,14 @@
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>58.185</v>
+        <v>58.73611</v>
       </c>
       <c r="W14" t="n">
-        <v>-125.30611</v>
+        <v>-133.27</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
         </is>
       </c>
     </row>
@@ -1810,30 +1810,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RED CAP - EAST CIRQUE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>104K  141</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1854,28 +1854,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 3.7g/t, Ag 26.0g/t</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$208k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>2007</v>
+        <v>2022</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1886,17 +1886,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V15" t="n">
-        <v>58.73639</v>
+        <v>58.185</v>
       </c>
       <c r="W15" t="n">
-        <v>-133.24944</v>
+        <v>-125.30611</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1906,21 +1906,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DALEY WEST</t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>093M  053</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>New Hazelton</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2.7</v>
+        <v>39.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Lead, Zinc, Tungsten</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1950,28 +1950,28 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 3.9g/t, Ag 215g/t, Cu 7.00%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>A 38-centimetre-wide channel sample, taken from the face of the main adit, assayed 1.4 grams per tonne gold, 47.0 grams per tonne silver and 1.92 per cent copper (Geological Survey of Canada Memoir 223). A sample above the main adit assayed 6.32 grams gold, 215 parts per million silver, 7 per cent copper, and is anomalous in cobalt, bismuth, arsenic (Assessment Report 33297). A chip sample taken from above the main adit is reported to have assayed 6.32 grams per tonne gold, 215 grams per tonne silver and 7 per cent copper (Reeder, J.J.</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$193k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P16" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Primary Energy Metals Inc., Primary Cobalt Corp.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1982,17 +1982,17 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V16" t="n">
-        <v>55.22278</v>
+        <v>58.15222</v>
       </c>
       <c r="W16" t="n">
-        <v>-127.56333</v>
+        <v>-125.27778</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++053</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -2002,30 +2002,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6.1</v>
+        <v>21</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2041,33 +2041,33 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>2023</v>
+        <v>2007</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -2081,14 +2081,14 @@
         <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>50.37417</v>
+        <v>58.73639</v>
       </c>
       <c r="W17" t="n">
-        <v>-116.36167</v>
+        <v>-133.24944</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -2098,21 +2098,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2137,33 +2137,33 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
@@ -2177,14 +2177,14 @@
         <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>50.16611</v>
+        <v>50.37417</v>
       </c>
       <c r="W18" t="n">
-        <v>-125.39944</v>
+        <v>-116.36167</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -2194,35 +2194,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>37.4</v>
+        <v>5.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2233,29 +2233,33 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Cu 9.10%</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P19" t="n">
-        <v>1966</v>
+        <v>2019</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
@@ -2266,17 +2270,17 @@
         <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V19" t="n">
-        <v>58.88222</v>
+        <v>50.16611</v>
       </c>
       <c r="W19" t="n">
-        <v>-132.1175</v>
+        <v>-125.39944</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -2286,21 +2290,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AVON</t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>092F  350</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Chetarpe</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>24.6</v>
+        <v>11.4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2309,7 +2313,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2325,54 +2329,54 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 47.3g/t, Ag 53.1g/t</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>$33k</t>
+          <t>$74k</t>
         </is>
       </c>
       <c r="O20" t="n">
         <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>1985</v>
+        <v>1999</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="T20" t="n">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="U20" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="V20" t="n">
-        <v>49.40417</v>
+        <v>52.85806</v>
       </c>
       <c r="W20" t="n">
-        <v>-125.75833</v>
+        <v>-132.15722</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -2382,35 +2386,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KATANGA</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>092GNE009</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Williams Landing</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>9.5</v>
+        <v>37.4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I21" t="b">
@@ -2421,33 +2425,29 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Au 62.0g/t</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>$4k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>1985</v>
+        <v>1966</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Black Swan Gold Mines Ltd.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
@@ -2458,17 +2458,17 @@
         <v>325</v>
       </c>
       <c r="U21" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="V21" t="n">
-        <v>49.51111</v>
+        <v>58.88222</v>
       </c>
       <c r="W21" t="n">
-        <v>-122.57306</v>
+        <v>-132.1175</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2478,21 +2478,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
+          <t>KATANGA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>093M  076</t>
+          <t>092GNE009</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Kispiox</t>
+          <t>Williams Landing</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.6</v>
+        <v>9.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2517,25 +2517,35 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+          <t>Au 62.0g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>$4k</t>
+        </is>
+      </c>
       <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Black Swan Gold Mines Ltd.</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
         <v>13</v>
@@ -2544,17 +2554,17 @@
         <v>325</v>
       </c>
       <c r="U22" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V22" t="n">
-        <v>55.33556</v>
+        <v>49.51111</v>
       </c>
       <c r="W22" t="n">
-        <v>-127.69194</v>
+        <v>-122.57306</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
         </is>
       </c>
     </row>
@@ -2564,30 +2574,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
+          <t xml:space="preserve">SILVER BELL                   </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>092B  060</t>
+          <t>093M  076</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Kispiox</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+          <t>Gold, Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2608,12 +2618,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2633,14 +2643,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>48.6075</v>
+        <v>55.33556</v>
       </c>
       <c r="W23" t="n">
-        <v>-123.57111</v>
+        <v>-127.69194</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
         </is>
       </c>
     </row>
@@ -2650,30 +2660,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROANAN                        </t>
+          <t xml:space="preserve">CORMORANT                     </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>104B  164</t>
+          <t>092K  098</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Premier</t>
+          <t>Granite Bay</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2694,12 +2704,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2710,21 +2720,107 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T24" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U24" t="n">
         <v>55</v>
       </c>
       <c r="V24" t="n">
+        <v>50.18694</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-125.28056</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROANAN                        </t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>104B  164</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Premier</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>13</v>
+      </c>
+      <c r="T25" t="n">
+        <v>325</v>
+      </c>
+      <c r="U25" t="n">
+        <v>55</v>
+      </c>
+      <c r="V25" t="n">
         <v>56.00194</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W25" t="n">
         <v>-130.04972</v>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -1050,30 +1050,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WINCO</t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>104I  019</t>
+          <t>104I  098</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Boulder City</t>
+          <t>McDame</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>66.40000000000001</v>
+        <v>31.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Gold, Zinc</t>
+          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1094,28 +1094,28 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ag 487g/t, Cu 9.85%</t>
+          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>chip sample results include maximum values over 1 metre of 9.85 per cent copper and 486.86 grams per tonne silver;</t>
+          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$3.2M</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Quartz Mountain Resources Ltd., Wyn Development Inc., Horseshoe Gold Mining Inc.</t>
+          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1129,14 +1129,14 @@
         <v>70</v>
       </c>
       <c r="V7" t="n">
-        <v>58.78</v>
+        <v>58.90944</v>
       </c>
       <c r="W7" t="n">
-        <v>-128.12222</v>
+        <v>-129.09278</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++019</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
         </is>
       </c>
     </row>
@@ -1146,21 +1146,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>31.5</v>
+        <v>2.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,33 +1185,25 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P8" t="n">
-        <v>2022</v>
+        <v>1986</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1222,17 +1214,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V8" t="n">
-        <v>58.90944</v>
+        <v>49.7075</v>
       </c>
       <c r="W8" t="n">
-        <v>-129.09278</v>
+        <v>-116.00528</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1242,30 +1234,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2.2</v>
+        <v>7.4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1281,46 +1273,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+          <t>119.0 Mt</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Cu 0.43%</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>1986</v>
+        <v>2012</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U9" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>49.7075</v>
+        <v>54.94444</v>
       </c>
       <c r="W9" t="n">
-        <v>-116.00528</v>
+        <v>-126.15722</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1522,35 +1522,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092E  088</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7.4</v>
+        <v>1.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Gold, Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1561,54 +1561,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$766k</t>
         </is>
       </c>
       <c r="O12" t="n">
         <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>2012</v>
+        <v>1988</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T12" t="n">
-        <v>275</v>
+        <v>200</v>
       </c>
       <c r="U12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>54.94444</v>
+        <v>49.29694</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.15722</v>
+        <v>-126.08111</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
         </is>
       </c>
     </row>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MAIN</t>
+          <t>ORMOND 3 (L.353)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092E  088</t>
+          <t>092E  012</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1632,16 +1632,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Zinc</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,28 +1662,28 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
+          <t>Ag 127g/t, Cu 6.07%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
+          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$766k</t>
+          <t>$750k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
         <v>1988</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
+          <t>Parallax Development Corp.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -1697,14 +1697,14 @@
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>49.29694</v>
+        <v>49.29972</v>
       </c>
       <c r="W13" t="n">
-        <v>-126.08111</v>
+        <v>-126.09722</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
         </is>
       </c>
     </row>
@@ -1714,30 +1714,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RED CAP - SLOPE ZONE</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>104K  010</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1758,28 +1758,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$666k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>2007</v>
+        <v>2019</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1793,14 +1793,14 @@
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>58.73611</v>
+        <v>57.94639</v>
       </c>
       <c r="W14" t="n">
-        <v>-133.27</v>
+        <v>-131.66722</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -2098,21 +2098,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2137,33 +2137,33 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
@@ -2177,14 +2177,14 @@
         <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>50.37417</v>
+        <v>50.16611</v>
       </c>
       <c r="W18" t="n">
-        <v>-116.36167</v>
+        <v>-125.39944</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -2194,35 +2194,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5.6</v>
+        <v>37.4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2233,33 +2233,29 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Cu 9.10%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>2019</v>
+        <v>1966</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
@@ -2270,17 +2266,17 @@
         <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V19" t="n">
-        <v>50.16611</v>
+        <v>58.88222</v>
       </c>
       <c r="W19" t="n">
-        <v>-125.39944</v>
+        <v>-132.1175</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2290,21 +2286,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HAIDA GOLD</t>
+          <t xml:space="preserve">MIDNIGHT NAILS 1-2            </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>103C  002</t>
+          <t>082LSE063</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sewell Inlet</t>
+          <t>Cherryville</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>11.4</v>
+        <v>8.1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2313,7 +2309,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2329,54 +2325,54 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>544 t</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 8.7g/t</t>
+          <t>Au 11.1g/t, Ag 76.0g/t, Pb 1.05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+          <t>In 1983, samples from the Cherry shear assayed up to 158 grams per tonne gold and 1251 grams per tonne silver, while a sample of the altered dike or sill assayed 4.2 per cent lead, 1.86 per cent zinc, 42.2 grams per tonne gold and 212.5 grams per tonne silver (Assessment Report 11892). In 1987, a sample (R-7) wall rock adjacent to the vein assayed 75.3 grams per tonne gold, 147 grams per tonne silver and 1.96 per cent lead over 0.6 metre (Assessment Report 17386). In 1988, samples from the vein in the Cherry shear assayed up to 2.16 grams per tonne gold and 0.9 gram per tonne silver over 1 metre, while samples from areas with no quartz veining assayed up to 20 grams per tonne gold, 1.05 per cent lead and 76 grams per tonne silver over 90 metres (Assessment Report 18706). Samples from disco</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>$74k</t>
+          <t>$47k</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P20" t="n">
-        <v>1999</v>
+        <v>2026</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+          <t>Mohawk Oil Co. Ltd., Howard, Lennie Lee</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="U20" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="V20" t="n">
-        <v>52.85806</v>
+        <v>50.17861</v>
       </c>
       <c r="W20" t="n">
-        <v>-132.15722</v>
+        <v>-118.54</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSE063</t>
         </is>
       </c>
     </row>
@@ -2386,35 +2382,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>KING GEORGE (L.159)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>092B  011</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>East Sooke</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>37.4</v>
+        <v>0.8</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I21" t="b">
@@ -2425,50 +2421,44 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>13 t</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>$2k</t>
-        </is>
-      </c>
+          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1966</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T21" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U21" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>58.88222</v>
+        <v>48.36806</v>
       </c>
       <c r="W21" t="n">
-        <v>-132.1175</v>
+        <v>-123.69528</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
         </is>
       </c>
     </row>
@@ -2478,30 +2468,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KATANGA</t>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>092GNE009</t>
+          <t>092B  056</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Williams Landing</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>9.5</v>
+        <v>1.9</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2517,35 +2507,25 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 62.0g/t</t>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>$4k</t>
-        </is>
-      </c>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>2</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Black Swan Gold Mines Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
         <v>13</v>
@@ -2554,17 +2534,17 @@
         <v>325</v>
       </c>
       <c r="U22" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>49.51111</v>
+        <v>48.61472</v>
       </c>
       <c r="W22" t="n">
-        <v>-122.57306</v>
+        <v>-123.59222</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
         </is>
       </c>
     </row>
@@ -2574,30 +2554,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>093M  076</t>
+          <t>092B  060</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Kispiox</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead</t>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2618,12 +2598,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2643,14 +2623,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>55.33556</v>
+        <v>48.6075</v>
       </c>
       <c r="W23" t="n">
-        <v>-127.69194</v>
+        <v>-123.57111</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
         </is>
       </c>
     </row>
@@ -2660,30 +2640,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORMORANT                     </t>
+          <t xml:space="preserve">SILVER BELL                   </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>092K  098</t>
+          <t>093M  076</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Granite Bay</t>
+          <t>Kispiox</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2704,12 +2684,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2720,23 +2700,23 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T24" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U24" t="n">
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>50.18694</v>
+        <v>55.33556</v>
       </c>
       <c r="W24" t="n">
-        <v>-125.28056</v>
+        <v>-127.69194</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
         </is>
       </c>
     </row>
@@ -2746,30 +2726,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROANAN                        </t>
+          <t xml:space="preserve">CORMORANT                     </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>104B  164</t>
+          <t>092K  098</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Premier</t>
+          <t>Granite Bay</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2790,12 +2770,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2806,23 +2786,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T25" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U25" t="n">
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>56.00194</v>
+        <v>50.18694</v>
       </c>
       <c r="W25" t="n">
-        <v>-130.04972</v>
+        <v>-125.28056</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:X27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1234,21 +1234,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.4</v>
+        <v>10.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1273,54 +1273,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2012</v>
+        <v>1987</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>54.94444</v>
+        <v>50.53139</v>
       </c>
       <c r="W9" t="n">
-        <v>-126.15722</v>
+        <v>-125.2025</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1330,35 +1330,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10.8</v>
+        <v>6.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,33 +1369,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>1987</v>
+        <v>2018</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1409,14 +1409,14 @@
         <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>50.53139</v>
+        <v>49.73278</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.2025</v>
+        <v>-125.21139</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1426,35 +1426,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U11" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>49.73278</v>
+        <v>54.94444</v>
       </c>
       <c r="W11" t="n">
-        <v>-125.21139</v>
+        <v>-126.15722</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1618,30 +1618,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORMOND 3 (L.353)</t>
+          <t>RED CAP - SLOPE ZONE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092E  012</t>
+          <t>104K  010</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.8</v>
+        <v>20</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,49 +1662,49 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ag 127g/t, Cu 6.07%</t>
+          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
+          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$750k</t>
+          <t>$666k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="P13" t="n">
-        <v>1988</v>
+        <v>2007</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Parallax Development Corp.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>49.29972</v>
+        <v>58.73611</v>
       </c>
       <c r="W13" t="n">
-        <v>-126.09722</v>
+        <v>-133.27</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
         </is>
       </c>
     </row>
@@ -1714,21 +1714,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>20.1</v>
+        <v>36</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1758,28 +1758,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P14" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1793,14 +1793,14 @@
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>57.94639</v>
+        <v>58.185</v>
       </c>
       <c r="W14" t="n">
-        <v>-131.66722</v>
+        <v>-125.30611</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>36</v>
+        <v>39.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1854,28 +1854,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P15" t="n">
         <v>2022</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1889,14 +1889,14 @@
         <v>65</v>
       </c>
       <c r="V15" t="n">
-        <v>58.185</v>
+        <v>58.15222</v>
       </c>
       <c r="W15" t="n">
-        <v>-125.30611</v>
+        <v>-125.27778</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -1906,21 +1906,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>39.3</v>
+        <v>6.1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1945,33 +1945,33 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1982,17 +1982,17 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V16" t="n">
-        <v>58.15222</v>
+        <v>50.37417</v>
       </c>
       <c r="W16" t="n">
-        <v>-125.27778</v>
+        <v>-116.36167</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -2002,21 +2002,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RED CAP - EAST CIRQUE</t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>104K  141</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>21</v>
+        <v>11.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2041,54 +2041,54 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 3.7g/t, Ag 26.0g/t</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$208k</t>
+          <t>$74k</t>
         </is>
       </c>
       <c r="O17" t="n">
         <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>2007</v>
+        <v>1999</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U17" t="n">
         <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>58.73639</v>
+        <v>52.85806</v>
       </c>
       <c r="W17" t="n">
-        <v>-133.24944</v>
+        <v>-132.15722</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -2098,30 +2098,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5.6</v>
+        <v>7.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2137,54 +2137,54 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>2019</v>
+        <v>1986</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T18" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U18" t="n">
         <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>50.16611</v>
+        <v>49.30889</v>
       </c>
       <c r="W18" t="n">
-        <v>-125.39944</v>
+        <v>-120.00417</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -2286,30 +2286,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIDNIGHT NAILS 1-2            </t>
+          <t xml:space="preserve">JOHN BULL                     </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>082LSE063</t>
+          <t>092F  146</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cherryville</t>
+          <t>toxʷnač</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.1</v>
+        <v>3.3</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc</t>
+          <t>Zinc, Silver, Copper, Lead, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 11.1g/t, Ag 76.0g/t, Pb 1.05%</t>
+          <t>Ag 150.83g/t, Au 23.99g/t, Cu 0.8%, Pb 2%, Zn 52%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>In 1983, samples from the Cherry shear assayed up to 158 grams per tonne gold and 1251 grams per tonne silver, while a sample of the altered dike or sill assayed 4.2 per cent lead, 1.86 per cent zinc, 42.2 grams per tonne gold and 212.5 grams per tonne silver (Assessment Report 11892). In 1987, a sample (R-7) wall rock adjacent to the vein assayed 75.3 grams per tonne gold, 147 grams per tonne silver and 1.96 per cent lead over 0.6 metre (Assessment Report 17386). In 1988, samples from the vein in the Cherry shear assayed up to 2.16 grams per tonne gold and 0.9 gram per tonne silver over 1 metre, while samples from areas with no quartz veining assayed up to 20 grams per tonne gold, 1.05 per cent lead and 76 grams per tonne silver over 90 metres (Assessment Report 18706). Samples from disco</t>
+          <t>The best assays from several samples were 52 per cent zinc, 150.83 grams per tonne silver, 0.8 per cent copper, 2.0 per cent lead and 23.99 grams per tonne gold (Minister of Mines Annual Report 1926, page A312).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2344,35 +2344,35 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P20" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Mohawk Oil Co. Ltd., Howard, Lennie Lee</t>
+          <t>Aquarius Resources Limited, Geiger, K. Warren</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T20" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="U20" t="n">
         <v>57</v>
       </c>
       <c r="V20" t="n">
-        <v>50.17861</v>
+        <v>49.94611</v>
       </c>
       <c r="W20" t="n">
-        <v>-118.54</v>
+        <v>-124.71056</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSE063</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++146</t>
         </is>
       </c>
     </row>
@@ -2382,30 +2382,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KING GEORGE (L.159)</t>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>092B  011</t>
+          <t>092B  056</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>East Sooke</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2421,17 +2421,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>13 t</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2442,23 +2442,23 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T21" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="U21" t="n">
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>48.36806</v>
+        <v>48.61472</v>
       </c>
       <c r="W21" t="n">
-        <v>-123.69528</v>
+        <v>-123.59222</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
         </is>
       </c>
     </row>
@@ -2468,12 +2468,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>092B  056</t>
+          <t>092B  060</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2512,12 +2512,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2537,14 +2537,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>48.61472</v>
+        <v>48.6075</v>
       </c>
       <c r="W22" t="n">
-        <v>-123.59222</v>
+        <v>-123.57111</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
         </is>
       </c>
     </row>
@@ -2554,30 +2554,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>092B  060</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2593,17 +2593,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2623,14 +2623,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>48.6075</v>
+        <v>55.99139</v>
       </c>
       <c r="W23" t="n">
-        <v>-123.57111</v>
+        <v>-130.03694</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
         </is>
       </c>
     </row>
@@ -2640,21 +2640,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
+          <t xml:space="preserve">ROANAN                        </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>093M  076</t>
+          <t>104B  164</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Kispiox</t>
+          <t>Premier</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2709,14 +2709,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>55.33556</v>
+        <v>56.00194</v>
       </c>
       <c r="W24" t="n">
-        <v>-127.69194</v>
+        <v>-130.04972</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>
       </c>
     </row>
@@ -2726,30 +2726,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORMORANT                     </t>
+          <t>SIXMILE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>092K  098</t>
+          <t>103O  002</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Granite Bay</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2765,17 +2765,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2786,23 +2786,195 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T25" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U25" t="n">
         <v>55</v>
       </c>
       <c r="V25" t="n">
+        <v>55.98833</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-130.06194</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CORMORANT                     </t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>092K  098</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Granite Bay</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="n">
+        <v>250</v>
+      </c>
+      <c r="U26" t="n">
+        <v>55</v>
+      </c>
+      <c r="V26" t="n">
         <v>50.18694</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W26" t="n">
         <v>-125.28056</v>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILVER BELL                   </t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>093M  076</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Kispiox</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Zinc, Lead</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>13</v>
+      </c>
+      <c r="T27" t="n">
+        <v>325</v>
+      </c>
+      <c r="U27" t="n">
+        <v>55</v>
+      </c>
+      <c r="V27" t="n">
+        <v>55.33556</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-127.69194</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -1050,21 +1050,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>31.5</v>
+        <v>2.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,33 +1089,25 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P7" t="n">
-        <v>2022</v>
+        <v>1986</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1126,17 +1118,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V7" t="n">
-        <v>58.90944</v>
+        <v>49.7075</v>
       </c>
       <c r="W7" t="n">
-        <v>-129.09278</v>
+        <v>-116.00528</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1146,35 +1138,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.2</v>
+        <v>10.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,25 +1177,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+          <t>118 kt (assay)</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1214,17 +1214,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V8" t="n">
-        <v>49.7075</v>
+        <v>50.53139</v>
       </c>
       <c r="W8" t="n">
-        <v>-116.00528</v>
+        <v>-125.2025</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1234,35 +1234,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10.8</v>
+        <v>6.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1273,33 +1273,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>1987</v>
+        <v>2018</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1313,14 +1313,14 @@
         <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>50.53139</v>
+        <v>49.73278</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.2025</v>
+        <v>-125.21139</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1330,35 +1330,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,54 +1369,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>49.73278</v>
+        <v>54.94444</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.21139</v>
+        <v>-126.15722</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1426,35 +1426,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>MAGNET</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092L  097</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Nimpkish</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Magnetite, Iron, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Cu 15.40%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$780k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P11" t="n">
-        <v>2012</v>
+        <v>2025</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T11" t="n">
-        <v>275</v>
+        <v>175</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>54.94444</v>
+        <v>50.40806</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.15722</v>
+        <v>-126.96167</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
         </is>
       </c>
     </row>
@@ -1618,30 +1618,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RED CAP - SLOPE ZONE</t>
+          <t>ORMOND 3 (L.353)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>104K  010</t>
+          <t>092E  012</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>2.8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,49 +1662,49 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
+          <t>Ag 127g/t, Cu 6.07%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
+          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$666k</t>
+          <t>$750k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>2007</v>
+        <v>1988</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Parallax Development Corp.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U13" t="n">
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>58.73611</v>
+        <v>49.29972</v>
       </c>
       <c r="W13" t="n">
-        <v>-133.27</v>
+        <v>-126.09722</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
         </is>
       </c>
     </row>
@@ -1714,21 +1714,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>36</v>
+        <v>20.1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1758,28 +1758,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1793,14 +1793,14 @@
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>58.185</v>
+        <v>57.94639</v>
       </c>
       <c r="W14" t="n">
-        <v>-125.30611</v>
+        <v>-131.66722</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>39.3</v>
+        <v>36</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1854,28 +1854,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
         <v>2022</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1889,14 +1889,14 @@
         <v>65</v>
       </c>
       <c r="V15" t="n">
-        <v>58.15222</v>
+        <v>58.185</v>
       </c>
       <c r="W15" t="n">
-        <v>-125.27778</v>
+        <v>-125.30611</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1906,21 +1906,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6.1</v>
+        <v>39.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1945,33 +1945,33 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P16" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1982,17 +1982,17 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V16" t="n">
-        <v>50.37417</v>
+        <v>58.15222</v>
       </c>
       <c r="W16" t="n">
-        <v>-116.36167</v>
+        <v>-125.27778</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -2002,21 +2002,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HAIDA GOLD</t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>103C  002</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sewell Inlet</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11.4</v>
+        <v>21</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2041,54 +2041,54 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>544 t</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 8.7g/t</t>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$74k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O17" t="n">
         <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>1999</v>
+        <v>2007</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
         <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>52.85806</v>
+        <v>58.73639</v>
       </c>
       <c r="W17" t="n">
-        <v>-132.15722</v>
+        <v>-133.24944</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -2098,30 +2098,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2142,49 +2142,49 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>1986</v>
+        <v>2023</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
         <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>49.30889</v>
+        <v>50.37417</v>
       </c>
       <c r="W18" t="n">
-        <v>-120.00417</v>
+        <v>-116.36167</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -2194,35 +2194,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>37.4</v>
+        <v>5.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2233,29 +2233,33 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Cu 9.10%</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P19" t="n">
-        <v>1966</v>
+        <v>2019</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
@@ -2266,17 +2270,17 @@
         <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V19" t="n">
-        <v>58.88222</v>
+        <v>50.16611</v>
       </c>
       <c r="W19" t="n">
-        <v>-132.1175</v>
+        <v>-125.39944</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -2286,30 +2290,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOHN BULL                     </t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>092F  146</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>toxʷnač</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3.3</v>
+        <v>7.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Lead, Gold, Molybdenum</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2330,49 +2334,49 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Ag 150.83g/t, Au 23.99g/t, Cu 0.8%, Pb 2%, Zn 52%</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>The best assays from several samples were 52 per cent zinc, 150.83 grams per tonne silver, 0.8 per cent copper, 2.0 per cent lead and 23.99 grams per tonne gold (Minister of Mines Annual Report 1926, page A312).</t>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>$47k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>2023</v>
+        <v>1986</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Aquarius Resources Limited, Geiger, K. Warren</t>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T20" t="n">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="U20" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="V20" t="n">
-        <v>49.94611</v>
+        <v>49.30889</v>
       </c>
       <c r="W20" t="n">
-        <v>-124.71056</v>
+        <v>-120.00417</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -2382,35 +2386,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>092B  056</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.9</v>
+        <v>37.4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I21" t="b">
@@ -2421,44 +2425,50 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>$2k</t>
+        </is>
+      </c>
       <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T21" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U21" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="V21" t="n">
-        <v>48.61472</v>
+        <v>58.88222</v>
       </c>
       <c r="W21" t="n">
-        <v>-123.59222</v>
+        <v>-132.1175</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2468,30 +2478,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
+          <t>KATANGA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>092B  060</t>
+          <t>092GNE009</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Williams Landing</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3.6</v>
+        <v>9.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2507,25 +2517,35 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+          <t>Au 62.0g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>$4k</t>
+        </is>
+      </c>
       <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Black Swan Gold Mines Ltd.</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
         <v>13</v>
@@ -2534,17 +2554,17 @@
         <v>325</v>
       </c>
       <c r="U22" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V22" t="n">
-        <v>48.6075</v>
+        <v>49.51111</v>
       </c>
       <c r="W22" t="n">
-        <v>-123.57111</v>
+        <v>-122.57306</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
         </is>
       </c>
     </row>
@@ -2554,30 +2574,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FISH CREEK</t>
+          <t>KING GEORGE (L.159)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>103O  005</t>
+          <t>092B  011</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>East Sooke</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2593,17 +2613,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>13 t</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2614,23 +2634,23 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T23" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U23" t="n">
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>55.99139</v>
+        <v>48.36806</v>
       </c>
       <c r="W23" t="n">
-        <v>-130.03694</v>
+        <v>-123.69528</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
         </is>
       </c>
     </row>
@@ -2640,30 +2660,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROANAN                        </t>
+          <t xml:space="preserve">CORMORANT                     </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>104B  164</t>
+          <t>092K  098</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Premier</t>
+          <t>Granite Bay</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2684,12 +2704,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2700,23 +2720,23 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T24" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U24" t="n">
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>56.00194</v>
+        <v>50.18694</v>
       </c>
       <c r="W24" t="n">
-        <v>-130.04972</v>
+        <v>-125.28056</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
         </is>
       </c>
     </row>
@@ -2726,21 +2746,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SIXMILE</t>
+          <t xml:space="preserve">SILVER BELL                   </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>103O  002</t>
+          <t>093M  076</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Kispiox</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7.1</v>
+        <v>1.6</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2749,7 +2769,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Gold, Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2765,17 +2785,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2795,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>55.98833</v>
+        <v>55.33556</v>
       </c>
       <c r="W25" t="n">
-        <v>-130.06194</v>
+        <v>-127.69194</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
         </is>
       </c>
     </row>
@@ -2812,30 +2832,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORMORANT                     </t>
+          <t xml:space="preserve">ROANAN                        </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>092K  098</t>
+          <t>104B  164</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Granite Bay</t>
+          <t>Premier</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2856,12 +2876,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -2872,109 +2892,23 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T26" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U26" t="n">
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>50.18694</v>
+        <v>56.00194</v>
       </c>
       <c r="W26" t="n">
-        <v>-125.28056</v>
+        <v>-130.04972</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>093M  076</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Kispiox</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Zinc, Lead</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I27" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="n">
-        <v>13</v>
-      </c>
-      <c r="T27" t="n">
-        <v>325</v>
-      </c>
-      <c r="U27" t="n">
-        <v>55</v>
-      </c>
-      <c r="V27" t="n">
-        <v>55.33556</v>
-      </c>
-      <c r="W27" t="n">
-        <v>-127.69194</v>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:X25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1050,30 +1050,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t xml:space="preserve">EDYE PASS                     </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>103J  015</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Hunts Inlet</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2.2</v>
+        <v>10.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1089,46 +1089,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+          <t>226 kt</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Au 29.0g/t, Ag 10.0g/t</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Assays of a 1-metre wide vein yielded 29 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1935). The highest rock sample sample #780401 with 45g/t Au gold over a 45 centimetre width was located 60 m west of the drill pad where earlier exploration was conducted on the Cedar Vein system 200 m east of the historic Dawson workings in the area of the lineament of the Edye Shear zone.</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$1.8M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P7" t="n">
-        <v>1986</v>
+        <v>2022</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>Porcher Island Gold Corporation, Cathedral Gold Corp., Tombill Mines</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V7" t="n">
-        <v>49.7075</v>
+        <v>54.0275</v>
       </c>
       <c r="W7" t="n">
-        <v>-116.00528</v>
+        <v>-130.585</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103J++015</t>
         </is>
       </c>
     </row>
@@ -1138,35 +1146,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10.8</v>
+        <v>2.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1177,33 +1185,25 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P8" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1214,17 +1214,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="V8" t="n">
-        <v>50.53139</v>
+        <v>49.7075</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.2025</v>
+        <v>-116.00528</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1234,35 +1234,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6.8</v>
+        <v>10.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1273,33 +1273,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2018</v>
+        <v>1987</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1313,14 +1313,14 @@
         <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>49.73278</v>
+        <v>50.53139</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.21139</v>
+        <v>-125.2025</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1330,35 +1330,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,54 +1369,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>54.94444</v>
+        <v>49.73278</v>
       </c>
       <c r="W10" t="n">
-        <v>-126.15722</v>
+        <v>-125.21139</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1426,35 +1426,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MAGNET</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092L  097</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nimpkish</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Magnetite, Iron, Copper</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 15.40%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$780k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2025</v>
+        <v>2012</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="U11" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>50.40806</v>
+        <v>54.94444</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.96167</v>
+        <v>-126.15722</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1522,30 +1522,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MAIN</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>092E  088</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.8</v>
+        <v>36</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Zinc</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1566,49 +1566,49 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$766k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>1988</v>
+        <v>2022</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
         <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>49.29694</v>
+        <v>58.185</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.08111</v>
+        <v>-125.30611</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1618,21 +1618,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORMOND 3 (L.353)</t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092E  012</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.8</v>
+        <v>39.3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,49 +1662,49 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ag 127g/t, Cu 6.07%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$750k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>1988</v>
+        <v>2022</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Parallax Development Corp.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>49.29972</v>
+        <v>58.15222</v>
       </c>
       <c r="W13" t="n">
-        <v>-126.09722</v>
+        <v>-125.27778</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -1714,35 +1714,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>PRIDE OF EMORY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>092HSW004</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Dogwood Valley</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>20.1</v>
+        <v>6.9</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1753,54 +1753,54 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>4.3 Mt</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$234k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U14" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V14" t="n">
-        <v>57.94639</v>
+        <v>49.47472</v>
       </c>
       <c r="W14" t="n">
-        <v>-131.66722</v>
+        <v>-121.51417</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
         </is>
       </c>
     </row>
@@ -1810,30 +1810,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1854,28 +1854,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>2022</v>
+        <v>2007</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1886,17 +1886,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V15" t="n">
-        <v>58.185</v>
+        <v>58.73639</v>
       </c>
       <c r="W15" t="n">
-        <v>-125.30611</v>
+        <v>-133.24944</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -1906,21 +1906,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>39.3</v>
+        <v>6.1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1945,33 +1945,33 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1982,17 +1982,17 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V16" t="n">
-        <v>58.15222</v>
+        <v>50.37417</v>
       </c>
       <c r="W16" t="n">
-        <v>-125.27778</v>
+        <v>-116.36167</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -2002,30 +2002,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RED CAP - EAST CIRQUE</t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>104K  141</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>21</v>
+        <v>5.6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2046,28 +2046,28 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 3.7g/t, Ag 26.0g/t</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$208k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>2007</v>
+        <v>2019</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -2081,14 +2081,14 @@
         <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>58.73639</v>
+        <v>50.16611</v>
       </c>
       <c r="W17" t="n">
-        <v>-133.24944</v>
+        <v>-125.39944</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -2098,30 +2098,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6.1</v>
+        <v>11.4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2137,54 +2137,54 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$74k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>2023</v>
+        <v>1999</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T18" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U18" t="n">
         <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>50.37417</v>
+        <v>52.85806</v>
       </c>
       <c r="W18" t="n">
-        <v>-116.36167</v>
+        <v>-132.15722</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -2194,30 +2194,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5.6</v>
+        <v>7.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2233,54 +2233,54 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
-        <v>2019</v>
+        <v>1986</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T19" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U19" t="n">
         <v>61</v>
       </c>
       <c r="V19" t="n">
-        <v>50.16611</v>
+        <v>49.30889</v>
       </c>
       <c r="W19" t="n">
-        <v>-125.39944</v>
+        <v>-120.00417</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -2290,35 +2290,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>7.5</v>
+        <v>37.4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2329,54 +2329,50 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>1986</v>
+        <v>1966</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U20" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V20" t="n">
-        <v>49.30889</v>
+        <v>58.88222</v>
       </c>
       <c r="W20" t="n">
-        <v>-120.00417</v>
+        <v>-132.1175</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2386,35 +2382,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">ROANAN                        </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>104B  164</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Premier</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>37.4</v>
+        <v>5.7</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I21" t="b">
@@ -2425,31 +2421,25 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>$2k</t>
-        </is>
-      </c>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1966</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
         <v>13</v>
@@ -2458,17 +2448,17 @@
         <v>325</v>
       </c>
       <c r="U21" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>58.88222</v>
+        <v>56.00194</v>
       </c>
       <c r="W21" t="n">
-        <v>-132.1175</v>
+        <v>-130.04972</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>
       </c>
     </row>
@@ -2478,21 +2468,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KATANGA</t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>092GNE009</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Williams Landing</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>9.5</v>
+        <v>6.6</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2501,7 +2491,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2522,30 +2512,20 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 62.0g/t</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>$4k</t>
-        </is>
-      </c>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>2</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Black Swan Gold Mines Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
         <v>13</v>
@@ -2554,17 +2534,17 @@
         <v>325</v>
       </c>
       <c r="U22" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>49.51111</v>
+        <v>55.99139</v>
       </c>
       <c r="W22" t="n">
-        <v>-122.57306</v>
+        <v>-130.03694</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
         </is>
       </c>
     </row>
@@ -2574,30 +2554,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KING GEORGE (L.159)</t>
+          <t>SIXMILE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>092B  011</t>
+          <t>103O  002</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>East Sooke</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.8</v>
+        <v>7.1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2613,17 +2593,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>13 t</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2634,23 +2614,23 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U23" t="n">
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>48.36806</v>
+        <v>55.98833</v>
       </c>
       <c r="W23" t="n">
-        <v>-123.69528</v>
+        <v>-130.06194</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
         </is>
       </c>
     </row>
@@ -2660,30 +2640,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORMORANT                     </t>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>092K  098</t>
+          <t>092B  060</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Granite Bay</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2704,12 +2684,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2720,23 +2700,23 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T24" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U24" t="n">
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>50.18694</v>
+        <v>48.6075</v>
       </c>
       <c r="W24" t="n">
-        <v>-125.28056</v>
+        <v>-123.57111</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
         </is>
       </c>
     </row>
@@ -2746,30 +2726,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>093M  076</t>
+          <t>092B  056</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Kispiox</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead</t>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2790,12 +2770,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2806,109 +2786,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T25" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U25" t="n">
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>55.33556</v>
+        <v>48.61472</v>
       </c>
       <c r="W25" t="n">
-        <v>-127.69194</v>
+        <v>-123.59222</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ROANAN                        </t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>104B  164</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Premier</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="n">
-        <v>13</v>
-      </c>
-      <c r="T26" t="n">
-        <v>325</v>
-      </c>
-      <c r="U26" t="n">
-        <v>55</v>
-      </c>
-      <c r="V26" t="n">
-        <v>56.00194</v>
-      </c>
-      <c r="W26" t="n">
-        <v>-130.04972</v>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -954,35 +954,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MAPLE LEAF</t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>092F  039</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kakawis</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>16.7</v>
+        <v>2.2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -993,54 +993,46 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3 t</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Au 15.1g/t</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>$307k</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P6" t="n">
-        <v>2023</v>
+        <v>1986</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="V6" t="n">
-        <v>49.27111</v>
+        <v>49.7075</v>
       </c>
       <c r="W6" t="n">
-        <v>-125.73167</v>
+        <v>-116.00528</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1050,35 +1042,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDYE PASS                     </t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>103J  015</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hunts Inlet</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,54 +1081,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>226 kt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 29.0g/t, Ag 10.0g/t</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Assays of a 1-metre wide vein yielded 29 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1935). The highest rock sample sample #780401 with 45g/t Au gold over a 45 centimetre width was located 60 m west of the drill pad where earlier exploration was conducted on the Cedar Vein system 200 m east of the historic Dawson workings in the area of the lineament of the Edye Shear zone.</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$1.8M</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>2022</v>
+        <v>1987</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Porcher Island Gold Corporation, Cathedral Gold Corp., Tombill Mines</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="V7" t="n">
-        <v>54.0275</v>
+        <v>50.53139</v>
       </c>
       <c r="W7" t="n">
-        <v>-130.585</v>
+        <v>-125.2025</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103J++015</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1146,35 +1138,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.2</v>
+        <v>6.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,25 +1177,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+          <t>1.0 Mt</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>1986</v>
+        <v>2018</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1214,17 +1214,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V8" t="n">
-        <v>49.7075</v>
+        <v>49.73278</v>
       </c>
       <c r="W8" t="n">
-        <v>-116.00528</v>
+        <v>-125.21139</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1234,21 +1234,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10.8</v>
+        <v>7.4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1273,54 +1273,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>1987</v>
+        <v>2012</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U9" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V9" t="n">
-        <v>50.53139</v>
+        <v>54.94444</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.2025</v>
+        <v>-126.15722</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1330,35 +1330,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>MAGNET</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>092L  097</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Nimpkish</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Magnetite, Iron, Copper</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,54 +1369,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Cu 15.40%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$780k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="P10" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U10" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="V10" t="n">
-        <v>49.73278</v>
+        <v>50.40806</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.21139</v>
+        <v>-126.96167</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
         </is>
       </c>
     </row>
@@ -1426,21 +1426,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>ORMOND 3 (L.353)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092E  012</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.4</v>
+        <v>2.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Ag 127g/t, Cu 6.07%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$750k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>2012</v>
+        <v>1988</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Parallax Development Corp.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T11" t="n">
-        <v>275</v>
+        <v>125</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>54.94444</v>
+        <v>49.29972</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.15722</v>
+        <v>-126.09722</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
         </is>
       </c>
     </row>
@@ -1522,21 +1522,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>36</v>
+        <v>20.1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1566,28 +1566,28 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
@@ -1601,14 +1601,14 @@
         <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>58.185</v>
+        <v>57.94639</v>
       </c>
       <c r="W12" t="n">
-        <v>-125.30611</v>
+        <v>-131.66722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>39.3</v>
+        <v>36</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,28 +1662,28 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P13" t="n">
         <v>2022</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -1697,14 +1697,14 @@
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>58.15222</v>
+        <v>58.185</v>
       </c>
       <c r="W13" t="n">
-        <v>-125.27778</v>
+        <v>-125.30611</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1714,35 +1714,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PRIDE OF EMORY</t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>092HSW004</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Dogwood Valley</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.9</v>
+        <v>39.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Gold, Silver, Chromium, Platinum, Palladium</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1753,54 +1753,54 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4.3 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 0.7g/t, Pt 2.8g/t, Pd 4.9g/t</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>In 1987, 63 samples were collected and all were anomalous in chromium with assays up to 1.28 per cent. One high-grade sample from the bottom of the "1500" orebody assayed 2.85 grams per tonne platinum and 4.94 grams per tonne palladium. The best gold assay from the rock samples was 0.93 gram per tonne gold. In 1936, one 22.7 tonne bulk sample taken from the 488 metre (1600 feet) crosscut averaged 2.74 grams per tonne platinum and palladium and 0.68 gram per tonne gold.</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$234k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>International Corona Corp., International Millennium Mining Corp., Mascot Gold Mines Ltd.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>49.47472</v>
+        <v>58.15222</v>
       </c>
       <c r="W14" t="n">
-        <v>-121.51417</v>
+        <v>-125.27778</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSW004</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -1810,30 +1810,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RED CAP - EAST CIRQUE</t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>104K  141</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>21</v>
+        <v>5.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1854,28 +1854,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 3.7g/t, Ag 26.0g/t</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$208k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>2007</v>
+        <v>2019</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1889,14 +1889,14 @@
         <v>61</v>
       </c>
       <c r="V15" t="n">
-        <v>58.73639</v>
+        <v>50.16611</v>
       </c>
       <c r="W15" t="n">
-        <v>-133.24944</v>
+        <v>-125.39944</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -1906,30 +1906,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6.1</v>
+        <v>11.4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1945,54 +1945,54 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$74k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>2023</v>
+        <v>1999</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U16" t="n">
         <v>61</v>
       </c>
       <c r="V16" t="n">
-        <v>50.37417</v>
+        <v>52.85806</v>
       </c>
       <c r="W16" t="n">
-        <v>-116.36167</v>
+        <v>-132.15722</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -2002,30 +2002,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5.6</v>
+        <v>7.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2041,54 +2041,54 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>2019</v>
+        <v>1986</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U17" t="n">
         <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>50.16611</v>
+        <v>49.30889</v>
       </c>
       <c r="W17" t="n">
-        <v>-125.39944</v>
+        <v>-120.00417</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -2098,35 +2098,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HAIDA GOLD</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>103C  002</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sewell Inlet</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.4</v>
+        <v>37.4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -2137,54 +2137,50 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>544 t</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Au 8.7g/t</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$74k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>1999</v>
+        <v>1966</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V18" t="n">
-        <v>52.85806</v>
+        <v>58.88222</v>
       </c>
       <c r="W18" t="n">
-        <v>-132.15722</v>
+        <v>-132.1175</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2194,21 +2190,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t>AVON</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>092F  350</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Chetarpe</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>7.5</v>
+        <v>24.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2217,7 +2213,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Gold, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2233,54 +2229,54 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Au 47.3g/t, Ag 53.1g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$33k</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>225</v>
+        <v>25</v>
       </c>
       <c r="U19" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="V19" t="n">
-        <v>49.30889</v>
+        <v>49.40417</v>
       </c>
       <c r="W19" t="n">
-        <v>-120.00417</v>
+        <v>-125.75833</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
         </is>
       </c>
     </row>
@@ -2290,35 +2286,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>KATANGA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>092GNE009</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Williams Landing</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>37.4</v>
+        <v>9.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2329,29 +2325,33 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Au 62.0g/t</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$4k</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>1966</v>
+        <v>1985</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Black Swan Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
@@ -2362,17 +2362,17 @@
         <v>325</v>
       </c>
       <c r="U20" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="V20" t="n">
-        <v>58.88222</v>
+        <v>49.51111</v>
       </c>
       <c r="W20" t="n">
-        <v>-132.1175</v>
+        <v>-122.57306</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
         </is>
       </c>
     </row>
@@ -2468,30 +2468,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FISH CREEK</t>
+          <t>KING GEORGE (L.159)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>103O  005</t>
+          <t>092B  011</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>East Sooke</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2507,17 +2507,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>13 t</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2528,23 +2528,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T22" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U22" t="n">
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>55.99139</v>
+        <v>48.36806</v>
       </c>
       <c r="W22" t="n">
-        <v>-130.03694</v>
+        <v>-123.69528</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SIXMILE</t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>103O  002</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2623,14 +2623,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>55.98833</v>
+        <v>55.99139</v>
       </c>
       <c r="W23" t="n">
-        <v>-130.06194</v>
+        <v>-130.03694</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
         </is>
       </c>
     </row>
@@ -2640,30 +2640,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
+          <t>SIXMILE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>092B  060</t>
+          <t>103O  002</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.6</v>
+        <v>7.1</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2679,17 +2679,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2709,14 +2709,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>48.6075</v>
+        <v>55.98833</v>
       </c>
       <c r="W24" t="n">
-        <v>-123.57111</v>
+        <v>-130.06194</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
         </is>
       </c>
     </row>
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>092B  056</t>
+          <t>092B  060</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2786,21 +2786,107 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T25" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U25" t="n">
         <v>55</v>
       </c>
       <c r="V25" t="n">
+        <v>48.6075</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-123.57111</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>092B  056</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Cliffside</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>13</v>
+      </c>
+      <c r="T26" t="n">
+        <v>325</v>
+      </c>
+      <c r="U26" t="n">
+        <v>55</v>
+      </c>
+      <c r="V26" t="n">
         <v>48.61472</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W26" t="n">
         <v>-123.59222</v>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
         </is>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:X22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -954,35 +954,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t>WINCO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>104I  019</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Boulder City</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2.2</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Silver, Copper, Lead, Gold, Zinc</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -993,25 +993,33 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Ag 487g/t, Cu 9.85%</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>chip sample results include maximum values over 1 metre of 9.85 per cent copper and 486.86 grams per tonne silver;</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$3.2M</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P6" t="n">
-        <v>1986</v>
+        <v>2025</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>Quartz Mountain Resources Ltd., Wyn Development Inc., Horseshoe Gold Mining Inc.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
@@ -1022,17 +1030,17 @@
         <v>325</v>
       </c>
       <c r="U6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V6" t="n">
-        <v>49.7075</v>
+        <v>58.78</v>
       </c>
       <c r="W6" t="n">
-        <v>-116.00528</v>
+        <v>-128.12222</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++019</t>
         </is>
       </c>
     </row>
@@ -1042,30 +1050,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>104I  098</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>McDame</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10.8</v>
+        <v>31.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1081,33 +1089,33 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>1987</v>
+        <v>2022</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1118,17 +1126,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V7" t="n">
-        <v>50.53139</v>
+        <v>58.90944</v>
       </c>
       <c r="W7" t="n">
-        <v>-125.2025</v>
+        <v>-129.09278</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
         </is>
       </c>
     </row>
@@ -1138,35 +1146,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6.8</v>
+        <v>2.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1177,33 +1185,25 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P8" t="n">
-        <v>2018</v>
+        <v>1986</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1214,17 +1214,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="V8" t="n">
-        <v>49.73278</v>
+        <v>49.7075</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.21139</v>
+        <v>-116.00528</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1234,21 +1234,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.4</v>
+        <v>10.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1273,54 +1273,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2012</v>
+        <v>1987</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>54.94444</v>
+        <v>50.53139</v>
       </c>
       <c r="W9" t="n">
-        <v>-126.15722</v>
+        <v>-125.2025</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1330,35 +1330,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MAGNET</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092L  097</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nimpkish</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Magnetite, Iron, Copper</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,54 +1369,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 15.40%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$780k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>50.40806</v>
+        <v>49.73278</v>
       </c>
       <c r="W10" t="n">
-        <v>-126.96167</v>
+        <v>-125.21139</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1426,21 +1426,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ORMOND 3 (L.353)</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092E  012</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2.8</v>
+        <v>7.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Ag 127g/t, Cu 6.07%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$750k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>1988</v>
+        <v>2012</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Parallax Development Corp.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>125</v>
+        <v>275</v>
       </c>
       <c r="U11" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>49.29972</v>
+        <v>54.94444</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.09722</v>
+        <v>-126.15722</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1522,21 +1522,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>ORMOND 3 (L.353)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>092E  012</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20.1</v>
+        <v>2.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1566,49 +1566,49 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Ag 127g/t, Cu 6.07%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$750k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2019</v>
+        <v>1988</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>Parallax Development Corp.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U12" t="n">
         <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>57.94639</v>
+        <v>49.29972</v>
       </c>
       <c r="W12" t="n">
-        <v>-131.66722</v>
+        <v>-126.09722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
         </is>
       </c>
     </row>
@@ -1618,21 +1618,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>36</v>
+        <v>20.1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1662,28 +1662,28 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -1697,14 +1697,14 @@
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>58.185</v>
+        <v>57.94639</v>
       </c>
       <c r="W13" t="n">
-        <v>-125.30611</v>
+        <v>-131.66722</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>39.3</v>
+        <v>36</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1758,28 +1758,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P14" t="n">
         <v>2022</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1793,14 +1793,14 @@
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>58.15222</v>
+        <v>58.185</v>
       </c>
       <c r="W14" t="n">
-        <v>-125.27778</v>
+        <v>-125.30611</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1810,21 +1810,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5.6</v>
+        <v>39.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1854,28 +1854,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1886,17 +1886,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V15" t="n">
-        <v>50.16611</v>
+        <v>58.15222</v>
       </c>
       <c r="W15" t="n">
-        <v>-125.39944</v>
+        <v>-125.27778</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -1906,30 +1906,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HAIDA GOLD</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>103C  002</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sewell Inlet</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>11.4</v>
+        <v>6.1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1945,54 +1945,54 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>544 t</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 8.7g/t</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$74k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>1999</v>
+        <v>2023</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
         <v>61</v>
       </c>
       <c r="V16" t="n">
-        <v>52.85806</v>
+        <v>50.37417</v>
       </c>
       <c r="W16" t="n">
-        <v>-132.15722</v>
+        <v>-116.36167</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -2002,21 +2002,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7.5</v>
+        <v>11.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2041,54 +2041,54 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$74k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>1986</v>
+        <v>1999</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U17" t="n">
         <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>49.30889</v>
+        <v>52.85806</v>
       </c>
       <c r="W17" t="n">
-        <v>-120.00417</v>
+        <v>-132.15722</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -2190,30 +2190,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AVON</t>
+          <t xml:space="preserve">CORMORANT                     </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>092F  350</t>
+          <t>092K  098</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Chetarpe</t>
+          <t>Granite Bay</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>24.6</v>
+        <v>5.3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2229,54 +2229,44 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 47.3g/t, Ag 53.1g/t</t>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>$33k</t>
-        </is>
-      </c>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>4</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T19" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="U19" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>49.40417</v>
+        <v>50.18694</v>
       </c>
       <c r="W19" t="n">
-        <v>-125.75833</v>
+        <v>-125.28056</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
         </is>
       </c>
     </row>
@@ -2286,21 +2276,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KATANGA</t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>092GNE009</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Williams Landing</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9.5</v>
+        <v>6.6</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2309,7 +2299,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2330,30 +2320,20 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 62.0g/t</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>$4k</t>
-        </is>
-      </c>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>2</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Black Swan Gold Mines Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
         <v>13</v>
@@ -2362,17 +2342,17 @@
         <v>325</v>
       </c>
       <c r="U20" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>49.51111</v>
+        <v>55.99139</v>
       </c>
       <c r="W20" t="n">
-        <v>-122.57306</v>
+        <v>-130.03694</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
         </is>
       </c>
     </row>
@@ -2382,21 +2362,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROANAN                        </t>
+          <t xml:space="preserve">SILVER BELL                   </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>104B  164</t>
+          <t>093M  076</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Premier</t>
+          <t>Kispiox</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2405,7 +2385,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Gold, Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2426,12 +2406,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2451,14 +2431,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>56.00194</v>
+        <v>55.33556</v>
       </c>
       <c r="W21" t="n">
-        <v>-130.04972</v>
+        <v>-127.69194</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
         </is>
       </c>
     </row>
@@ -2468,30 +2448,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KING GEORGE (L.159)</t>
+          <t xml:space="preserve">ROANAN                        </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>092B  011</t>
+          <t>104B  164</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>East Sooke</t>
+          <t>Premier</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.8</v>
+        <v>5.7</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2507,17 +2487,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>13 t</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2528,367 +2508,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T22" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U22" t="n">
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>48.36806</v>
+        <v>56.00194</v>
       </c>
       <c r="W22" t="n">
-        <v>-123.69528</v>
+        <v>-130.04972</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>FISH CREEK</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>103O  005</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>13</v>
-      </c>
-      <c r="T23" t="n">
-        <v>325</v>
-      </c>
-      <c r="U23" t="n">
-        <v>55</v>
-      </c>
-      <c r="V23" t="n">
-        <v>55.99139</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-130.03694</v>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>SIXMILE</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>103O  002</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>13</v>
-      </c>
-      <c r="T24" t="n">
-        <v>325</v>
-      </c>
-      <c r="U24" t="n">
-        <v>55</v>
-      </c>
-      <c r="V24" t="n">
-        <v>55.98833</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-130.06194</v>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>092B  060</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Cliffside</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>13</v>
-      </c>
-      <c r="T25" t="n">
-        <v>325</v>
-      </c>
-      <c r="U25" t="n">
-        <v>55</v>
-      </c>
-      <c r="V25" t="n">
-        <v>48.6075</v>
-      </c>
-      <c r="W25" t="n">
-        <v>-123.57111</v>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>092B  056</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Cliffside</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="n">
-        <v>13</v>
-      </c>
-      <c r="T26" t="n">
-        <v>325</v>
-      </c>
-      <c r="U26" t="n">
-        <v>55</v>
-      </c>
-      <c r="V26" t="n">
-        <v>48.61472</v>
-      </c>
-      <c r="W26" t="n">
-        <v>-123.59222</v>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:X28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -954,35 +954,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WINCO</t>
+          <t>MAPLE LEAF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>104I  019</t>
+          <t>092F  039</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Boulder City</t>
+          <t>Kakawis</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>66.40000000000001</v>
+        <v>16.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Gold, Zinc</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -993,54 +993,54 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>3 t</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Ag 487g/t, Cu 9.85%</t>
+          <t>Au 15.1g/t</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>chip sample results include maximum values over 1 metre of 9.85 per cent copper and 486.86 grams per tonne silver;</t>
+          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>$3.2M</t>
+          <t>$307k</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Quartz Mountain Resources Ltd., Wyn Development Inc., Horseshoe Gold Mining Inc.</t>
+          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="V6" t="n">
-        <v>58.78</v>
+        <v>49.27111</v>
       </c>
       <c r="W6" t="n">
-        <v>-128.12222</v>
+        <v>-125.73167</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++019</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
         </is>
       </c>
     </row>
@@ -1050,30 +1050,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t>WINCO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>104I  019</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>Boulder City</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>31.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Silver, Copper, Lead, Gold, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1094,28 +1094,28 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
+          <t>Ag 487g/t, Cu 9.85%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
+          <t>chip sample results include maximum values over 1 metre of 9.85 per cent copper and 486.86 grams per tonne silver;</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$3.2M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P7" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>Quartz Mountain Resources Ltd., Wyn Development Inc., Horseshoe Gold Mining Inc.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1129,14 +1129,14 @@
         <v>70</v>
       </c>
       <c r="V7" t="n">
-        <v>58.90944</v>
+        <v>58.78</v>
       </c>
       <c r="W7" t="n">
-        <v>-129.09278</v>
+        <v>-128.12222</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++019</t>
         </is>
       </c>
     </row>
@@ -1146,21 +1146,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>104I  098</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>McDame</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.2</v>
+        <v>31.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,25 +1185,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>1986</v>
+        <v>2022</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1214,17 +1222,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V8" t="n">
-        <v>49.7075</v>
+        <v>58.90944</v>
       </c>
       <c r="W8" t="n">
-        <v>-116.00528</v>
+        <v>-129.09278</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
         </is>
       </c>
     </row>
@@ -1234,35 +1242,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10.8</v>
+        <v>2.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1273,33 +1281,25 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P9" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1310,17 +1310,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="V9" t="n">
-        <v>50.53139</v>
+        <v>49.7075</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.2025</v>
+        <v>-116.00528</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1330,35 +1330,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.8</v>
+        <v>10.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,33 +1369,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>2018</v>
+        <v>1987</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1409,14 +1409,14 @@
         <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>49.73278</v>
+        <v>50.53139</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.21139</v>
+        <v>-125.2025</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1426,35 +1426,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V11" t="n">
-        <v>54.94444</v>
+        <v>49.73278</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.15722</v>
+        <v>-125.21139</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1522,21 +1522,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ORMOND 3 (L.353)</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>092E  012</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.8</v>
+        <v>7.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1561,54 +1561,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ag 127g/t, Cu 6.07%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$750k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>1988</v>
+        <v>2012</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Parallax Development Corp.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T12" t="n">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="U12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V12" t="n">
-        <v>49.29972</v>
+        <v>54.94444</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.09722</v>
+        <v>-126.15722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1618,30 +1618,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>MAGNET</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>092L  097</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Nimpkish</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>20.1</v>
+        <v>8.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Magnetite, Iron, Copper</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,49 +1662,49 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Cu 15.40%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$780k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="P13" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U13" t="n">
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>57.94639</v>
+        <v>50.40806</v>
       </c>
       <c r="W13" t="n">
-        <v>-131.66722</v>
+        <v>-126.96167</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
         </is>
       </c>
     </row>
@@ -1714,30 +1714,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>RED CAP - SLOPE ZONE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>104K  010</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1758,28 +1758,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$666k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P14" t="n">
-        <v>2022</v>
+        <v>2007</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1793,14 +1793,14 @@
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>58.185</v>
+        <v>58.73611</v>
       </c>
       <c r="W14" t="n">
-        <v>-125.30611</v>
+        <v>-133.27</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>39.3</v>
+        <v>36</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1854,28 +1854,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
         <v>2022</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1889,14 +1889,14 @@
         <v>65</v>
       </c>
       <c r="V15" t="n">
-        <v>58.15222</v>
+        <v>58.185</v>
       </c>
       <c r="W15" t="n">
-        <v>-125.27778</v>
+        <v>-125.30611</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1906,21 +1906,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6.1</v>
+        <v>39.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1945,33 +1945,33 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P16" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1982,17 +1982,17 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V16" t="n">
-        <v>50.37417</v>
+        <v>58.15222</v>
       </c>
       <c r="W16" t="n">
-        <v>-116.36167</v>
+        <v>-125.27778</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -2002,21 +2002,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HAIDA GOLD</t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>103C  002</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sewell Inlet</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11.4</v>
+        <v>21</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2041,54 +2041,54 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>544 t</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 8.7g/t</t>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$74k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O17" t="n">
         <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>1999</v>
+        <v>2007</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
         <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>52.85806</v>
+        <v>58.73639</v>
       </c>
       <c r="W17" t="n">
-        <v>-132.15722</v>
+        <v>-133.24944</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -2098,35 +2098,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>37.4</v>
+        <v>6.1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -2137,29 +2137,33 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Ag 15g/t, Cu 13.36%</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>1966</v>
+        <v>2023</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
@@ -2170,17 +2174,17 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>58.88222</v>
+        <v>50.37417</v>
       </c>
       <c r="W18" t="n">
-        <v>-132.1175</v>
+        <v>-116.36167</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -2190,21 +2194,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORMORANT                     </t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>092K  098</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Granite Bay</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2213,7 +2217,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2229,44 +2233,54 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>$102k</t>
+        </is>
+      </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2019</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Volatus Capital Corp., Osborne, T.</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T19" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V19" t="n">
-        <v>50.18694</v>
+        <v>50.16611</v>
       </c>
       <c r="W19" t="n">
-        <v>-125.28056</v>
+        <v>-125.39944</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -2276,21 +2290,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FISH CREEK</t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>103O  005</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6.6</v>
+        <v>11.4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2299,7 +2313,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2315,44 +2329,54 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>$74k</t>
+        </is>
+      </c>
       <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1999</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T20" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U20" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V20" t="n">
-        <v>55.99139</v>
+        <v>52.85806</v>
       </c>
       <c r="W20" t="n">
-        <v>-130.03694</v>
+        <v>-132.15722</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -2362,35 +2386,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>093M  076</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kispiox</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.6</v>
+        <v>37.4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I21" t="b">
@@ -2401,25 +2425,31 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>$2k</t>
+        </is>
+      </c>
       <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
         <v>13</v>
@@ -2428,17 +2458,17 @@
         <v>325</v>
       </c>
       <c r="U21" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="V21" t="n">
-        <v>55.33556</v>
+        <v>58.88222</v>
       </c>
       <c r="W21" t="n">
-        <v>-127.69194</v>
+        <v>-132.1175</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2448,21 +2478,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROANAN                        </t>
+          <t>AVON</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>104B  164</t>
+          <t>092F  350</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Premier</t>
+          <t>Chetarpe</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5.7</v>
+        <v>24.6</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2471,7 +2501,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Gold, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2487,44 +2517,580 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+          <t>Au 47.3g/t, Ag 53.1g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>$33k</t>
+        </is>
+      </c>
       <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>25</v>
+      </c>
+      <c r="U22" t="n">
+        <v>57</v>
+      </c>
+      <c r="V22" t="n">
+        <v>49.40417</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-125.75833</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>KATANGA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>092GNE009</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Williams Landing</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Gold, Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Au 62.0g/t</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>$4k</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>2</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Black Swan Gold Mines Ltd.</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
         <v>13</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>325</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U23" t="n">
+        <v>57</v>
+      </c>
+      <c r="V23" t="n">
+        <v>49.51111</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-122.57306</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILVER BELL                   </t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>093M  076</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Kispiox</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Zinc, Lead</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>13</v>
+      </c>
+      <c r="T24" t="n">
+        <v>325</v>
+      </c>
+      <c r="U24" t="n">
         <v>55</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V24" t="n">
+        <v>55.33556</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-127.69194</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>092B  056</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Cliffside</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>13</v>
+      </c>
+      <c r="T25" t="n">
+        <v>325</v>
+      </c>
+      <c r="U25" t="n">
+        <v>55</v>
+      </c>
+      <c r="V25" t="n">
+        <v>48.61472</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-123.59222</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>092B  060</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Cliffside</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>13</v>
+      </c>
+      <c r="T26" t="n">
+        <v>325</v>
+      </c>
+      <c r="U26" t="n">
+        <v>55</v>
+      </c>
+      <c r="V26" t="n">
+        <v>48.6075</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-123.57111</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROANAN                        </t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>104B  164</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Premier</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>13</v>
+      </c>
+      <c r="T27" t="n">
+        <v>325</v>
+      </c>
+      <c r="U27" t="n">
+        <v>55</v>
+      </c>
+      <c r="V27" t="n">
         <v>56.00194</v>
       </c>
-      <c r="W22" t="n">
+      <c r="W27" t="n">
         <v>-130.04972</v>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CORMORANT                     </t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>092K  098</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Granite Bay</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>200</v>
+      </c>
+      <c r="U28" t="n">
+        <v>55</v>
+      </c>
+      <c r="V28" t="n">
+        <v>50.18694</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-125.28056</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X28"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WINCO</t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>104I  019</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Boulder City</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>66.40000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Gold, Zinc</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,33 +1089,25 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Ag 487g/t, Cu 9.85%</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>chip sample results include maximum values over 1 metre of 9.85 per cent copper and 486.86 grams per tonne silver;</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$3.2M</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P7" t="n">
-        <v>2025</v>
+        <v>1986</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Quartz Mountain Resources Ltd., Wyn Development Inc., Horseshoe Gold Mining Inc.</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1126,17 +1118,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V7" t="n">
-        <v>58.78</v>
+        <v>49.7075</v>
       </c>
       <c r="W7" t="n">
-        <v>-128.12222</v>
+        <v>-116.00528</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++019</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1146,30 +1138,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>31.5</v>
+        <v>10.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1185,33 +1177,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>2022</v>
+        <v>1987</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1222,17 +1214,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="V8" t="n">
-        <v>58.90944</v>
+        <v>50.53139</v>
       </c>
       <c r="W8" t="n">
-        <v>-129.09278</v>
+        <v>-125.2025</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1242,35 +1234,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2.2</v>
+        <v>6.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,25 +1273,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+          <t>1.0 Mt</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>1986</v>
+        <v>2018</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1310,17 +1310,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>49.7075</v>
+        <v>49.73278</v>
       </c>
       <c r="W9" t="n">
-        <v>-116.00528</v>
+        <v>-125.21139</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1330,21 +1330,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10.8</v>
+        <v>7.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,54 +1369,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>1987</v>
+        <v>2012</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>50.53139</v>
+        <v>54.94444</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.2025</v>
+        <v>-126.15722</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1426,35 +1426,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.8</v>
+        <v>20.1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P11" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
@@ -1502,17 +1502,17 @@
         <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>49.73278</v>
+        <v>57.94639</v>
       </c>
       <c r="W11" t="n">
-        <v>-125.21139</v>
+        <v>-131.66722</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1522,35 +1522,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1561,54 +1561,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O12" t="n">
         <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="V12" t="n">
-        <v>54.94444</v>
+        <v>58.73639</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.15722</v>
+        <v>-133.24944</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -1618,30 +1618,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MAGNET</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092L  097</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nimpkish</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>8.4</v>
+        <v>6.1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Magnetite, Iron, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1657,54 +1657,54 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Cu 15.40%</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$780k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V13" t="n">
-        <v>50.40806</v>
+        <v>50.37417</v>
       </c>
       <c r="W13" t="n">
-        <v>-126.96167</v>
+        <v>-116.36167</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -1714,30 +1714,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RED CAP - SLOPE ZONE</t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>104K  010</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>5.6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1758,28 +1758,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$666k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>2007</v>
+        <v>2019</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1790,17 +1790,17 @@
         <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V14" t="n">
-        <v>58.73611</v>
+        <v>50.16611</v>
       </c>
       <c r="W14" t="n">
-        <v>-133.27</v>
+        <v>-125.39944</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -1810,30 +1810,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>36</v>
+        <v>7.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1849,54 +1849,54 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>2022</v>
+        <v>1986</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U15" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V15" t="n">
-        <v>58.185</v>
+        <v>49.30889</v>
       </c>
       <c r="W15" t="n">
-        <v>-125.30611</v>
+        <v>-120.00417</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -1906,35 +1906,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>39.3</v>
+        <v>37.4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1945,33 +1945,29 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>2022</v>
+        <v>1966</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1982,17 +1978,17 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="V16" t="n">
-        <v>58.15222</v>
+        <v>58.88222</v>
       </c>
       <c r="W16" t="n">
-        <v>-125.27778</v>
+        <v>-132.1175</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2002,21 +1998,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RED CAP - EAST CIRQUE</t>
+          <t>KATANGA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>104K  141</t>
+          <t>092GNE009</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Williams Landing</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>21</v>
+        <v>9.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2025,7 +2021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2046,28 +2042,28 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 3.7g/t, Ag 26.0g/t</t>
+          <t>Au 62.0g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
+          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$208k</t>
+          <t>$4k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>2007</v>
+        <v>1985</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Black Swan Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -2078,17 +2074,17 @@
         <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="V17" t="n">
-        <v>58.73639</v>
+        <v>49.51111</v>
       </c>
       <c r="W17" t="n">
-        <v>-133.24944</v>
+        <v>-122.57306</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
         </is>
       </c>
     </row>
@@ -2098,30 +2094,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t>SIXMILE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>103O  002</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6.1</v>
+        <v>7.1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2137,35 +2133,25 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>$170k</t>
-        </is>
-      </c>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>3</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2023</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
         <v>13</v>
@@ -2174,17 +2160,17 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>50.37417</v>
+        <v>55.98833</v>
       </c>
       <c r="W18" t="n">
-        <v>-116.36167</v>
+        <v>-130.06194</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
         </is>
       </c>
     </row>
@@ -2194,30 +2180,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2238,30 +2224,20 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>$102k</t>
-        </is>
-      </c>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>5</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2019</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
         <v>13</v>
@@ -2270,827 +2246,17 @@
         <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>50.16611</v>
+        <v>55.99139</v>
       </c>
       <c r="W19" t="n">
-        <v>-125.39944</v>
+        <v>-130.03694</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>HAIDA GOLD</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>103C  002</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Sewell Inlet</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>544 t</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Au 8.7g/t</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>$74k</t>
-        </is>
-      </c>
-      <c r="O20" t="n">
-        <v>4</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1999</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="n">
-        <v>12</v>
-      </c>
-      <c r="T20" t="n">
-        <v>300</v>
-      </c>
-      <c r="U20" t="n">
-        <v>61</v>
-      </c>
-      <c r="V20" t="n">
-        <v>52.85806</v>
-      </c>
-      <c r="W20" t="n">
-        <v>-132.15722</v>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACE                           </t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>104K  025</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Callison Ranch</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Asbestos</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Developed Prospect  </t>
-        </is>
-      </c>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>$2k</t>
-        </is>
-      </c>
-      <c r="O21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1966</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>13</v>
-      </c>
-      <c r="T21" t="n">
-        <v>325</v>
-      </c>
-      <c r="U21" t="n">
-        <v>60</v>
-      </c>
-      <c r="V21" t="n">
-        <v>58.88222</v>
-      </c>
-      <c r="W21" t="n">
-        <v>-132.1175</v>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>AVON</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>092F  350</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Chetarpe</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Copper, Lead</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Au 47.3g/t, Ag 53.1g/t</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>$33k</t>
-        </is>
-      </c>
-      <c r="O22" t="n">
-        <v>4</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>25</v>
-      </c>
-      <c r="U22" t="n">
-        <v>57</v>
-      </c>
-      <c r="V22" t="n">
-        <v>49.40417</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-125.75833</v>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>KATANGA</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>092GNE009</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Williams Landing</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Au 62.0g/t</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>$4k</t>
-        </is>
-      </c>
-      <c r="O23" t="n">
-        <v>2</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Black Swan Gold Mines Ltd.</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>13</v>
-      </c>
-      <c r="T23" t="n">
-        <v>325</v>
-      </c>
-      <c r="U23" t="n">
-        <v>57</v>
-      </c>
-      <c r="V23" t="n">
-        <v>49.51111</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-122.57306</v>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>093M  076</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Kispiox</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Zinc, Lead</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>13</v>
-      </c>
-      <c r="T24" t="n">
-        <v>325</v>
-      </c>
-      <c r="U24" t="n">
-        <v>55</v>
-      </c>
-      <c r="V24" t="n">
-        <v>55.33556</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-127.69194</v>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>092B  056</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Cliffside</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>13</v>
-      </c>
-      <c r="T25" t="n">
-        <v>325</v>
-      </c>
-      <c r="U25" t="n">
-        <v>55</v>
-      </c>
-      <c r="V25" t="n">
-        <v>48.61472</v>
-      </c>
-      <c r="W25" t="n">
-        <v>-123.59222</v>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>092B  060</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Cliffside</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="n">
-        <v>13</v>
-      </c>
-      <c r="T26" t="n">
-        <v>325</v>
-      </c>
-      <c r="U26" t="n">
-        <v>55</v>
-      </c>
-      <c r="V26" t="n">
-        <v>48.6075</v>
-      </c>
-      <c r="W26" t="n">
-        <v>-123.57111</v>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ROANAN                        </t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>104B  164</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Premier</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I27" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="n">
-        <v>13</v>
-      </c>
-      <c r="T27" t="n">
-        <v>325</v>
-      </c>
-      <c r="U27" t="n">
-        <v>55</v>
-      </c>
-      <c r="V27" t="n">
-        <v>56.00194</v>
-      </c>
-      <c r="W27" t="n">
-        <v>-130.04972</v>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CORMORANT                     </t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>092K  098</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Granite Bay</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I28" t="b">
-        <v>1</v>
-      </c>
-      <c r="J28" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="n">
-        <v>8</v>
-      </c>
-      <c r="T28" t="n">
-        <v>200</v>
-      </c>
-      <c r="U28" t="n">
-        <v>55</v>
-      </c>
-      <c r="V28" t="n">
-        <v>50.18694</v>
-      </c>
-      <c r="W28" t="n">
-        <v>-125.28056</v>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -954,35 +954,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MAPLE LEAF</t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>092F  039</t>
+          <t>104I  098</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kakawis</t>
+          <t>McDame</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>16.7</v>
+        <v>31.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -993,54 +993,54 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3 t</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 15.1g/t</t>
+          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
+          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>$307k</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
+          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="V6" t="n">
-        <v>49.27111</v>
+        <v>58.90944</v>
       </c>
       <c r="W6" t="n">
-        <v>-125.73167</v>
+        <v>-129.09278</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
         </is>
       </c>
     </row>
@@ -1426,21 +1426,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>ORMOND 3 (L.353)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>092E  012</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>20.1</v>
+        <v>2.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1470,49 +1470,49 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Ag 127g/t, Cu 6.07%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$750k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>2019</v>
+        <v>1988</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>Parallax Development Corp.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U11" t="n">
         <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>57.94639</v>
+        <v>49.29972</v>
       </c>
       <c r="W11" t="n">
-        <v>-131.66722</v>
+        <v>-126.09722</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
         </is>
       </c>
     </row>
@@ -1522,30 +1522,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RED CAP - EAST CIRQUE</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>104K  141</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>21</v>
+        <v>20.1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1566,28 +1566,28 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 3.7g/t, Ag 26.0g/t</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$208k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>2007</v>
+        <v>2019</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
@@ -1598,17 +1598,17 @@
         <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>58.73639</v>
+        <v>57.94639</v>
       </c>
       <c r="W12" t="n">
-        <v>-133.24944</v>
+        <v>-131.66722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1618,30 +1618,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6.1</v>
+        <v>21</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1657,33 +1657,33 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>2023</v>
+        <v>2007</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -1697,14 +1697,14 @@
         <v>61</v>
       </c>
       <c r="V13" t="n">
-        <v>50.37417</v>
+        <v>58.73639</v>
       </c>
       <c r="W13" t="n">
-        <v>-116.36167</v>
+        <v>-133.24944</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -1714,21 +1714,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1753,33 +1753,33 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1793,14 +1793,14 @@
         <v>61</v>
       </c>
       <c r="V14" t="n">
-        <v>50.16611</v>
+        <v>50.37417</v>
       </c>
       <c r="W14" t="n">
-        <v>-125.39944</v>
+        <v>-116.36167</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -1810,30 +1810,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>7.5</v>
+        <v>5.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1849,54 +1849,54 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>1986</v>
+        <v>2019</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>61</v>
       </c>
       <c r="V15" t="n">
-        <v>49.30889</v>
+        <v>50.16611</v>
       </c>
       <c r="W15" t="n">
-        <v>-120.00417</v>
+        <v>-125.39944</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -1998,30 +1998,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KATANGA</t>
+          <t>KING GEORGE (L.159)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>092GNE009</t>
+          <t>092B  011</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Williams Landing</t>
+          <t>East Sooke</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9.5</v>
+        <v>0.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2037,54 +2037,44 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>13 t</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 62.0g/t</t>
+          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>$4k</t>
-        </is>
-      </c>
+          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>2</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Black Swan Gold Mines Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U17" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>49.51111</v>
+        <v>48.36806</v>
       </c>
       <c r="W17" t="n">
-        <v>-122.57306</v>
+        <v>-123.69528</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
         </is>
       </c>
     </row>
@@ -2094,21 +2084,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SIXMILE</t>
+          <t xml:space="preserve">SILVER BELL                   </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>103O  002</t>
+          <t>093M  076</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Kispiox</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7.1</v>
+        <v>1.6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2117,7 +2107,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Gold, Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2133,17 +2123,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2163,100 +2153,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>55.98833</v>
+        <v>55.33556</v>
       </c>
       <c r="W18" t="n">
-        <v>-130.06194</v>
+        <v>-127.69194</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>FISH CREEK</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>103O  005</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>13</v>
-      </c>
-      <c r="T19" t="n">
-        <v>325</v>
-      </c>
-      <c r="U19" t="n">
-        <v>55</v>
-      </c>
-      <c r="V19" t="n">
-        <v>55.99139</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-130.03694</v>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:X24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -954,21 +954,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>31.5</v>
+        <v>2.2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -977,12 +977,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -993,33 +993,25 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P6" t="n">
-        <v>2022</v>
+        <v>1986</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
@@ -1030,17 +1022,17 @@
         <v>325</v>
       </c>
       <c r="U6" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V6" t="n">
-        <v>58.90944</v>
+        <v>49.7075</v>
       </c>
       <c r="W6" t="n">
-        <v>-129.09278</v>
+        <v>-116.00528</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1050,35 +1042,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2.2</v>
+        <v>10.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,25 +1081,33 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+          <t>118 kt (assay)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1118,17 +1118,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V7" t="n">
-        <v>49.7075</v>
+        <v>50.53139</v>
       </c>
       <c r="W7" t="n">
-        <v>-116.00528</v>
+        <v>-125.2025</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1138,35 +1138,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10.8</v>
+        <v>6.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1177,33 +1177,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>1987</v>
+        <v>2018</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1217,14 +1217,14 @@
         <v>67</v>
       </c>
       <c r="V8" t="n">
-        <v>50.53139</v>
+        <v>49.73278</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.2025</v>
+        <v>-125.21139</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1234,35 +1234,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1273,54 +1273,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U9" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V9" t="n">
-        <v>49.73278</v>
+        <v>54.94444</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.21139</v>
+        <v>-126.15722</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1330,21 +1330,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.4</v>
+        <v>20.1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,54 +1369,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V10" t="n">
-        <v>54.94444</v>
+        <v>57.94639</v>
       </c>
       <c r="W10" t="n">
-        <v>-126.15722</v>
+        <v>-131.66722</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1426,21 +1426,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ORMOND 3 (L.353)</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092E  012</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2.8</v>
+        <v>36</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1470,49 +1470,49 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Ag 127g/t, Cu 6.07%</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$750k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P11" t="n">
-        <v>1988</v>
+        <v>2022</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Parallax Development Corp.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>49.29972</v>
+        <v>58.185</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.09722</v>
+        <v>-125.30611</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1522,21 +1522,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20.1</v>
+        <v>39.3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1566,28 +1566,28 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O12" t="n">
         <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
@@ -1601,14 +1601,14 @@
         <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>57.94639</v>
+        <v>58.15222</v>
       </c>
       <c r="W12" t="n">
-        <v>-131.66722</v>
+        <v>-125.27778</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -1714,21 +1714,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1753,33 +1753,33 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1793,14 +1793,14 @@
         <v>61</v>
       </c>
       <c r="V14" t="n">
-        <v>50.37417</v>
+        <v>50.16611</v>
       </c>
       <c r="W14" t="n">
-        <v>-116.36167</v>
+        <v>-125.39944</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -1810,30 +1810,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5.6</v>
+        <v>11.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1849,54 +1849,54 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$74k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>2019</v>
+        <v>1999</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U15" t="n">
         <v>61</v>
       </c>
       <c r="V15" t="n">
-        <v>50.16611</v>
+        <v>52.85806</v>
       </c>
       <c r="W15" t="n">
-        <v>-125.39944</v>
+        <v>-132.15722</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -1906,35 +1906,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>37.4</v>
+        <v>7.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1945,50 +1945,54 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Ag 10g/t, Au 9.6g/t</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>1966</v>
+        <v>1986</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U16" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V16" t="n">
-        <v>58.88222</v>
+        <v>49.30889</v>
       </c>
       <c r="W16" t="n">
-        <v>-132.1175</v>
+        <v>-120.00417</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -1998,35 +2002,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KING GEORGE (L.159)</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>092B  011</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>East Sooke</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.8</v>
+        <v>37.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2037,44 +2041,50 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>13 t</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>$2k</t>
+        </is>
+      </c>
       <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="V17" t="n">
-        <v>48.36806</v>
+        <v>58.88222</v>
       </c>
       <c r="W17" t="n">
-        <v>-123.69528</v>
+        <v>-132.1175</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2084,21 +2094,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
+          <t>AVON</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>093M  076</t>
+          <t>092F  350</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Kispiox</t>
+          <t>Chetarpe</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.6</v>
+        <v>24.6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2107,7 +2117,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead</t>
+          <t>Gold, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2123,44 +2133,570 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+          <t>Au 47.3g/t, Ag 53.1g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>$33k</t>
+        </is>
+      </c>
       <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>25</v>
+      </c>
+      <c r="U18" t="n">
+        <v>57</v>
+      </c>
+      <c r="V18" t="n">
+        <v>49.40417</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-125.75833</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROANAN                        </t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>104B  164</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Premier</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
         <v>13</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>325</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>55</v>
       </c>
-      <c r="V18" t="n">
-        <v>55.33556</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-127.69194</v>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+      <c r="V19" t="n">
+        <v>56.00194</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-130.04972</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>KING GEORGE (L.159)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>092B  011</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>East Sooke</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>13 t</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>7</v>
+      </c>
+      <c r="T20" t="n">
+        <v>175</v>
+      </c>
+      <c r="U20" t="n">
+        <v>55</v>
+      </c>
+      <c r="V20" t="n">
+        <v>48.36806</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-123.69528</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FISH CREEK</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>103O  005</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>13</v>
+      </c>
+      <c r="T21" t="n">
+        <v>325</v>
+      </c>
+      <c r="U21" t="n">
+        <v>55</v>
+      </c>
+      <c r="V21" t="n">
+        <v>55.99139</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-130.03694</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SIXMILE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>103O  002</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>13</v>
+      </c>
+      <c r="T22" t="n">
+        <v>325</v>
+      </c>
+      <c r="U22" t="n">
+        <v>55</v>
+      </c>
+      <c r="V22" t="n">
+        <v>55.98833</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-130.06194</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>092B  060</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Cliffside</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>13</v>
+      </c>
+      <c r="T23" t="n">
+        <v>325</v>
+      </c>
+      <c r="U23" t="n">
+        <v>55</v>
+      </c>
+      <c r="V23" t="n">
+        <v>48.6075</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-123.57111</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>092B  056</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Cliffside</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>12</v>
+      </c>
+      <c r="T24" t="n">
+        <v>300</v>
+      </c>
+      <c r="U24" t="n">
+        <v>55</v>
+      </c>
+      <c r="V24" t="n">
+        <v>48.61472</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-123.59222</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -954,35 +954,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t>MAPLE LEAF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>092F  039</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Kakawis</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2.2</v>
+        <v>16.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -993,46 +993,54 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+          <t>3 t</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Au 15.1g/t</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$307k</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>1986</v>
+        <v>2023</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="V6" t="n">
-        <v>49.7075</v>
+        <v>49.27111</v>
       </c>
       <c r="W6" t="n">
-        <v>-116.00528</v>
+        <v>-125.73167</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
         </is>
       </c>
     </row>
@@ -1042,30 +1050,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>WINCO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>104I  019</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Boulder City</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Silver, Copper, Lead, Gold, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1081,33 +1089,33 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Ag 487g/t, Cu 9.85%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>chip sample results include maximum values over 1 metre of 9.85 per cent copper and 486.86 grams per tonne silver;</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$3.2M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P7" t="n">
-        <v>1987</v>
+        <v>2025</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Quartz Mountain Resources Ltd., Wyn Development Inc., Horseshoe Gold Mining Inc.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1118,17 +1126,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V7" t="n">
-        <v>50.53139</v>
+        <v>58.78</v>
       </c>
       <c r="W7" t="n">
-        <v>-125.2025</v>
+        <v>-128.12222</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++019</t>
         </is>
       </c>
     </row>
@@ -1138,35 +1146,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>104I  098</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>McDame</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6.8</v>
+        <v>31.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1177,33 +1185,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1214,17 +1222,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V8" t="n">
-        <v>49.73278</v>
+        <v>58.90944</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.21139</v>
+        <v>-129.09278</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
         </is>
       </c>
     </row>
@@ -1234,30 +1242,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.4</v>
+        <v>2.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1273,54 +1281,46 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Cu 0.43%</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P9" t="n">
-        <v>2012</v>
+        <v>1986</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="V9" t="n">
-        <v>54.94444</v>
+        <v>49.7075</v>
       </c>
       <c r="W9" t="n">
-        <v>-126.15722</v>
+        <v>-116.00528</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1330,21 +1330,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>20.1</v>
+        <v>10.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1369,33 +1369,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>2019</v>
+        <v>1987</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1406,17 +1406,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>57.94639</v>
+        <v>50.53139</v>
       </c>
       <c r="W10" t="n">
-        <v>-131.66722</v>
+        <v>-125.2025</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1426,35 +1426,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>36</v>
+        <v>6.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
@@ -1502,17 +1502,17 @@
         <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V11" t="n">
-        <v>58.185</v>
+        <v>49.73278</v>
       </c>
       <c r="W11" t="n">
-        <v>-125.30611</v>
+        <v>-125.21139</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1522,21 +1522,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>39.3</v>
+        <v>7.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1561,54 +1561,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V12" t="n">
-        <v>58.15222</v>
+        <v>54.94444</v>
       </c>
       <c r="W12" t="n">
-        <v>-125.27778</v>
+        <v>-126.15722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1618,21 +1618,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RED CAP - EAST CIRQUE</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>104K  141</t>
+          <t>092E  088</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>21</v>
+        <v>1.8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Gold, Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,49 +1662,49 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 3.7g/t, Ag 26.0g/t</t>
+          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
+          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$208k</t>
+          <t>$766k</t>
         </is>
       </c>
       <c r="O13" t="n">
         <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>2007</v>
+        <v>1988</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U13" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>58.73639</v>
+        <v>49.29694</v>
       </c>
       <c r="W13" t="n">
-        <v>-133.24944</v>
+        <v>-126.08111</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
         </is>
       </c>
     </row>
@@ -1714,21 +1714,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1753,33 +1753,33 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1793,14 +1793,14 @@
         <v>61</v>
       </c>
       <c r="V14" t="n">
-        <v>50.16611</v>
+        <v>50.37417</v>
       </c>
       <c r="W14" t="n">
-        <v>-125.39944</v>
+        <v>-116.36167</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -1810,30 +1810,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HAIDA GOLD</t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>103C  002</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sewell Inlet</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>11.4</v>
+        <v>5.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1849,54 +1849,54 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>544 t</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 8.7g/t</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$74k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>1999</v>
+        <v>2019</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>61</v>
       </c>
       <c r="V15" t="n">
-        <v>52.85806</v>
+        <v>50.16611</v>
       </c>
       <c r="W15" t="n">
-        <v>-132.15722</v>
+        <v>-125.39944</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -1906,21 +1906,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7.5</v>
+        <v>11.4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1945,33 +1945,33 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$74k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>1986</v>
+        <v>1999</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1985,14 +1985,14 @@
         <v>61</v>
       </c>
       <c r="V16" t="n">
-        <v>49.30889</v>
+        <v>52.85806</v>
       </c>
       <c r="W16" t="n">
-        <v>-120.00417</v>
+        <v>-132.15722</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -2002,35 +2002,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>37.4</v>
+        <v>7.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2041,50 +2041,54 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Ag 10g/t, Au 9.6g/t</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>1966</v>
+        <v>1986</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U17" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>58.88222</v>
+        <v>49.30889</v>
       </c>
       <c r="W17" t="n">
-        <v>-132.1175</v>
+        <v>-120.00417</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -2094,35 +2098,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AVON</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>092F  350</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Chetarpe</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>24.6</v>
+        <v>37.4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -2133,54 +2137,50 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Au 47.3g/t, Ag 53.1g/t</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$33k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>1985</v>
+        <v>1966</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="V18" t="n">
-        <v>49.40417</v>
+        <v>58.88222</v>
       </c>
       <c r="W18" t="n">
-        <v>-125.75833</v>
+        <v>-132.1175</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2190,21 +2190,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROANAN                        </t>
+          <t>AVON</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>104B  164</t>
+          <t>092F  350</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Premier</t>
+          <t>Chetarpe</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5.7</v>
+        <v>24.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Gold, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2229,44 +2229,54 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+          <t>Au 47.3g/t, Ag 53.1g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>$33k</t>
+        </is>
+      </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U19" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V19" t="n">
-        <v>56.00194</v>
+        <v>49.40417</v>
       </c>
       <c r="W19" t="n">
-        <v>-130.04972</v>
+        <v>-125.75833</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
         </is>
       </c>
     </row>
@@ -2276,30 +2286,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KING GEORGE (L.159)</t>
+          <t>KATANGA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>092B  011</t>
+          <t>092GNE009</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>East Sooke</t>
+          <t>Williams Landing</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.8</v>
+        <v>9.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2315,44 +2325,54 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>13 t</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+          <t>Au 62.0g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>$4k</t>
+        </is>
+      </c>
       <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Black Swan Gold Mines Ltd.</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U20" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V20" t="n">
-        <v>48.36806</v>
+        <v>49.51111</v>
       </c>
       <c r="W20" t="n">
-        <v>-123.69528</v>
+        <v>-122.57306</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
         </is>
       </c>
     </row>
@@ -2362,30 +2382,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FISH CREEK</t>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>103O  005</t>
+          <t>092B  060</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2401,17 +2421,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2431,14 +2451,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>55.99139</v>
+        <v>48.6075</v>
       </c>
       <c r="W21" t="n">
-        <v>-130.03694</v>
+        <v>-123.57111</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
         </is>
       </c>
     </row>
@@ -2448,30 +2468,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SIXMILE</t>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>103O  002</t>
+          <t>092B  056</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7.1</v>
+        <v>1.9</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2487,17 +2507,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2508,23 +2528,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T22" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U22" t="n">
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>55.98833</v>
+        <v>48.61472</v>
       </c>
       <c r="W22" t="n">
-        <v>-130.06194</v>
+        <v>-123.59222</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
         </is>
       </c>
     </row>
@@ -2534,30 +2554,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
+          <t xml:space="preserve">ROANAN                        </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>092B  060</t>
+          <t>104B  164</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Premier</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2578,12 +2598,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2603,14 +2623,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>48.6075</v>
+        <v>56.00194</v>
       </c>
       <c r="W23" t="n">
-        <v>-123.57111</v>
+        <v>-130.04972</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>
       </c>
     </row>
@@ -2620,30 +2640,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>092B  056</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2659,17 +2679,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2680,23 +2700,195 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T24" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U24" t="n">
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>48.61472</v>
+        <v>55.99139</v>
       </c>
       <c r="W24" t="n">
-        <v>-123.59222</v>
+        <v>-130.03694</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CORMORANT                     </t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>092K  098</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Granite Bay</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>8</v>
+      </c>
+      <c r="T25" t="n">
+        <v>200</v>
+      </c>
+      <c r="U25" t="n">
+        <v>55</v>
+      </c>
+      <c r="V25" t="n">
+        <v>50.18694</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-125.28056</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SIXMILE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>103O  002</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>13</v>
+      </c>
+      <c r="T26" t="n">
+        <v>325</v>
+      </c>
+      <c r="U26" t="n">
+        <v>55</v>
+      </c>
+      <c r="V26" t="n">
+        <v>55.98833</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-130.06194</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -1146,21 +1146,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>31.5</v>
+        <v>2.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,33 +1185,25 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P8" t="n">
-        <v>2022</v>
+        <v>1986</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1222,17 +1214,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V8" t="n">
-        <v>58.90944</v>
+        <v>49.7075</v>
       </c>
       <c r="W8" t="n">
-        <v>-129.09278</v>
+        <v>-116.00528</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1242,35 +1234,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2.2</v>
+        <v>10.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,25 +1273,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+          <t>118 kt (assay)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1310,17 +1310,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>49.7075</v>
+        <v>50.53139</v>
       </c>
       <c r="W9" t="n">
-        <v>-116.00528</v>
+        <v>-125.2025</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1330,35 +1330,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10.8</v>
+        <v>6.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,33 +1369,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>1987</v>
+        <v>2018</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1409,14 +1409,14 @@
         <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>50.53139</v>
+        <v>49.73278</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.2025</v>
+        <v>-125.21139</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1426,35 +1426,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U11" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>49.73278</v>
+        <v>54.94444</v>
       </c>
       <c r="W11" t="n">
-        <v>-125.21139</v>
+        <v>-126.15722</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1522,21 +1522,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>ORMOND 3 (L.353)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092E  012</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7.4</v>
+        <v>2.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1561,54 +1561,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Ag 127g/t, Cu 6.07%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$750k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2012</v>
+        <v>1988</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Parallax Development Corp.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>275</v>
+        <v>125</v>
       </c>
       <c r="U12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>54.94444</v>
+        <v>49.29972</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.15722</v>
+        <v>-126.09722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
         </is>
       </c>
     </row>
@@ -1618,30 +1618,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MAIN</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092E  088</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.8</v>
+        <v>36</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Zinc</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,49 +1662,49 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$766k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>1988</v>
+        <v>2022</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>49.29694</v>
+        <v>58.185</v>
       </c>
       <c r="W13" t="n">
-        <v>-126.08111</v>
+        <v>-125.30611</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1714,21 +1714,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.1</v>
+        <v>39.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1753,33 +1753,33 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1790,17 +1790,17 @@
         <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>50.37417</v>
+        <v>58.15222</v>
       </c>
       <c r="W14" t="n">
-        <v>-116.36167</v>
+        <v>-125.27778</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -2072,10 +2072,10 @@
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U17" t="n">
         <v>61</v>
@@ -2190,30 +2190,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AVON</t>
+          <t xml:space="preserve">JOHN BULL                     </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>092F  350</t>
+          <t>092F  146</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Chetarpe</t>
+          <t>toxʷnač</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>24.6</v>
+        <v>3.3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead</t>
+          <t>Zinc, Silver, Copper, Lead, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2229,54 +2229,54 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 47.3g/t, Ag 53.1g/t</t>
+          <t>Ag 150.83g/t, Au 23.99g/t, Cu 0.8%, Pb 2%, Zn 52%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
+          <t>The best assays from several samples were 52 per cent zinc, 150.83 grams per tonne silver, 0.8 per cent copper, 2.0 per cent lead and 23.99 grams per tonne gold (Minister of Mines Annual Report 1926, page A312).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>$33k</t>
+          <t>$47k</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>1985</v>
+        <v>2023</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
+          <t>Aquarius Resources Limited, Geiger, K. Warren</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T19" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U19" t="n">
         <v>57</v>
       </c>
       <c r="V19" t="n">
-        <v>49.40417</v>
+        <v>49.94611</v>
       </c>
       <c r="W19" t="n">
-        <v>-125.75833</v>
+        <v>-124.71056</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++146</t>
         </is>
       </c>
     </row>
@@ -2286,30 +2286,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KATANGA</t>
+          <t>KING GEORGE (L.159)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>092GNE009</t>
+          <t>092B  011</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Williams Landing</t>
+          <t>East Sooke</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9.5</v>
+        <v>0.8</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2325,54 +2325,44 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>13 t</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 62.0g/t</t>
+          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>$4k</t>
-        </is>
-      </c>
+          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>2</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Black Swan Gold Mines Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U20" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>49.51111</v>
+        <v>48.36806</v>
       </c>
       <c r="W20" t="n">
-        <v>-122.57306</v>
+        <v>-123.69528</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
         </is>
       </c>
     </row>
@@ -2382,30 +2372,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
+          <t xml:space="preserve">ROANAN                        </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>092B  060</t>
+          <t>104B  164</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Premier</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2426,12 +2416,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2451,14 +2441,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>48.6075</v>
+        <v>56.00194</v>
       </c>
       <c r="W21" t="n">
-        <v>-123.57111</v>
+        <v>-130.04972</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>
       </c>
     </row>
@@ -2554,30 +2544,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROANAN                        </t>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>104B  164</t>
+          <t>092B  060</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Premier</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2598,12 +2588,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2623,14 +2613,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>56.00194</v>
+        <v>48.6075</v>
       </c>
       <c r="W23" t="n">
-        <v>-130.04972</v>
+        <v>-123.57111</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
         </is>
       </c>
     </row>
@@ -2640,12 +2630,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FISH CREEK</t>
+          <t>SIXMILE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>103O  005</t>
+          <t>103O  002</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2654,7 +2644,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2663,7 +2653,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2684,12 +2674,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2709,14 +2699,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>55.99139</v>
+        <v>55.98833</v>
       </c>
       <c r="W24" t="n">
-        <v>-130.03694</v>
+        <v>-130.06194</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
         </is>
       </c>
     </row>
@@ -2726,30 +2716,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORMORANT                     </t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>092K  098</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Granite Bay</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2765,17 +2755,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2786,23 +2776,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T25" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U25" t="n">
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>50.18694</v>
+        <v>55.99139</v>
       </c>
       <c r="W25" t="n">
-        <v>-125.28056</v>
+        <v>-130.03694</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
         </is>
       </c>
     </row>
@@ -2812,30 +2802,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SIXMILE</t>
+          <t xml:space="preserve">CORMORANT                     </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>103O  002</t>
+          <t>092K  098</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Granite Bay</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2851,17 +2841,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -2872,23 +2862,23 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T26" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U26" t="n">
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>55.98833</v>
+        <v>50.18694</v>
       </c>
       <c r="W26" t="n">
-        <v>-130.06194</v>
+        <v>-125.28056</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -1146,21 +1146,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>104I  098</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>McDame</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.2</v>
+        <v>31.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,25 +1185,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>1986</v>
+        <v>2022</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1214,17 +1222,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V8" t="n">
-        <v>49.7075</v>
+        <v>58.90944</v>
       </c>
       <c r="W8" t="n">
-        <v>-116.00528</v>
+        <v>-129.09278</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
         </is>
       </c>
     </row>
@@ -1234,35 +1242,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10.8</v>
+        <v>2.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1273,33 +1281,25 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P9" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1310,17 +1310,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="V9" t="n">
-        <v>50.53139</v>
+        <v>49.7075</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.2025</v>
+        <v>-116.00528</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1330,35 +1330,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.8</v>
+        <v>10.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,33 +1369,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>2018</v>
+        <v>1987</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1409,14 +1409,14 @@
         <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>49.73278</v>
+        <v>50.53139</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.21139</v>
+        <v>-125.2025</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1426,35 +1426,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V11" t="n">
-        <v>54.94444</v>
+        <v>49.73278</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.15722</v>
+        <v>-125.21139</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1522,21 +1522,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ORMOND 3 (L.353)</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>092E  012</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.8</v>
+        <v>7.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1561,54 +1561,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ag 127g/t, Cu 6.07%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$750k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>1988</v>
+        <v>2012</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Parallax Development Corp.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T12" t="n">
-        <v>125</v>
+        <v>275</v>
       </c>
       <c r="U12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V12" t="n">
-        <v>49.29972</v>
+        <v>54.94444</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.09722</v>
+        <v>-126.15722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1618,21 +1618,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>ORMOND 3 (L.353)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>092E  012</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>36</v>
+        <v>2.8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,49 +1662,49 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Ag 127g/t, Cu 6.07%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$750k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>2022</v>
+        <v>1988</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>Parallax Development Corp.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U13" t="n">
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>58.185</v>
+        <v>49.29972</v>
       </c>
       <c r="W13" t="n">
-        <v>-125.30611</v>
+        <v>-126.09722</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
         </is>
       </c>
     </row>
@@ -1714,30 +1714,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t>RED CAP - SLOPE ZONE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>104K  010</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>39.3</v>
+        <v>20</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1758,28 +1758,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
+          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$666k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P14" t="n">
-        <v>2022</v>
+        <v>2007</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1793,14 +1793,14 @@
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>58.15222</v>
+        <v>58.73611</v>
       </c>
       <c r="W14" t="n">
-        <v>-125.27778</v>
+        <v>-133.27</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
         </is>
       </c>
     </row>
@@ -1810,21 +1810,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5.6</v>
+        <v>20.1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1854,28 +1854,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P15" t="n">
         <v>2019</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1886,17 +1886,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V15" t="n">
-        <v>50.16611</v>
+        <v>57.94639</v>
       </c>
       <c r="W15" t="n">
-        <v>-125.39944</v>
+        <v>-131.66722</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1906,30 +1906,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HAIDA GOLD</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>103C  002</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sewell Inlet</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>11.4</v>
+        <v>36</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1945,54 +1945,54 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>544 t</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 8.7g/t</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$74k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>1999</v>
+        <v>2022</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V16" t="n">
-        <v>52.85806</v>
+        <v>58.185</v>
       </c>
       <c r="W16" t="n">
-        <v>-132.15722</v>
+        <v>-125.30611</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -2002,30 +2002,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7.5</v>
+        <v>39.3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2041,54 +2041,54 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>1986</v>
+        <v>2022</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V17" t="n">
-        <v>49.30889</v>
+        <v>58.15222</v>
       </c>
       <c r="W17" t="n">
-        <v>-120.00417</v>
+        <v>-125.27778</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -2098,35 +2098,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>37.4</v>
+        <v>21</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -2137,29 +2137,33 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>1966</v>
+        <v>2007</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
@@ -2170,17 +2174,17 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>58.88222</v>
+        <v>58.73639</v>
       </c>
       <c r="W18" t="n">
-        <v>-132.1175</v>
+        <v>-133.24944</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -2190,30 +2194,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOHN BULL                     </t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>092F  146</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>toxʷnač</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Lead, Gold, Molybdenum</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2234,49 +2238,49 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 150.83g/t, Au 23.99g/t, Cu 0.8%, Pb 2%, Zn 52%</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>The best assays from several samples were 52 per cent zinc, 150.83 grams per tonne silver, 0.8 per cent copper, 2.0 per cent lead and 23.99 grams per tonne gold (Minister of Mines Annual Report 1926, page A312).</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>$47k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
         <v>2023</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Aquarius Resources Limited, Geiger, K. Warren</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T19" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="V19" t="n">
-        <v>49.94611</v>
+        <v>50.37417</v>
       </c>
       <c r="W19" t="n">
-        <v>-124.71056</v>
+        <v>-116.36167</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -2286,30 +2290,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KING GEORGE (L.159)</t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>092B  011</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>East Sooke</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.8</v>
+        <v>11.4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2325,44 +2329,54 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>13 t</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>$74k</t>
+        </is>
+      </c>
       <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1999</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T20" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="U20" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V20" t="n">
-        <v>48.36806</v>
+        <v>52.85806</v>
       </c>
       <c r="W20" t="n">
-        <v>-123.69528</v>
+        <v>-132.15722</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -2372,35 +2386,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROANAN                        </t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>104B  164</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Premier</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5.7</v>
+        <v>37.4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I21" t="b">
@@ -2411,25 +2425,31 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>$2k</t>
+        </is>
+      </c>
       <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
         <v>13</v>
@@ -2438,447 +2458,17 @@
         <v>325</v>
       </c>
       <c r="U21" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="V21" t="n">
-        <v>56.00194</v>
+        <v>58.88222</v>
       </c>
       <c r="W21" t="n">
-        <v>-130.04972</v>
+        <v>-132.1175</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>092B  056</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Cliffside</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>12</v>
-      </c>
-      <c r="T22" t="n">
-        <v>300</v>
-      </c>
-      <c r="U22" t="n">
-        <v>55</v>
-      </c>
-      <c r="V22" t="n">
-        <v>48.61472</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-123.59222</v>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>092B  060</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Cliffside</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>13</v>
-      </c>
-      <c r="T23" t="n">
-        <v>325</v>
-      </c>
-      <c r="U23" t="n">
-        <v>55</v>
-      </c>
-      <c r="V23" t="n">
-        <v>48.6075</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-123.57111</v>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>SIXMILE</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>103O  002</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>13</v>
-      </c>
-      <c r="T24" t="n">
-        <v>325</v>
-      </c>
-      <c r="U24" t="n">
-        <v>55</v>
-      </c>
-      <c r="V24" t="n">
-        <v>55.98833</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-130.06194</v>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>FISH CREEK</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>103O  005</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>13</v>
-      </c>
-      <c r="T25" t="n">
-        <v>325</v>
-      </c>
-      <c r="U25" t="n">
-        <v>55</v>
-      </c>
-      <c r="V25" t="n">
-        <v>55.99139</v>
-      </c>
-      <c r="W25" t="n">
-        <v>-130.03694</v>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CORMORANT                     </t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>092K  098</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Granite Bay</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="n">
-        <v>11</v>
-      </c>
-      <c r="T26" t="n">
-        <v>275</v>
-      </c>
-      <c r="U26" t="n">
-        <v>55</v>
-      </c>
-      <c r="V26" t="n">
-        <v>50.18694</v>
-      </c>
-      <c r="W26" t="n">
-        <v>-125.28056</v>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WINCO</t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>104I  019</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Boulder City</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>66.40000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Gold, Zinc</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,33 +1089,25 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Ag 487g/t, Cu 9.85%</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>chip sample results include maximum values over 1 metre of 9.85 per cent copper and 486.86 grams per tonne silver;</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$3.2M</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P7" t="n">
-        <v>2025</v>
+        <v>1986</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Quartz Mountain Resources Ltd., Wyn Development Inc., Horseshoe Gold Mining Inc.</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1126,17 +1118,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V7" t="n">
-        <v>58.78</v>
+        <v>49.7075</v>
       </c>
       <c r="W7" t="n">
-        <v>-128.12222</v>
+        <v>-116.00528</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++019</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1146,30 +1138,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>31.5</v>
+        <v>10.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1185,33 +1177,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>2022</v>
+        <v>1987</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1222,17 +1214,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="V8" t="n">
-        <v>58.90944</v>
+        <v>50.53139</v>
       </c>
       <c r="W8" t="n">
-        <v>-129.09278</v>
+        <v>-125.2025</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1242,35 +1234,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2.2</v>
+        <v>6.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,25 +1273,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+          <t>1.0 Mt</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>1986</v>
+        <v>2018</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1310,17 +1310,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>49.7075</v>
+        <v>49.73278</v>
       </c>
       <c r="W9" t="n">
-        <v>-116.00528</v>
+        <v>-125.21139</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1330,21 +1330,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10.8</v>
+        <v>7.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,54 +1369,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>1987</v>
+        <v>2012</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>50.53139</v>
+        <v>54.94444</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.2025</v>
+        <v>-126.15722</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1426,35 +1426,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>MAGNET</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>092L  097</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Nimpkish</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Magnetite, Iron, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Cu 15.40%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$780k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="P11" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U11" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>49.73278</v>
+        <v>50.40806</v>
       </c>
       <c r="W11" t="n">
-        <v>-125.21139</v>
+        <v>-126.96167</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
         </is>
       </c>
     </row>
@@ -1522,21 +1522,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7.4</v>
+        <v>20.1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1561,54 +1561,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>54.94444</v>
+        <v>57.94639</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.15722</v>
+        <v>-131.66722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1618,21 +1618,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORMOND 3 (L.353)</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092E  012</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.8</v>
+        <v>36</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,49 +1662,49 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ag 127g/t, Cu 6.07%</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$750k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>1988</v>
+        <v>2022</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Parallax Development Corp.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>49.29972</v>
+        <v>58.185</v>
       </c>
       <c r="W13" t="n">
-        <v>-126.09722</v>
+        <v>-125.30611</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1714,30 +1714,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RED CAP - SLOPE ZONE</t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>104K  010</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>39.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1758,28 +1758,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$666k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>2007</v>
+        <v>2022</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1793,14 +1793,14 @@
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>58.73611</v>
+        <v>58.15222</v>
       </c>
       <c r="W14" t="n">
-        <v>-133.27</v>
+        <v>-125.27778</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -1810,21 +1810,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>20.1</v>
+        <v>6.1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1849,33 +1849,33 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1886,17 +1886,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V15" t="n">
-        <v>57.94639</v>
+        <v>50.37417</v>
       </c>
       <c r="W15" t="n">
-        <v>-131.66722</v>
+        <v>-116.36167</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -1906,30 +1906,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>36</v>
+        <v>7.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1945,54 +1945,54 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>2022</v>
+        <v>1986</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U16" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V16" t="n">
-        <v>58.185</v>
+        <v>49.30889</v>
       </c>
       <c r="W16" t="n">
-        <v>-125.30611</v>
+        <v>-120.00417</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -2002,35 +2002,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>39.3</v>
+        <v>37.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2041,33 +2041,29 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>2022</v>
+        <v>1966</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -2078,17 +2074,17 @@
         <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="V17" t="n">
-        <v>58.15222</v>
+        <v>58.88222</v>
       </c>
       <c r="W17" t="n">
-        <v>-125.27778</v>
+        <v>-132.1175</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2098,30 +2094,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RED CAP - EAST CIRQUE</t>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>104K  141</t>
+          <t>092B  060</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>21</v>
+        <v>3.6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2137,35 +2133,25 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 3.7g/t, Ag 26.0g/t</t>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>$208k</t>
-        </is>
-      </c>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>4</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2007</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
         <v>13</v>
@@ -2174,17 +2160,17 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>58.73639</v>
+        <v>48.6075</v>
       </c>
       <c r="W18" t="n">
-        <v>-133.24944</v>
+        <v>-123.57111</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
         </is>
       </c>
     </row>
@@ -2194,30 +2180,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>092B  056</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6.1</v>
+        <v>1.9</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2238,237 +2224,39 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>$170k</t>
-        </is>
-      </c>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>3</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2023</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T19" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>50.37417</v>
+        <v>48.61472</v>
       </c>
       <c r="W19" t="n">
-        <v>-116.36167</v>
+        <v>-123.59222</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>HAIDA GOLD</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>103C  002</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Sewell Inlet</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>544 t</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Au 8.7g/t</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>$74k</t>
-        </is>
-      </c>
-      <c r="O20" t="n">
-        <v>4</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1999</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="n">
-        <v>12</v>
-      </c>
-      <c r="T20" t="n">
-        <v>300</v>
-      </c>
-      <c r="U20" t="n">
-        <v>61</v>
-      </c>
-      <c r="V20" t="n">
-        <v>52.85806</v>
-      </c>
-      <c r="W20" t="n">
-        <v>-132.15722</v>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACE                           </t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>104K  025</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Callison Ranch</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Asbestos</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Developed Prospect  </t>
-        </is>
-      </c>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>$2k</t>
-        </is>
-      </c>
-      <c r="O21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1966</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>13</v>
-      </c>
-      <c r="T21" t="n">
-        <v>325</v>
-      </c>
-      <c r="U21" t="n">
-        <v>60</v>
-      </c>
-      <c r="V21" t="n">
-        <v>58.88222</v>
-      </c>
-      <c r="W21" t="n">
-        <v>-132.1175</v>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -954,35 +954,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MAPLE LEAF</t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>092F  039</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kakawis</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>16.7</v>
+        <v>2.2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -993,54 +993,46 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3 t</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Au 15.1g/t</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>$307k</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P6" t="n">
-        <v>2023</v>
+        <v>1986</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="V6" t="n">
-        <v>49.27111</v>
+        <v>49.7075</v>
       </c>
       <c r="W6" t="n">
-        <v>-125.73167</v>
+        <v>-116.00528</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1050,35 +1042,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2.2</v>
+        <v>10.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,25 +1081,33 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+          <t>118 kt (assay)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1118,17 +1118,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V7" t="n">
-        <v>49.7075</v>
+        <v>50.53139</v>
       </c>
       <c r="W7" t="n">
-        <v>-116.00528</v>
+        <v>-125.2025</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1138,35 +1138,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10.8</v>
+        <v>6.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1177,33 +1177,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>1987</v>
+        <v>2018</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1217,14 +1217,14 @@
         <v>67</v>
       </c>
       <c r="V8" t="n">
-        <v>50.53139</v>
+        <v>49.73278</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.2025</v>
+        <v>-125.21139</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1234,35 +1234,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1273,54 +1273,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U9" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V9" t="n">
-        <v>49.73278</v>
+        <v>54.94444</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.21139</v>
+        <v>-126.15722</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1330,21 +1330,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.4</v>
+        <v>20.1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,54 +1369,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V10" t="n">
-        <v>54.94444</v>
+        <v>57.94639</v>
       </c>
       <c r="W10" t="n">
-        <v>-126.15722</v>
+        <v>-131.66722</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1426,30 +1426,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MAGNET</t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092L  097</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nimpkish</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8.4</v>
+        <v>39.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Magnetite, Iron, Copper</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1470,49 +1470,49 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 15.40%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$780k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="P11" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>50.40806</v>
+        <v>58.15222</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.96167</v>
+        <v>-125.27778</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -1522,21 +1522,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20.1</v>
+        <v>6.1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1561,33 +1561,33 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
@@ -1598,17 +1598,17 @@
         <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V12" t="n">
-        <v>57.94639</v>
+        <v>50.37417</v>
       </c>
       <c r="W12" t="n">
-        <v>-131.66722</v>
+        <v>-116.36167</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -1618,30 +1618,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>36</v>
+        <v>7.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1657,54 +1657,54 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>2022</v>
+        <v>1986</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U13" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V13" t="n">
-        <v>58.185</v>
+        <v>49.30889</v>
       </c>
       <c r="W13" t="n">
-        <v>-125.30611</v>
+        <v>-120.00417</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -1714,35 +1714,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>39.3</v>
+        <v>37.4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1753,33 +1753,29 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>2022</v>
+        <v>1966</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1790,17 +1786,17 @@
         <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="V14" t="n">
-        <v>58.15222</v>
+        <v>58.88222</v>
       </c>
       <c r="W14" t="n">
-        <v>-125.27778</v>
+        <v>-132.1175</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -1810,30 +1806,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t xml:space="preserve">JOHN BULL                     </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>092F  146</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>toxʷnač</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.1</v>
+        <v>3.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Zinc, Silver, Copper, Lead, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1854,49 +1850,49 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Ag 150.83g/t, Au 23.99g/t, Cu 0.8%, Pb 2%, Zn 52%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>The best assays from several samples were 52 per cent zinc, 150.83 grams per tonne silver, 0.8 per cent copper, 2.0 per cent lead and 23.99 grams per tonne gold (Minister of Mines Annual Report 1926, page A312).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$47k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P15" t="n">
         <v>2023</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Aquarius Resources Limited, Geiger, K. Warren</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U15" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="V15" t="n">
-        <v>50.37417</v>
+        <v>49.94611</v>
       </c>
       <c r="W15" t="n">
-        <v>-116.36167</v>
+        <v>-124.71056</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++146</t>
         </is>
       </c>
     </row>
@@ -1906,30 +1902,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>092B  056</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7.5</v>
+        <v>1.9</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1950,49 +1946,39 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>$64k</t>
-        </is>
-      </c>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>2</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1986</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U16" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>49.30889</v>
+        <v>48.61472</v>
       </c>
       <c r="W16" t="n">
-        <v>-120.00417</v>
+        <v>-123.59222</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
         </is>
       </c>
     </row>
@@ -2002,35 +1988,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>092B  060</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>37.4</v>
+        <v>3.6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2041,31 +2027,25 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>$2k</t>
-        </is>
-      </c>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1966</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
         <v>13</v>
@@ -2074,17 +2054,17 @@
         <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>58.88222</v>
+        <v>48.6075</v>
       </c>
       <c r="W17" t="n">
-        <v>-132.1175</v>
+        <v>-123.57111</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
         </is>
       </c>
     </row>
@@ -2094,30 +2074,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
+          <t xml:space="preserve">SILVER BELL                   </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>092B  060</t>
+          <t>093M  076</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Kispiox</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+          <t>Gold, Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2138,12 +2118,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2163,100 +2143,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>48.6075</v>
+        <v>55.33556</v>
       </c>
       <c r="W18" t="n">
-        <v>-123.57111</v>
+        <v>-127.69194</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>092B  056</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Cliffside</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>12</v>
-      </c>
-      <c r="T19" t="n">
-        <v>300</v>
-      </c>
-      <c r="U19" t="n">
-        <v>55</v>
-      </c>
-      <c r="V19" t="n">
-        <v>48.61472</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-123.59222</v>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:X25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -954,35 +954,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t>MAPLE LEAF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>092F  039</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Kakawis</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2.2</v>
+        <v>16.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -993,46 +993,54 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+          <t>3 t</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Au 15.1g/t</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$307k</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>1986</v>
+        <v>2023</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="V6" t="n">
-        <v>49.7075</v>
+        <v>49.27111</v>
       </c>
       <c r="W6" t="n">
-        <v>-116.00528</v>
+        <v>-125.73167</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
         </is>
       </c>
     </row>
@@ -1042,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10.8</v>
+        <v>2.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1081,33 +1089,25 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P7" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1118,17 +1118,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="V7" t="n">
-        <v>50.53139</v>
+        <v>49.7075</v>
       </c>
       <c r="W7" t="n">
-        <v>-125.2025</v>
+        <v>-116.00528</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1138,35 +1138,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6.8</v>
+        <v>10.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1177,33 +1177,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>2018</v>
+        <v>1987</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1217,14 +1217,14 @@
         <v>67</v>
       </c>
       <c r="V8" t="n">
-        <v>49.73278</v>
+        <v>50.53139</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.21139</v>
+        <v>-125.2025</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1234,35 +1234,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1273,54 +1273,54 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>54.94444</v>
+        <v>49.73278</v>
       </c>
       <c r="W9" t="n">
-        <v>-126.15722</v>
+        <v>-125.21139</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1330,21 +1330,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>20.1</v>
+        <v>7.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,54 +1369,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U10" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>57.94639</v>
+        <v>54.94444</v>
       </c>
       <c r="W10" t="n">
-        <v>-131.66722</v>
+        <v>-126.15722</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1426,30 +1426,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t>MAGNET</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>092L  097</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Nimpkish</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>39.3</v>
+        <v>8.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Magnetite, Iron, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1470,49 +1470,49 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
+          <t>Cu 15.40%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$780k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="P11" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U11" t="n">
         <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>58.15222</v>
+        <v>50.40806</v>
       </c>
       <c r="W11" t="n">
-        <v>-125.27778</v>
+        <v>-126.96167</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
         </is>
       </c>
     </row>
@@ -1522,30 +1522,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t>RED CAP - SLOPE ZONE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>104K  010</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.1</v>
+        <v>20</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1561,33 +1561,33 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$666k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="P12" t="n">
-        <v>2023</v>
+        <v>2007</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
@@ -1598,17 +1598,17 @@
         <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>50.37417</v>
+        <v>58.73611</v>
       </c>
       <c r="W12" t="n">
-        <v>-116.36167</v>
+        <v>-133.27</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
         </is>
       </c>
     </row>
@@ -1618,30 +1618,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7.5</v>
+        <v>20.1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1657,54 +1657,54 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>1986</v>
+        <v>2019</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>49.30889</v>
+        <v>57.94639</v>
       </c>
       <c r="W13" t="n">
-        <v>-120.00417</v>
+        <v>-131.66722</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1714,35 +1714,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>37.4</v>
+        <v>36</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1753,29 +1753,33 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Au 5.8g/t, Cu 7.88%</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P14" t="n">
-        <v>1966</v>
+        <v>2022</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1786,17 +1790,17 @@
         <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>58.88222</v>
+        <v>58.185</v>
       </c>
       <c r="W14" t="n">
-        <v>-132.1175</v>
+        <v>-125.30611</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1806,30 +1810,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOHN BULL                     </t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>092F  146</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>toxʷnač</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3.3</v>
+        <v>39.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Lead, Gold, Molybdenum</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1845,54 +1849,54 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ag 150.83g/t, Au 23.99g/t, Cu 0.8%, Pb 2%, Zn 52%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>The best assays from several samples were 52 per cent zinc, 150.83 grams per tonne silver, 0.8 per cent copper, 2.0 per cent lead and 23.99 grams per tonne gold (Minister of Mines Annual Report 1926, page A312).</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$47k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Aquarius Resources Limited, Geiger, K. Warren</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="V15" t="n">
-        <v>49.94611</v>
+        <v>58.15222</v>
       </c>
       <c r="W15" t="n">
-        <v>-124.71056</v>
+        <v>-125.27778</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -1902,30 +1906,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>092B  056</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1941,44 +1945,54 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>$102k</t>
+        </is>
+      </c>
       <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2019</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Volatus Capital Corp., Osborne, T.</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V16" t="n">
-        <v>48.61472</v>
+        <v>50.16611</v>
       </c>
       <c r="W16" t="n">
-        <v>-123.59222</v>
+        <v>-125.39944</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -1988,30 +2002,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>092B  060</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3.6</v>
+        <v>11.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2027,25 +2041,35 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>$74k</t>
+        </is>
+      </c>
       <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1999</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
         <v>13</v>
@@ -2054,17 +2078,17 @@
         <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>48.6075</v>
+        <v>52.85806</v>
       </c>
       <c r="W17" t="n">
-        <v>-123.57111</v>
+        <v>-132.15722</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -2074,35 +2098,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>093M  076</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Kispiox</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.6</v>
+        <v>37.4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -2113,25 +2137,31 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>$2k</t>
+        </is>
+      </c>
       <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
         <v>13</v>
@@ -2140,17 +2170,629 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
+        <v>60</v>
+      </c>
+      <c r="V18" t="n">
+        <v>58.88222</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-132.1175</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIDNIGHT NAILS 1-2            </t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>082LSE063</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Cherryville</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Au 11.1g/t, Ag 76.0g/t, Pb 1.05%</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>In 1983, samples from the Cherry shear assayed up to 158 grams per tonne gold and 1251 grams per tonne silver, while a sample of the altered dike or sill assayed 4.2 per cent lead, 1.86 per cent zinc, 42.2 grams per tonne gold and 212.5 grams per tonne silver (Assessment Report 11892). In 1987, a sample (R-7) wall rock adjacent to the vein assayed 75.3 grams per tonne gold, 147 grams per tonne silver and 1.96 per cent lead over 0.6 metre (Assessment Report 17386). In 1988, samples from the vein in the Cherry shear assayed up to 2.16 grams per tonne gold and 0.9 gram per tonne silver over 1 metre, while samples from areas with no quartz veining assayed up to 20 grams per tonne gold, 1.05 per cent lead and 76 grams per tonne silver over 90 metres (Assessment Report 18706). Samples from disco</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>$47k</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>9</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2026</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Mohawk Oil Co. Ltd., Howard, Lennie Lee</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>6</v>
+      </c>
+      <c r="T19" t="n">
+        <v>150</v>
+      </c>
+      <c r="U19" t="n">
+        <v>57</v>
+      </c>
+      <c r="V19" t="n">
+        <v>50.17861</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-118.54</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSE063</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>092B  056</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Cliffside</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>12</v>
+      </c>
+      <c r="T20" t="n">
+        <v>300</v>
+      </c>
+      <c r="U20" t="n">
         <v>55</v>
       </c>
-      <c r="V18" t="n">
+      <c r="V20" t="n">
+        <v>48.61472</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-123.59222</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILVER BELL                   </t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>093M  076</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Kispiox</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Zinc, Lead</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>13</v>
+      </c>
+      <c r="T21" t="n">
+        <v>325</v>
+      </c>
+      <c r="U21" t="n">
+        <v>55</v>
+      </c>
+      <c r="V21" t="n">
         <v>55.33556</v>
       </c>
-      <c r="W18" t="n">
+      <c r="W21" t="n">
         <v>-127.69194</v>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CORMORANT                     </t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>092K  098</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Granite Bay</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" t="n">
+        <v>200</v>
+      </c>
+      <c r="U22" t="n">
+        <v>55</v>
+      </c>
+      <c r="V22" t="n">
+        <v>50.18694</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-125.28056</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FISH CREEK</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>103O  005</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>13</v>
+      </c>
+      <c r="T23" t="n">
+        <v>325</v>
+      </c>
+      <c r="U23" t="n">
+        <v>55</v>
+      </c>
+      <c r="V23" t="n">
+        <v>55.99139</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-130.03694</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SIXMILE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>103O  002</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>13</v>
+      </c>
+      <c r="T24" t="n">
+        <v>325</v>
+      </c>
+      <c r="U24" t="n">
+        <v>55</v>
+      </c>
+      <c r="V24" t="n">
+        <v>55.98833</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-130.06194</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROANAN                        </t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>104B  164</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Premier</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>13</v>
+      </c>
+      <c r="T25" t="n">
+        <v>325</v>
+      </c>
+      <c r="U25" t="n">
+        <v>55</v>
+      </c>
+      <c r="V25" t="n">
+        <v>56.00194</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-130.04972</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -1426,30 +1426,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MAGNET</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092L  097</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nimpkish</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8.4</v>
+        <v>20.1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Magnetite, Iron, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1470,49 +1470,49 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 15.40%</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$780k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="P11" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>50.40806</v>
+        <v>57.94639</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.96167</v>
+        <v>-131.66722</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RED CAP - SLOPE ZONE</t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>104K  010</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1536,16 +1536,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1566,21 +1566,21 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$666k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
         <v>2007</v>
@@ -1598,17 +1598,17 @@
         <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V12" t="n">
-        <v>58.73611</v>
+        <v>58.73639</v>
       </c>
       <c r="W12" t="n">
-        <v>-133.27</v>
+        <v>-133.24944</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -1618,21 +1618,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>20.1</v>
+        <v>5.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,28 +1662,28 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
         <v>2019</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -1694,17 +1694,17 @@
         <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V13" t="n">
-        <v>57.94639</v>
+        <v>50.16611</v>
       </c>
       <c r="W13" t="n">
-        <v>-131.66722</v>
+        <v>-125.39944</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -1714,30 +1714,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>36</v>
+        <v>7.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1753,54 +1753,54 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>2022</v>
+        <v>1986</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U14" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V14" t="n">
-        <v>58.185</v>
+        <v>49.30889</v>
       </c>
       <c r="W14" t="n">
-        <v>-125.30611</v>
+        <v>-120.00417</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -1810,35 +1810,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>39.3</v>
+        <v>37.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1849,33 +1849,29 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>2022</v>
+        <v>1966</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1886,17 +1882,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="V15" t="n">
-        <v>58.15222</v>
+        <v>58.88222</v>
       </c>
       <c r="W15" t="n">
-        <v>-125.27778</v>
+        <v>-132.1175</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -1906,30 +1902,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t xml:space="preserve">JOHN BULL                     </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>092F  146</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>toxʷnač</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Zinc, Silver, Copper, Lead, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1945,54 +1941,54 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Ag 150.83g/t, Au 23.99g/t, Cu 0.8%, Pb 2%, Zn 52%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>The best assays from several samples were 52 per cent zinc, 150.83 grams per tonne silver, 0.8 per cent copper, 2.0 per cent lead and 23.99 grams per tonne gold (Minister of Mines Annual Report 1926, page A312).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$47k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P16" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>Aquarius Resources Limited, Geiger, K. Warren</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U16" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="V16" t="n">
-        <v>50.16611</v>
+        <v>49.94611</v>
       </c>
       <c r="W16" t="n">
-        <v>-125.39944</v>
+        <v>-124.71056</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++146</t>
         </is>
       </c>
     </row>
@@ -2002,30 +1998,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HAIDA GOLD</t>
+          <t>KING GEORGE (L.159)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>103C  002</t>
+          <t>092B  011</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sewell Inlet</t>
+          <t>East Sooke</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11.4</v>
+        <v>0.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2041,54 +2037,44 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>544 t</t>
+          <t>13 t</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 8.7g/t</t>
+          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>$74k</t>
-        </is>
-      </c>
+          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>4</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1999</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U17" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>52.85806</v>
+        <v>48.36806</v>
       </c>
       <c r="W17" t="n">
-        <v>-132.15722</v>
+        <v>-123.69528</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
         </is>
       </c>
     </row>
@@ -2098,35 +2084,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>092B  056</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>37.4</v>
+        <v>1.9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -2137,31 +2123,25 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>$2k</t>
-        </is>
-      </c>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1966</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
         <v>13</v>
@@ -2170,17 +2150,17 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>58.88222</v>
+        <v>48.61472</v>
       </c>
       <c r="W18" t="n">
-        <v>-132.1175</v>
+        <v>-123.59222</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
         </is>
       </c>
     </row>
@@ -2190,30 +2170,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIDNIGHT NAILS 1-2            </t>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>082LSE063</t>
+          <t>092B  060</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cherryville</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.1</v>
+        <v>3.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc</t>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2229,54 +2209,44 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 11.1g/t, Ag 76.0g/t, Pb 1.05%</t>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>In 1983, samples from the Cherry shear assayed up to 158 grams per tonne gold and 1251 grams per tonne silver, while a sample of the altered dike or sill assayed 4.2 per cent lead, 1.86 per cent zinc, 42.2 grams per tonne gold and 212.5 grams per tonne silver (Assessment Report 11892). In 1987, a sample (R-7) wall rock adjacent to the vein assayed 75.3 grams per tonne gold, 147 grams per tonne silver and 1.96 per cent lead over 0.6 metre (Assessment Report 17386). In 1988, samples from the vein in the Cherry shear assayed up to 2.16 grams per tonne gold and 0.9 gram per tonne silver over 1 metre, while samples from areas with no quartz veining assayed up to 20 grams per tonne gold, 1.05 per cent lead and 76 grams per tonne silver over 90 metres (Assessment Report 18706). Samples from disco</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>$47k</t>
-        </is>
-      </c>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>9</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2026</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Mohawk Oil Co. Ltd., Howard, Lennie Lee</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T19" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>50.17861</v>
+        <v>48.6075</v>
       </c>
       <c r="W19" t="n">
-        <v>-118.54</v>
+        <v>-123.57111</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSE063</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
         </is>
       </c>
     </row>
@@ -2286,30 +2256,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>092B  056</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2325,17 +2295,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2346,23 +2316,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U20" t="n">
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>48.61472</v>
+        <v>55.99139</v>
       </c>
       <c r="W20" t="n">
-        <v>-123.59222</v>
+        <v>-130.03694</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
         </is>
       </c>
     </row>
@@ -2458,30 +2428,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORMORANT                     </t>
+          <t>SIXMILE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>092K  098</t>
+          <t>103O  002</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Granite Bay</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2497,17 +2467,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2518,23 +2488,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T22" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U22" t="n">
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>50.18694</v>
+        <v>55.98833</v>
       </c>
       <c r="W22" t="n">
-        <v>-125.28056</v>
+        <v>-130.06194</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
         </is>
       </c>
     </row>
@@ -2544,30 +2514,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FISH CREEK</t>
+          <t xml:space="preserve">CORMORANT                     </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>103O  005</t>
+          <t>092K  098</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Granite Bay</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2583,17 +2553,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2604,195 +2574,23 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T23" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U23" t="n">
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>55.99139</v>
+        <v>50.18694</v>
       </c>
       <c r="W23" t="n">
-        <v>-130.03694</v>
+        <v>-125.28056</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>SIXMILE</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>103O  002</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>13</v>
-      </c>
-      <c r="T24" t="n">
-        <v>325</v>
-      </c>
-      <c r="U24" t="n">
-        <v>55</v>
-      </c>
-      <c r="V24" t="n">
-        <v>55.98833</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-130.06194</v>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ROANAN                        </t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>104B  164</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Premier</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>13</v>
-      </c>
-      <c r="T25" t="n">
-        <v>325</v>
-      </c>
-      <c r="U25" t="n">
-        <v>55</v>
-      </c>
-      <c r="V25" t="n">
-        <v>56.00194</v>
-      </c>
-      <c r="W25" t="n">
-        <v>-130.04972</v>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:X25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -1426,30 +1426,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>MAGNET</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>092L  097</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Nimpkish</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>20.1</v>
+        <v>8.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Magnetite, Iron, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1470,49 +1470,49 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Cu 15.40%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$780k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="P11" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U11" t="n">
         <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>57.94639</v>
+        <v>50.40806</v>
       </c>
       <c r="W11" t="n">
-        <v>-131.66722</v>
+        <v>-126.96167</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RED CAP - EAST CIRQUE</t>
+          <t>RED CAP - SLOPE ZONE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>104K  141</t>
+          <t>104K  010</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1536,16 +1536,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1566,21 +1566,21 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 3.7g/t, Ag 26.0g/t</t>
+          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
+          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$208k</t>
+          <t>$666k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="P12" t="n">
         <v>2007</v>
@@ -1598,17 +1598,17 @@
         <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>58.73639</v>
+        <v>58.73611</v>
       </c>
       <c r="W12" t="n">
-        <v>-133.24944</v>
+        <v>-133.27</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
         </is>
       </c>
     </row>
@@ -1618,21 +1618,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5.6</v>
+        <v>20.1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,28 +1662,28 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P13" t="n">
         <v>2019</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -1694,17 +1694,17 @@
         <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>50.16611</v>
+        <v>57.94639</v>
       </c>
       <c r="W13" t="n">
-        <v>-125.39944</v>
+        <v>-131.66722</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1714,30 +1714,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>7.5</v>
+        <v>36</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1753,54 +1753,54 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P14" t="n">
-        <v>1986</v>
+        <v>2022</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>49.30889</v>
+        <v>58.185</v>
       </c>
       <c r="W14" t="n">
-        <v>-120.00417</v>
+        <v>-125.30611</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1810,35 +1810,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>37.4</v>
+        <v>39.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1849,29 +1849,33 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>1966</v>
+        <v>2022</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1882,17 +1886,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="V15" t="n">
-        <v>58.88222</v>
+        <v>58.15222</v>
       </c>
       <c r="W15" t="n">
-        <v>-132.1175</v>
+        <v>-125.27778</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -1902,30 +1906,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOHN BULL                     </t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>092F  146</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>toxʷnač</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Lead, Gold, Molybdenum</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1941,54 +1945,54 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ag 150.83g/t, Au 23.99g/t, Cu 0.8%, Pb 2%, Zn 52%</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>The best assays from several samples were 52 per cent zinc, 150.83 grams per tonne silver, 0.8 per cent copper, 2.0 per cent lead and 23.99 grams per tonne gold (Minister of Mines Annual Report 1926, page A312).</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$47k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Aquarius Resources Limited, Geiger, K. Warren</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="V16" t="n">
-        <v>49.94611</v>
+        <v>50.16611</v>
       </c>
       <c r="W16" t="n">
-        <v>-124.71056</v>
+        <v>-125.39944</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -1998,30 +2002,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KING GEORGE (L.159)</t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>092B  011</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>East Sooke</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.8</v>
+        <v>11.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2037,44 +2041,54 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>13 t</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>$74k</t>
+        </is>
+      </c>
       <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1999</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>48.36806</v>
+        <v>52.85806</v>
       </c>
       <c r="W17" t="n">
-        <v>-123.69528</v>
+        <v>-132.15722</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -2084,35 +2098,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>092B  056</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.9</v>
+        <v>37.4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -2123,25 +2137,31 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>$2k</t>
+        </is>
+      </c>
       <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
         <v>13</v>
@@ -2150,17 +2170,17 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="V18" t="n">
-        <v>48.61472</v>
+        <v>58.88222</v>
       </c>
       <c r="W18" t="n">
-        <v>-123.59222</v>
+        <v>-132.1175</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2170,30 +2190,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
+          <t xml:space="preserve">MIDNIGHT NAILS 1-2            </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>092B  060</t>
+          <t>082LSE063</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Cherryville</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3.6</v>
+        <v>8.1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+          <t>Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2209,44 +2229,54 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+          <t>Au 11.1g/t, Ag 76.0g/t, Pb 1.05%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>In 1983, samples from the Cherry shear assayed up to 158 grams per tonne gold and 1251 grams per tonne silver, while a sample of the altered dike or sill assayed 4.2 per cent lead, 1.86 per cent zinc, 42.2 grams per tonne gold and 212.5 grams per tonne silver (Assessment Report 11892). In 1987, a sample (R-7) wall rock adjacent to the vein assayed 75.3 grams per tonne gold, 147 grams per tonne silver and 1.96 per cent lead over 0.6 metre (Assessment Report 17386). In 1988, samples from the vein in the Cherry shear assayed up to 2.16 grams per tonne gold and 0.9 gram per tonne silver over 1 metre, while samples from areas with no quartz veining assayed up to 20 grams per tonne gold, 1.05 per cent lead and 76 grams per tonne silver over 90 metres (Assessment Report 18706). Samples from disco</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>$47k</t>
+        </is>
+      </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2026</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Mohawk Oil Co. Ltd., Howard, Lennie Lee</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U19" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V19" t="n">
-        <v>48.6075</v>
+        <v>50.17861</v>
       </c>
       <c r="W19" t="n">
-        <v>-123.57111</v>
+        <v>-118.54</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSE063</t>
         </is>
       </c>
     </row>
@@ -2256,30 +2286,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FISH CREEK</t>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>103O  005</t>
+          <t>092B  056</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2295,17 +2325,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2316,23 +2346,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T20" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U20" t="n">
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>55.99139</v>
+        <v>48.61472</v>
       </c>
       <c r="W20" t="n">
-        <v>-130.03694</v>
+        <v>-123.59222</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
         </is>
       </c>
     </row>
@@ -2428,30 +2458,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SIXMILE</t>
+          <t xml:space="preserve">CORMORANT                     </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>103O  002</t>
+          <t>092K  098</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Granite Bay</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2467,17 +2497,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2488,23 +2518,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T22" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U22" t="n">
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>55.98833</v>
+        <v>50.18694</v>
       </c>
       <c r="W22" t="n">
-        <v>-130.06194</v>
+        <v>-125.28056</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
         </is>
       </c>
     </row>
@@ -2514,30 +2544,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORMORANT                     </t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>092K  098</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Granite Bay</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2553,17 +2583,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2574,23 +2604,195 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U23" t="n">
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>50.18694</v>
+        <v>55.99139</v>
       </c>
       <c r="W23" t="n">
-        <v>-125.28056</v>
+        <v>-130.03694</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SIXMILE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>103O  002</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>13</v>
+      </c>
+      <c r="T24" t="n">
+        <v>325</v>
+      </c>
+      <c r="U24" t="n">
+        <v>55</v>
+      </c>
+      <c r="V24" t="n">
+        <v>55.98833</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-130.06194</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROANAN                        </t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>104B  164</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Premier</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>13</v>
+      </c>
+      <c r="T25" t="n">
+        <v>325</v>
+      </c>
+      <c r="U25" t="n">
+        <v>55</v>
+      </c>
+      <c r="V25" t="n">
+        <v>56.00194</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-130.04972</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:X28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -1050,30 +1050,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t xml:space="preserve">EDYE PASS                     </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>103J  015</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Hunts Inlet</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2.2</v>
+        <v>10.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1089,46 +1089,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+          <t>226 kt</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Au 29.0g/t, Ag 10.0g/t</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Assays of a 1-metre wide vein yielded 29 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1935). The highest rock sample sample #780401 with 45g/t Au gold over a 45 centimetre width was located 60 m west of the drill pad where earlier exploration was conducted on the Cedar Vein system 200 m east of the historic Dawson workings in the area of the lineament of the Edye Shear zone.</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$1.8M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P7" t="n">
-        <v>1986</v>
+        <v>2022</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>Porcher Island Gold Corporation, Cathedral Gold Corp., Tombill Mines</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U7" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V7" t="n">
-        <v>49.7075</v>
+        <v>54.0275</v>
       </c>
       <c r="W7" t="n">
-        <v>-116.00528</v>
+        <v>-130.585</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103J++015</t>
         </is>
       </c>
     </row>
@@ -1138,30 +1146,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>104I  098</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>McDame</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10.8</v>
+        <v>31.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1177,33 +1185,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>1987</v>
+        <v>2022</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1214,17 +1222,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V8" t="n">
-        <v>50.53139</v>
+        <v>58.90944</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.2025</v>
+        <v>-129.09278</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
         </is>
       </c>
     </row>
@@ -1234,35 +1242,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6.8</v>
+        <v>2.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1273,33 +1281,25 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P9" t="n">
-        <v>2018</v>
+        <v>1986</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1310,17 +1310,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="V9" t="n">
-        <v>49.73278</v>
+        <v>49.7075</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.21139</v>
+        <v>-116.00528</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1330,21 +1330,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.4</v>
+        <v>10.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,54 +1369,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>2012</v>
+        <v>1987</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>54.94444</v>
+        <v>50.53139</v>
       </c>
       <c r="W10" t="n">
-        <v>-126.15722</v>
+        <v>-125.2025</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1426,35 +1426,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MAGNET</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092L  097</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nimpkish</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Magnetite, Iron, Copper</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 15.40%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$780k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V11" t="n">
-        <v>50.40806</v>
+        <v>49.73278</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.96167</v>
+        <v>-125.21139</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1522,35 +1522,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RED CAP - SLOPE ZONE</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>104K  010</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1561,54 +1561,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$666k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>2007</v>
+        <v>2012</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V12" t="n">
-        <v>58.73611</v>
+        <v>54.94444</v>
       </c>
       <c r="W12" t="n">
-        <v>-133.27</v>
+        <v>-126.15722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1618,30 +1618,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>MAGNET</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>092L  097</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Nimpkish</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>20.1</v>
+        <v>8.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Magnetite, Iron, Copper</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,49 +1662,49 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Cu 15.40%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$780k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="P13" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U13" t="n">
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>57.94639</v>
+        <v>50.40806</v>
       </c>
       <c r="W13" t="n">
-        <v>-131.66722</v>
+        <v>-126.96167</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
         </is>
       </c>
     </row>
@@ -1714,30 +1714,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>RED CAP - SLOPE ZONE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>104K  010</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1758,28 +1758,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$666k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P14" t="n">
-        <v>2022</v>
+        <v>2007</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1793,14 +1793,14 @@
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>58.185</v>
+        <v>58.73611</v>
       </c>
       <c r="W14" t="n">
-        <v>-125.30611</v>
+        <v>-133.27</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>39.3</v>
+        <v>36</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1854,28 +1854,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
         <v>2022</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1889,14 +1889,14 @@
         <v>65</v>
       </c>
       <c r="V15" t="n">
-        <v>58.15222</v>
+        <v>58.185</v>
       </c>
       <c r="W15" t="n">
-        <v>-125.27778</v>
+        <v>-125.30611</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1906,21 +1906,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5.6</v>
+        <v>39.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1950,28 +1950,28 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P16" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1982,17 +1982,17 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V16" t="n">
-        <v>50.16611</v>
+        <v>58.15222</v>
       </c>
       <c r="W16" t="n">
-        <v>-125.39944</v>
+        <v>-125.27778</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -2002,21 +2002,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HAIDA GOLD</t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>103C  002</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sewell Inlet</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11.4</v>
+        <v>21</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2041,33 +2041,33 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>544 t</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 8.7g/t</t>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$74k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O17" t="n">
         <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>1999</v>
+        <v>2007</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -2081,14 +2081,14 @@
         <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>52.85806</v>
+        <v>58.73639</v>
       </c>
       <c r="W17" t="n">
-        <v>-132.15722</v>
+        <v>-133.24944</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -2098,35 +2098,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>37.4</v>
+        <v>11.4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -2137,29 +2137,33 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>544 t</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Au 8.7g/t</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$74k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>1966</v>
+        <v>1999</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
@@ -2170,17 +2174,17 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>58.88222</v>
+        <v>52.85806</v>
       </c>
       <c r="W18" t="n">
-        <v>-132.1175</v>
+        <v>-132.15722</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -2190,21 +2194,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIDNIGHT NAILS 1-2            </t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>082LSE063</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cherryville</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2213,7 +2217,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2229,54 +2233,54 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 11.1g/t, Ag 76.0g/t, Pb 1.05%</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>In 1983, samples from the Cherry shear assayed up to 158 grams per tonne gold and 1251 grams per tonne silver, while a sample of the altered dike or sill assayed 4.2 per cent lead, 1.86 per cent zinc, 42.2 grams per tonne gold and 212.5 grams per tonne silver (Assessment Report 11892). In 1987, a sample (R-7) wall rock adjacent to the vein assayed 75.3 grams per tonne gold, 147 grams per tonne silver and 1.96 per cent lead over 0.6 metre (Assessment Report 17386). In 1988, samples from the vein in the Cherry shear assayed up to 2.16 grams per tonne gold and 0.9 gram per tonne silver over 1 metre, while samples from areas with no quartz veining assayed up to 20 grams per tonne gold, 1.05 per cent lead and 76 grams per tonne silver over 90 metres (Assessment Report 18706). Samples from disco</t>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>$47k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
-        <v>2026</v>
+        <v>1986</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Mohawk Oil Co. Ltd., Howard, Lennie Lee</t>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T19" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="U19" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="V19" t="n">
-        <v>50.17861</v>
+        <v>49.30889</v>
       </c>
       <c r="W19" t="n">
-        <v>-118.54</v>
+        <v>-120.00417</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSE063</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -2286,35 +2290,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>092B  056</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.9</v>
+        <v>37.4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2325,44 +2329,50 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>$2k</t>
+        </is>
+      </c>
       <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U20" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="V20" t="n">
-        <v>48.61472</v>
+        <v>58.88222</v>
       </c>
       <c r="W20" t="n">
-        <v>-123.59222</v>
+        <v>-132.1175</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2372,30 +2382,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
+          <t xml:space="preserve">JOHN BULL                     </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>093M  076</t>
+          <t>092F  146</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kispiox</t>
+          <t>toxʷnač</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead</t>
+          <t>Zinc, Silver, Copper, Lead, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2416,39 +2426,49 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+          <t>Ag 150.83g/t, Au 23.99g/t, Cu 0.8%, Pb 2%, Zn 52%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>The best assays from several samples were 52 per cent zinc, 150.83 grams per tonne silver, 0.8 per cent copper, 2.0 per cent lead and 23.99 grams per tonne gold (Minister of Mines Annual Report 1926, page A312).</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>$47k</t>
+        </is>
+      </c>
       <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Aquarius Resources Limited, Geiger, K. Warren</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T21" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U21" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V21" t="n">
-        <v>55.33556</v>
+        <v>49.94611</v>
       </c>
       <c r="W21" t="n">
-        <v>-127.69194</v>
+        <v>-124.71056</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++146</t>
         </is>
       </c>
     </row>
@@ -2458,30 +2478,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORMORANT                     </t>
+          <t>AVON</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>092K  098</t>
+          <t>092F  350</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Granite Bay</t>
+          <t>Chetarpe</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5.3</v>
+        <v>24.6</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2497,44 +2517,54 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+          <t>Au 47.3g/t, Ag 53.1g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>$33k</t>
+        </is>
+      </c>
       <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="U22" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V22" t="n">
-        <v>50.18694</v>
+        <v>49.40417</v>
       </c>
       <c r="W22" t="n">
-        <v>-125.28056</v>
+        <v>-125.75833</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
         </is>
       </c>
     </row>
@@ -2544,21 +2574,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FISH CREEK</t>
+          <t>KATANGA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>103O  005</t>
+          <t>092GNE009</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Williams Landing</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6.6</v>
+        <v>9.5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2567,7 +2597,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2588,20 +2618,30 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+          <t>Au 62.0g/t</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>$4k</t>
+        </is>
+      </c>
       <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Black Swan Gold Mines Ltd.</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
         <v>13</v>
@@ -2610,17 +2650,17 @@
         <v>325</v>
       </c>
       <c r="U23" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V23" t="n">
-        <v>55.99139</v>
+        <v>49.51111</v>
       </c>
       <c r="W23" t="n">
-        <v>-130.03694</v>
+        <v>-122.57306</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
         </is>
       </c>
     </row>
@@ -2630,21 +2670,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SIXMILE</t>
+          <t xml:space="preserve">ROANAN                        </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>103O  002</t>
+          <t>104B  164</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Premier</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2653,7 +2693,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2669,17 +2709,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2699,14 +2739,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>55.98833</v>
+        <v>56.00194</v>
       </c>
       <c r="W24" t="n">
-        <v>-130.06194</v>
+        <v>-130.04972</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>
       </c>
     </row>
@@ -2716,21 +2756,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROANAN                        </t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>104B  164</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Premier</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2755,17 +2795,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2785,14 +2825,272 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>56.00194</v>
+        <v>55.99139</v>
       </c>
       <c r="W25" t="n">
-        <v>-130.04972</v>
+        <v>-130.03694</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SIXMILE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>103O  002</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>13</v>
+      </c>
+      <c r="T26" t="n">
+        <v>325</v>
+      </c>
+      <c r="U26" t="n">
+        <v>55</v>
+      </c>
+      <c r="V26" t="n">
+        <v>55.98833</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-130.06194</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CORMORANT                     </t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>092K  098</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Granite Bay</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>200</v>
+      </c>
+      <c r="U27" t="n">
+        <v>55</v>
+      </c>
+      <c r="V27" t="n">
+        <v>50.18694</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-125.28056</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>KING GEORGE (L.159)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>092B  011</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>East Sooke</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>13 t</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>125</v>
+      </c>
+      <c r="U28" t="n">
+        <v>55</v>
+      </c>
+      <c r="V28" t="n">
+        <v>48.36806</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-123.69528</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X28"/>
+  <dimension ref="A1:X25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDYE PASS                     </t>
+          <t>WINCO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>103J  015</t>
+          <t>104I  019</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hunts Inlet</t>
+          <t>Boulder City</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10.7</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Silver, Copper, Lead, Gold, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,54 +1089,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>226 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 29.0g/t, Ag 10.0g/t</t>
+          <t>Ag 487g/t, Cu 9.85%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Assays of a 1-metre wide vein yielded 29 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1935). The highest rock sample sample #780401 with 45g/t Au gold over a 45 centimetre width was located 60 m west of the drill pad where earlier exploration was conducted on the Cedar Vein system 200 m east of the historic Dawson workings in the area of the lineament of the Edye Shear zone.</t>
+          <t>chip sample results include maximum values over 1 metre of 9.85 per cent copper and 486.86 grams per tonne silver;</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$1.8M</t>
+          <t>$3.2M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="P7" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Porcher Island Gold Corporation, Cathedral Gold Corp., Tombill Mines</t>
+          <t>Quartz Mountain Resources Ltd., Wyn Development Inc., Horseshoe Gold Mining Inc.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
         <v>70</v>
       </c>
       <c r="V7" t="n">
-        <v>54.0275</v>
+        <v>58.78</v>
       </c>
       <c r="W7" t="n">
-        <v>-130.585</v>
+        <v>-128.12222</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103J++015</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++019</t>
         </is>
       </c>
     </row>
@@ -1618,30 +1618,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MAGNET</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092L  097</t>
+          <t>092E  088</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nimpkish</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>8.4</v>
+        <v>1.8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Magnetite, Iron, Copper</t>
+          <t>Gold, Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,49 +1662,49 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Cu 15.40%</t>
+          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
+          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$780k</t>
+          <t>$766k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>2025</v>
+        <v>1988</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
+          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T13" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="U13" t="n">
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>50.40806</v>
+        <v>49.29694</v>
       </c>
       <c r="W13" t="n">
-        <v>-126.96167</v>
+        <v>-126.08111</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
         </is>
       </c>
     </row>
@@ -1714,30 +1714,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RED CAP - SLOPE ZONE</t>
+          <t>ORMOND 3 (L.353)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>104K  010</t>
+          <t>092E  012</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>2.8</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1758,49 +1758,49 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
+          <t>Ag 127g/t, Cu 6.07%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
+          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$666k</t>
+          <t>$750k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>2007</v>
+        <v>1988</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Parallax Development Corp.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U14" t="n">
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>58.73611</v>
+        <v>49.29972</v>
       </c>
       <c r="W14" t="n">
-        <v>-133.27</v>
+        <v>-126.09722</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
         </is>
       </c>
     </row>
@@ -1810,30 +1810,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>RED CAP - SLOPE ZONE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>104K  010</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1854,28 +1854,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$666k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P15" t="n">
-        <v>2022</v>
+        <v>2007</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1889,14 +1889,14 @@
         <v>65</v>
       </c>
       <c r="V15" t="n">
-        <v>58.185</v>
+        <v>58.73611</v>
       </c>
       <c r="W15" t="n">
-        <v>-125.30611</v>
+        <v>-133.27</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
         </is>
       </c>
     </row>
@@ -1906,21 +1906,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>39.3</v>
+        <v>20.1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1950,28 +1950,28 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O16" t="n">
         <v>8</v>
       </c>
       <c r="P16" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1985,14 +1985,14 @@
         <v>65</v>
       </c>
       <c r="V16" t="n">
-        <v>58.15222</v>
+        <v>57.94639</v>
       </c>
       <c r="W16" t="n">
-        <v>-125.27778</v>
+        <v>-131.66722</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -2098,30 +2098,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HAIDA GOLD</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>103C  002</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sewell Inlet</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.4</v>
+        <v>6.1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2137,33 +2137,33 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>544 t</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 8.7g/t</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$74k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>1999</v>
+        <v>2023</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
@@ -2177,14 +2177,14 @@
         <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>52.85806</v>
+        <v>50.37417</v>
       </c>
       <c r="W18" t="n">
-        <v>-132.15722</v>
+        <v>-116.36167</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -2194,35 +2194,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>7.5</v>
+        <v>37.4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2233,54 +2233,50 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>1986</v>
+        <v>1966</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T19" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V19" t="n">
-        <v>49.30889</v>
+        <v>58.88222</v>
       </c>
       <c r="W19" t="n">
-        <v>-120.00417</v>
+        <v>-132.1175</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2290,35 +2286,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">MIDNIGHT NAILS 1-2            </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>082LSE063</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Cherryville</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>37.4</v>
+        <v>8.1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2329,50 +2325,54 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Au 11.1g/t, Ag 76.0g/t, Pb 1.05%</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>In 1983, samples from the Cherry shear assayed up to 158 grams per tonne gold and 1251 grams per tonne silver, while a sample of the altered dike or sill assayed 4.2 per cent lead, 1.86 per cent zinc, 42.2 grams per tonne gold and 212.5 grams per tonne silver (Assessment Report 11892). In 1987, a sample (R-7) wall rock adjacent to the vein assayed 75.3 grams per tonne gold, 147 grams per tonne silver and 1.96 per cent lead over 0.6 metre (Assessment Report 17386). In 1988, samples from the vein in the Cherry shear assayed up to 2.16 grams per tonne gold and 0.9 gram per tonne silver over 1 metre, while samples from areas with no quartz veining assayed up to 20 grams per tonne gold, 1.05 per cent lead and 76 grams per tonne silver over 90 metres (Assessment Report 18706). Samples from disco</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$47k</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P20" t="n">
-        <v>1966</v>
+        <v>2026</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Mohawk Oil Co. Ltd., Howard, Lennie Lee</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U20" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="V20" t="n">
-        <v>58.88222</v>
+        <v>50.17861</v>
       </c>
       <c r="W20" t="n">
-        <v>-132.1175</v>
+        <v>-118.54</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSE063</t>
         </is>
       </c>
     </row>
@@ -2382,30 +2382,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOHN BULL                     </t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>092F  146</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>toxʷnač</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Lead, Gold, Molybdenum</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2421,54 +2421,44 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ag 150.83g/t, Au 23.99g/t, Cu 0.8%, Pb 2%, Zn 52%</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>The best assays from several samples were 52 per cent zinc, 150.83 grams per tonne silver, 0.8 per cent copper, 2.0 per cent lead and 23.99 grams per tonne gold (Minister of Mines Annual Report 1926, page A312).</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>$47k</t>
-        </is>
-      </c>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>8</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2023</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Aquarius Resources Limited, Geiger, K. Warren</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T21" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U21" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>49.94611</v>
+        <v>55.99139</v>
       </c>
       <c r="W21" t="n">
-        <v>-124.71056</v>
+        <v>-130.03694</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
         </is>
       </c>
     </row>
@@ -2478,21 +2468,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AVON</t>
+          <t>SIXMILE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>092F  350</t>
+          <t>103O  002</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Chetarpe</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>24.6</v>
+        <v>7.1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2501,7 +2491,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2522,49 +2512,39 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 47.3g/t, Ag 53.1g/t</t>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>$33k</t>
-        </is>
-      </c>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>4</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T22" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U22" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>49.40417</v>
+        <v>55.98833</v>
       </c>
       <c r="W22" t="n">
-        <v>-125.75833</v>
+        <v>-130.06194</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
         </is>
       </c>
     </row>
@@ -2574,30 +2554,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KATANGA</t>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>092GNE009</t>
+          <t>092B  060</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Williams Landing</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>9.5</v>
+        <v>3.6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2613,35 +2593,25 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 62.0g/t</t>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>$4k</t>
-        </is>
-      </c>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
-        <v>2</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Black Swan Gold Mines Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
         <v>13</v>
@@ -2650,17 +2620,17 @@
         <v>325</v>
       </c>
       <c r="U23" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>49.51111</v>
+        <v>48.6075</v>
       </c>
       <c r="W23" t="n">
-        <v>-122.57306</v>
+        <v>-123.57111</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
         </is>
       </c>
     </row>
@@ -2670,30 +2640,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROANAN                        </t>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>104B  164</t>
+          <t>092B  056</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Premier</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2714,12 +2684,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2739,14 +2709,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>56.00194</v>
+        <v>48.61472</v>
       </c>
       <c r="W24" t="n">
-        <v>-130.04972</v>
+        <v>-123.59222</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
         </is>
       </c>
     </row>
@@ -2756,21 +2726,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FISH CREEK</t>
+          <t xml:space="preserve">SILVER BELL                   </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>103O  005</t>
+          <t>093M  076</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Kispiox</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6.6</v>
+        <v>1.6</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2779,7 +2749,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Gold, Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2795,17 +2765,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2825,272 +2795,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>55.99139</v>
+        <v>55.33556</v>
       </c>
       <c r="W25" t="n">
-        <v>-130.03694</v>
+        <v>-127.69194</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>SIXMILE</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>103O  002</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="n">
-        <v>13</v>
-      </c>
-      <c r="T26" t="n">
-        <v>325</v>
-      </c>
-      <c r="U26" t="n">
-        <v>55</v>
-      </c>
-      <c r="V26" t="n">
-        <v>55.98833</v>
-      </c>
-      <c r="W26" t="n">
-        <v>-130.06194</v>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CORMORANT                     </t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>092K  098</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Granite Bay</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I27" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="n">
-        <v>8</v>
-      </c>
-      <c r="T27" t="n">
-        <v>200</v>
-      </c>
-      <c r="U27" t="n">
-        <v>55</v>
-      </c>
-      <c r="V27" t="n">
-        <v>50.18694</v>
-      </c>
-      <c r="W27" t="n">
-        <v>-125.28056</v>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>KING GEORGE (L.159)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>092B  011</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>East Sooke</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I28" t="b">
-        <v>1</v>
-      </c>
-      <c r="J28" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>13 t</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="n">
-        <v>5</v>
-      </c>
-      <c r="T28" t="n">
-        <v>125</v>
-      </c>
-      <c r="U28" t="n">
-        <v>55</v>
-      </c>
-      <c r="V28" t="n">
-        <v>48.36806</v>
-      </c>
-      <c r="W28" t="n">
-        <v>-123.69528</v>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -1146,21 +1146,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>31.5</v>
+        <v>2.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,33 +1185,25 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P8" t="n">
-        <v>2022</v>
+        <v>1986</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1222,17 +1214,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V8" t="n">
-        <v>58.90944</v>
+        <v>49.7075</v>
       </c>
       <c r="W8" t="n">
-        <v>-129.09278</v>
+        <v>-116.00528</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1242,35 +1234,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2.2</v>
+        <v>10.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,25 +1273,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+          <t>118 kt (assay)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1310,17 +1310,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>49.7075</v>
+        <v>50.53139</v>
       </c>
       <c r="W9" t="n">
-        <v>-116.00528</v>
+        <v>-125.2025</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1330,35 +1330,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10.8</v>
+        <v>6.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,33 +1369,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>1987</v>
+        <v>2018</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1409,14 +1409,14 @@
         <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>50.53139</v>
+        <v>49.73278</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.2025</v>
+        <v>-125.21139</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1426,35 +1426,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U11" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>49.73278</v>
+        <v>54.94444</v>
       </c>
       <c r="W11" t="n">
-        <v>-125.21139</v>
+        <v>-126.15722</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1522,35 +1522,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>MAGNET</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092L  097</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Nimpkish</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Magnetite, Iron, Copper</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1561,54 +1561,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Cu 15.40%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$780k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P12" t="n">
-        <v>2012</v>
+        <v>2025</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T12" t="n">
-        <v>275</v>
+        <v>175</v>
       </c>
       <c r="U12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>54.94444</v>
+        <v>50.40806</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.15722</v>
+        <v>-126.96167</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
         </is>
       </c>
     </row>
@@ -1618,30 +1618,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MAIN</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092E  088</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.8</v>
+        <v>36</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Zinc</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,49 +1662,49 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$766k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>1988</v>
+        <v>2022</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>49.29694</v>
+        <v>58.185</v>
       </c>
       <c r="W13" t="n">
-        <v>-126.08111</v>
+        <v>-125.30611</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1714,21 +1714,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ORMOND 3 (L.353)</t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>092E  012</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2.8</v>
+        <v>39.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1758,49 +1758,49 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 127g/t, Cu 6.07%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$750k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>1988</v>
+        <v>2022</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Parallax Development Corp.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>49.29972</v>
+        <v>58.15222</v>
       </c>
       <c r="W14" t="n">
-        <v>-126.09722</v>
+        <v>-125.27778</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -1810,30 +1810,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RED CAP - SLOPE ZONE</t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>104K  010</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>20</v>
+        <v>5.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1854,28 +1854,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$666k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>2007</v>
+        <v>2019</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1886,17 +1886,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V15" t="n">
-        <v>58.73611</v>
+        <v>50.16611</v>
       </c>
       <c r="W15" t="n">
-        <v>-133.27</v>
+        <v>-125.39944</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -1906,30 +1906,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>20.1</v>
+        <v>11.4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1945,54 +1945,54 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$74k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>2019</v>
+        <v>1999</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U16" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V16" t="n">
-        <v>57.94639</v>
+        <v>52.85806</v>
       </c>
       <c r="W16" t="n">
-        <v>-131.66722</v>
+        <v>-132.15722</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -2002,21 +2002,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RED CAP - EAST CIRQUE</t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>104K  141</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>21</v>
+        <v>7.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2041,54 +2041,54 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 3.7g/t, Ag 26.0g/t</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$208k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>2007</v>
+        <v>1986</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U17" t="n">
         <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>58.73639</v>
+        <v>49.30889</v>
       </c>
       <c r="W17" t="n">
-        <v>-133.24944</v>
+        <v>-120.00417</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -2098,35 +2098,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6.1</v>
+        <v>37.4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -2137,33 +2137,29 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>2023</v>
+        <v>1966</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
@@ -2174,17 +2170,17 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V18" t="n">
-        <v>50.37417</v>
+        <v>58.88222</v>
       </c>
       <c r="W18" t="n">
-        <v>-116.36167</v>
+        <v>-132.1175</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2194,35 +2190,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">JOHN BULL                     </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>092F  146</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>toxʷnač</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>37.4</v>
+        <v>3.3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Zinc, Silver, Copper, Lead, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2233,50 +2229,54 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Ag 150.83g/t, Au 23.99g/t, Cu 0.8%, Pb 2%, Zn 52%</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>The best assays from several samples were 52 per cent zinc, 150.83 grams per tonne silver, 0.8 per cent copper, 2.0 per cent lead and 23.99 grams per tonne gold (Minister of Mines Annual Report 1926, page A312).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$47k</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>1966</v>
+        <v>2023</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Aquarius Resources Limited, Geiger, K. Warren</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T19" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U19" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="V19" t="n">
-        <v>58.88222</v>
+        <v>49.94611</v>
       </c>
       <c r="W19" t="n">
-        <v>-132.1175</v>
+        <v>-124.71056</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++146</t>
         </is>
       </c>
     </row>
@@ -2286,21 +2286,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIDNIGHT NAILS 1-2            </t>
+          <t>KATANGA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>082LSE063</t>
+          <t>092GNE009</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cherryville</t>
+          <t>Williams Landing</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.1</v>
+        <v>9.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2330,49 +2330,49 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 11.1g/t, Ag 76.0g/t, Pb 1.05%</t>
+          <t>Au 62.0g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>In 1983, samples from the Cherry shear assayed up to 158 grams per tonne gold and 1251 grams per tonne silver, while a sample of the altered dike or sill assayed 4.2 per cent lead, 1.86 per cent zinc, 42.2 grams per tonne gold and 212.5 grams per tonne silver (Assessment Report 11892). In 1987, a sample (R-7) wall rock adjacent to the vein assayed 75.3 grams per tonne gold, 147 grams per tonne silver and 1.96 per cent lead over 0.6 metre (Assessment Report 17386). In 1988, samples from the vein in the Cherry shear assayed up to 2.16 grams per tonne gold and 0.9 gram per tonne silver over 1 metre, while samples from areas with no quartz veining assayed up to 20 grams per tonne gold, 1.05 per cent lead and 76 grams per tonne silver over 90 metres (Assessment Report 18706). Samples from disco</t>
+          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>$47k</t>
+          <t>$4k</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>2026</v>
+        <v>1985</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Mohawk Oil Co. Ltd., Howard, Lennie Lee</t>
+          <t>Black Swan Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U20" t="n">
         <v>57</v>
       </c>
       <c r="V20" t="n">
-        <v>50.17861</v>
+        <v>49.51111</v>
       </c>
       <c r="W20" t="n">
-        <v>-118.54</v>
+        <v>-122.57306</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSE063</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
         </is>
       </c>
     </row>
@@ -2382,30 +2382,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FISH CREEK</t>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>103O  005</t>
+          <t>092B  060</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2421,17 +2421,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2451,14 +2451,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>55.99139</v>
+        <v>48.6075</v>
       </c>
       <c r="W21" t="n">
-        <v>-130.03694</v>
+        <v>-123.57111</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
         </is>
       </c>
     </row>
@@ -2468,30 +2468,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SIXMILE</t>
+          <t>KING GEORGE (L.159)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>103O  002</t>
+          <t>092B  011</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>East Sooke</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7.1</v>
+        <v>0.8</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2507,17 +2507,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>13 t</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2528,23 +2528,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T22" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U22" t="n">
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>55.98833</v>
+        <v>48.36806</v>
       </c>
       <c r="W22" t="n">
-        <v>-130.06194</v>
+        <v>-123.69528</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
         </is>
       </c>
     </row>
@@ -2554,30 +2554,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>092B  060</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2593,17 +2593,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2623,14 +2623,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>48.6075</v>
+        <v>55.99139</v>
       </c>
       <c r="W23" t="n">
-        <v>-123.57111</v>
+        <v>-130.03694</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
         </is>
       </c>
     </row>
@@ -2640,30 +2640,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+          <t>SIXMILE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>092B  056</t>
+          <t>103O  002</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.9</v>
+        <v>7.1</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2679,17 +2679,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2709,14 +2709,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>48.61472</v>
+        <v>55.98833</v>
       </c>
       <c r="W24" t="n">
-        <v>-123.59222</v>
+        <v>-130.06194</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
         </is>
       </c>
     </row>
@@ -2726,30 +2726,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>093M  076</t>
+          <t>092B  056</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Kispiox</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead</t>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2795,14 +2795,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>55.33556</v>
+        <v>48.61472</v>
       </c>
       <c r="W25" t="n">
-        <v>-127.69194</v>
+        <v>-123.59222</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:X24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -762,35 +762,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ERICKSEN-ASHBY</t>
+          <t>CHARLIE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>104K  009</t>
+          <t>092O  043</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Nemaiah Valley</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5.3</v>
+        <v>36.9</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold, Rhodonite</t>
+          <t>Gold, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -801,54 +801,54 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>907 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 0.9g/t, Ag 567g/t, Pb 5.68%, Zn 5.21%</t>
+          <t>Au 16.0g/t, Ag 224g/t</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3 intersected 20.2 metres which assayed 567.1 grams per tonne silver, 4.94 per cent lead and 4.22 per cent zinc; 4 intersected 5.1 metres which assayed 627.4 grams per tonne silver, 6.42 per cent lead and 6.2 per cent zinc (Assessment Report 10026). In 1981, a 15.1 metre drill intersection in mineralized cherts in Zone 8 assayed 173.1 grams per tonne silver, 1.2 per cent lead and 1.37 per cent zinc (Assessment Report 10026). Identified over an 8 metre width, some samples yielded high assays of 1203 grams per tonne silver, 23.23 per cent zinc, 20.24 per cent lead and 0.69 gram per tonne gold. Grab samples from the mineralized zone, 5 to 7 metres wide, of fine-grained pyrite, sphalerite, galena and quartz were assayed yielding 1.13 grams per tonne gold, 144.0 grams per tonne silver, 2.14 per</t>
+          <t>A chip sample assayed 279.9 grams per tonne silver, 10.6 grams per tonne gold and 13.68 per cent copper (Bulletin 81). The following year, samples from the East vein area assayed up to 0.48 per cent copper, 1.0 gram per tonne gold and 14.3 grams per tonne silver (Assessment Report 12105). In 1987, chip samples from the Charlie vein, taken over a length of 20 metres and width of 20 centimetres, averaged 22.1 grams per tonne gold and 224.0 grams per tonne silver, while a sample (AB 245B) of the DK vein assayed 9.9 grams per tonne gold, 95.8 grams per tonne silver and 0.14 per cent lead (Assessment Report 17038). A 20- centimetre sample of massive sulphide from the Big vein assayed 8.2 grams per tonne gold, 8557 grams per tonne silver and 26.0 per cent copper (Assessment Report 17038). In 199</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>$286k</t>
+          <t>$6.3M</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="P4" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Optima Minerals Inc., Northwind Ventures, Terratest</t>
+          <t>Galore Resources Inc., Suncor, Galore Resources Inc.; Zelon Enterprises Ltd.</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U4" t="n">
         <v>75</v>
       </c>
       <c r="V4" t="n">
-        <v>58.65806</v>
+        <v>51.18028</v>
       </c>
       <c r="W4" t="n">
-        <v>-133.475</v>
+        <v>-123.67083</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++009</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092O++043</t>
         </is>
       </c>
     </row>
@@ -858,30 +858,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DRIFTPILE CREEK</t>
+          <t>ERICKSEN-ASHBY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>094K  066</t>
+          <t>104K  009</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>5.3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Barite</t>
+          <t>Silver, Lead, Zinc, Gold, Rhodonite</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -897,54 +897,54 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>18.1 Mt</t>
+          <t>907 kt</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Pb 1.18%, Zn 10.00%</t>
+          <t>Au 0.9g/t, Ag 567g/t, Pb 5.68%, Zn 5.21%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>In 1980, it was reported that shallow drilling in 11 areas indicated reserves of approximately 18,145,000 tonnes averaging 2.38 per cent combined lead-zinc (Canadian Mines Handbook 1980-81, pages 280-281). In 1978, the best drill intersection from the North Trench zone (hole 78-07) was 11.7 metres grading 7.45 per cent combined lead and zinc, whereas drilling on the Ridge zone yielded 3 per cent combined lead and zinc over 26.2 metres and 4.14 per cent zinc over 7.5 metres in drillhole 78-09 (Assessment Report 7149 and 24609). In 1993, drilling on the Main zone intersected a 12-metre zone grading 10 per cent zinc and 1 per cent lead, including a zone of 6.02 metres grading 12.26 per cent zinc and 1.36 per cent lead in hole 93-56 (Assessment Report 23109). Several narrow high-grade intercep</t>
+          <t>3 intersected 20.2 metres which assayed 567.1 grams per tonne silver, 4.94 per cent lead and 4.22 per cent zinc; 4 intersected 5.1 metres which assayed 627.4 grams per tonne silver, 6.42 per cent lead and 6.2 per cent zinc (Assessment Report 10026). In 1981, a 15.1 metre drill intersection in mineralized cherts in Zone 8 assayed 173.1 grams per tonne silver, 1.2 per cent lead and 1.37 per cent zinc (Assessment Report 10026). Identified over an 8 metre width, some samples yielded high assays of 1203 grams per tonne silver, 23.23 per cent zinc, 20.24 per cent lead and 0.69 gram per tonne gold. Grab samples from the mineralized zone, 5 to 7 metres wide, of fine-grained pyrite, sphalerite, galena and quartz were assayed yielding 1.13 grams per tonne gold, 144.0 grams per tonne silver, 2.14 per</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>$1.4M</t>
+          <t>$286k</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Teck Exploration Ltd., Welcome North Mines Limited, Teck Corporation</t>
+          <t>Optima Minerals Inc., Northwind Ventures, Terratest</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V5" t="n">
-        <v>58.06639</v>
+        <v>58.65806</v>
       </c>
       <c r="W5" t="n">
-        <v>-125.90972</v>
+        <v>-133.475</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++066</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++009</t>
         </is>
       </c>
     </row>
@@ -954,30 +954,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MAPLE LEAF</t>
+          <t>DRIFTPILE CREEK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>092F  039</t>
+          <t>094K  066</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kakawis</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>16.7</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Zinc, Lead, Barite</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -993,54 +993,54 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3 t</t>
+          <t>18.1 Mt</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 15.1g/t</t>
+          <t>Pb 1.18%, Zn 10.00%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
+          <t>In 1980, it was reported that shallow drilling in 11 areas indicated reserves of approximately 18,145,000 tonnes averaging 2.38 per cent combined lead-zinc (Canadian Mines Handbook 1980-81, pages 280-281). In 1978, the best drill intersection from the North Trench zone (hole 78-07) was 11.7 metres grading 7.45 per cent combined lead and zinc, whereas drilling on the Ridge zone yielded 3 per cent combined lead and zinc over 26.2 metres and 4.14 per cent zinc over 7.5 metres in drillhole 78-09 (Assessment Report 7149 and 24609). In 1993, drilling on the Main zone intersected a 12-metre zone grading 10 per cent zinc and 1 per cent lead, including a zone of 6.02 metres grading 12.26 per cent zinc and 1.36 per cent lead in hole 93-56 (Assessment Report 23109). Several narrow high-grade intercep</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>$307k</t>
+          <t>$1.4M</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P6" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
+          <t>Teck Exploration Ltd., Welcome North Mines Limited, Teck Corporation</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="U6" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="V6" t="n">
-        <v>49.27111</v>
+        <v>58.06639</v>
       </c>
       <c r="W6" t="n">
-        <v>-125.73167</v>
+        <v>-125.90972</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++066</t>
         </is>
       </c>
     </row>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WINCO</t>
+          <t>MAPLE LEAF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>104I  019</t>
+          <t>092F  039</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Boulder City</t>
+          <t>Kakawis</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>66.40000000000001</v>
+        <v>16.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Gold, Zinc</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,54 +1089,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>3 t</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ag 487g/t, Cu 9.85%</t>
+          <t>Au 15.1g/t</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>chip sample results include maximum values over 1 metre of 9.85 per cent copper and 486.86 grams per tonne silver;</t>
+          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$3.2M</t>
+          <t>$307k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P7" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Quartz Mountain Resources Ltd., Wyn Development Inc., Horseshoe Gold Mining Inc.</t>
+          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="V7" t="n">
-        <v>58.78</v>
+        <v>49.27111</v>
       </c>
       <c r="W7" t="n">
-        <v>-128.12222</v>
+        <v>-125.73167</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++019</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
         </is>
       </c>
     </row>
@@ -1146,35 +1146,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t>WINCO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>104I  019</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Boulder City</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.2</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Silver, Copper, Lead, Gold, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,25 +1185,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Ag 487g/t, Cu 9.85%</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>chip sample results include maximum values over 1 metre of 9.85 per cent copper and 486.86 grams per tonne silver;</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$3.2M</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P8" t="n">
-        <v>1986</v>
+        <v>2025</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>Quartz Mountain Resources Ltd., Wyn Development Inc., Horseshoe Gold Mining Inc.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1214,17 +1222,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V8" t="n">
-        <v>49.7075</v>
+        <v>58.78</v>
       </c>
       <c r="W8" t="n">
-        <v>-116.00528</v>
+        <v>-128.12222</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++019</t>
         </is>
       </c>
     </row>
@@ -1234,30 +1242,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>104I  098</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>McDame</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10.8</v>
+        <v>31.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1273,33 +1281,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P9" t="n">
-        <v>1987</v>
+        <v>2022</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1310,17 +1318,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V9" t="n">
-        <v>50.53139</v>
+        <v>58.90944</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.2025</v>
+        <v>-129.09278</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
         </is>
       </c>
     </row>
@@ -1330,35 +1338,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.8</v>
+        <v>2.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,33 +1377,25 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>2018</v>
+        <v>1986</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1406,17 +1406,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="V10" t="n">
-        <v>49.73278</v>
+        <v>49.7075</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.21139</v>
+        <v>-116.00528</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1426,21 +1426,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.4</v>
+        <v>10.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>2012</v>
+        <v>1987</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V11" t="n">
-        <v>54.94444</v>
+        <v>50.53139</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.15722</v>
+        <v>-125.2025</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1522,35 +1522,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MAGNET</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>092L  097</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nimpkish</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Magnetite, Iron, Copper</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1561,54 +1561,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 15.40%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$780k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V12" t="n">
-        <v>50.40806</v>
+        <v>49.73278</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.96167</v>
+        <v>-125.21139</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1618,21 +1618,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>36</v>
+        <v>7.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1657,54 +1657,54 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U13" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V13" t="n">
-        <v>58.185</v>
+        <v>54.94444</v>
       </c>
       <c r="W13" t="n">
-        <v>-125.30611</v>
+        <v>-126.15722</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1714,30 +1714,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t>RED CAP - SLOPE ZONE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>104K  010</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>39.3</v>
+        <v>20</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1758,28 +1758,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
+          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$666k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P14" t="n">
-        <v>2022</v>
+        <v>2007</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1793,14 +1793,14 @@
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>58.15222</v>
+        <v>58.73611</v>
       </c>
       <c r="W14" t="n">
-        <v>-125.27778</v>
+        <v>-133.27</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
         </is>
       </c>
     </row>
@@ -1810,30 +1810,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5.6</v>
+        <v>21</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1854,28 +1854,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>2019</v>
+        <v>2007</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1889,14 +1889,14 @@
         <v>61</v>
       </c>
       <c r="V15" t="n">
-        <v>50.16611</v>
+        <v>58.73639</v>
       </c>
       <c r="W15" t="n">
-        <v>-125.39944</v>
+        <v>-133.24944</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -1906,30 +1906,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HAIDA GOLD</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>103C  002</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sewell Inlet</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>11.4</v>
+        <v>6.1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1945,54 +1945,54 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>544 t</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 8.7g/t</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$74k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>1999</v>
+        <v>2023</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
         <v>61</v>
       </c>
       <c r="V16" t="n">
-        <v>52.85806</v>
+        <v>50.37417</v>
       </c>
       <c r="W16" t="n">
-        <v>-132.15722</v>
+        <v>-116.36167</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -2002,30 +2002,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7.5</v>
+        <v>5.6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2041,54 +2041,54 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>1986</v>
+        <v>2019</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
         <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>49.30889</v>
+        <v>50.16611</v>
       </c>
       <c r="W17" t="n">
-        <v>-120.00417</v>
+        <v>-125.39944</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -2190,30 +2190,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOHN BULL                     </t>
+          <t xml:space="preserve">MIDNIGHT NAILS 1-2            </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>092F  146</t>
+          <t>082LSE063</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>toxʷnač</t>
+          <t>Cherryville</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3.3</v>
+        <v>8.1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Lead, Gold, Molybdenum</t>
+          <t>Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2229,17 +2229,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 150.83g/t, Au 23.99g/t, Cu 0.8%, Pb 2%, Zn 52%</t>
+          <t>Au 11.1g/t, Ag 76.0g/t, Pb 1.05%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>The best assays from several samples were 52 per cent zinc, 150.83 grams per tonne silver, 0.8 per cent copper, 2.0 per cent lead and 23.99 grams per tonne gold (Minister of Mines Annual Report 1926, page A312).</t>
+          <t>In 1983, samples from the Cherry shear assayed up to 158 grams per tonne gold and 1251 grams per tonne silver, while a sample of the altered dike or sill assayed 4.2 per cent lead, 1.86 per cent zinc, 42.2 grams per tonne gold and 212.5 grams per tonne silver (Assessment Report 11892). In 1987, a sample (R-7) wall rock adjacent to the vein assayed 75.3 grams per tonne gold, 147 grams per tonne silver and 1.96 per cent lead over 0.6 metre (Assessment Report 17386). In 1988, samples from the vein in the Cherry shear assayed up to 2.16 grams per tonne gold and 0.9 gram per tonne silver over 1 metre, while samples from areas with no quartz veining assayed up to 20 grams per tonne gold, 1.05 per cent lead and 76 grams per tonne silver over 90 metres (Assessment Report 18706). Samples from disco</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2248,35 +2248,35 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P19" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Aquarius Resources Limited, Geiger, K. Warren</t>
+          <t>Mohawk Oil Co. Ltd., Howard, Lennie Lee</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="U19" t="n">
         <v>57</v>
       </c>
       <c r="V19" t="n">
-        <v>49.94611</v>
+        <v>50.17861</v>
       </c>
       <c r="W19" t="n">
-        <v>-124.71056</v>
+        <v>-118.54</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSE063</t>
         </is>
       </c>
     </row>
@@ -2286,21 +2286,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KATANGA</t>
+          <t>AVON</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>092GNE009</t>
+          <t>092F  350</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Williams Landing</t>
+          <t>Chetarpe</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9.5</v>
+        <v>24.6</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2330,49 +2330,49 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 62.0g/t</t>
+          <t>Au 47.3g/t, Ag 53.1g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
+          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>$4k</t>
+          <t>$33k</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
         <v>1985</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Black Swan Gold Mines Ltd.</t>
+          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U20" t="n">
         <v>57</v>
       </c>
       <c r="V20" t="n">
-        <v>49.51111</v>
+        <v>49.40417</v>
       </c>
       <c r="W20" t="n">
-        <v>-122.57306</v>
+        <v>-125.75833</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
         </is>
       </c>
     </row>
@@ -2382,30 +2382,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
+          <t>KATANGA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>092B  060</t>
+          <t>092GNE009</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Williams Landing</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3.6</v>
+        <v>9.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2421,25 +2421,35 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+          <t>Au 62.0g/t</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>$4k</t>
+        </is>
+      </c>
       <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Black Swan Gold Mines Ltd.</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
         <v>13</v>
@@ -2448,17 +2458,17 @@
         <v>325</v>
       </c>
       <c r="U21" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V21" t="n">
-        <v>48.6075</v>
+        <v>49.51111</v>
       </c>
       <c r="W21" t="n">
-        <v>-123.57111</v>
+        <v>-122.57306</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
         </is>
       </c>
     </row>
@@ -2468,30 +2478,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KING GEORGE (L.159)</t>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>092B  011</t>
+          <t>092B  060</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>East Sooke</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2507,17 +2517,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>13 t</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2528,23 +2538,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T22" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U22" t="n">
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>48.36806</v>
+        <v>48.6075</v>
       </c>
       <c r="W22" t="n">
-        <v>-123.69528</v>
+        <v>-123.57111</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
         </is>
       </c>
     </row>
@@ -2554,30 +2564,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FISH CREEK</t>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>103O  005</t>
+          <t>092B  056</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2593,17 +2603,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2623,14 +2633,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>55.99139</v>
+        <v>48.61472</v>
       </c>
       <c r="W23" t="n">
-        <v>-130.03694</v>
+        <v>-123.59222</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
         </is>
       </c>
     </row>
@@ -2640,21 +2650,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SIXMILE</t>
+          <t xml:space="preserve">SILVER BELL                   </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>103O  002</t>
+          <t>093M  076</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Kispiox</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>7.1</v>
+        <v>1.6</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2663,7 +2673,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Gold, Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2679,17 +2689,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2709,100 +2719,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>55.98833</v>
+        <v>55.33556</v>
       </c>
       <c r="W24" t="n">
-        <v>-130.06194</v>
+        <v>-127.69194</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>092B  056</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Cliffside</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>13</v>
-      </c>
-      <c r="T25" t="n">
-        <v>325</v>
-      </c>
-      <c r="U25" t="n">
-        <v>55</v>
-      </c>
-      <c r="V25" t="n">
-        <v>48.61472</v>
-      </c>
-      <c r="W25" t="n">
-        <v>-123.59222</v>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:X22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1024,10 +1024,10 @@
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="U6" t="n">
         <v>74</v>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MAPLE LEAF</t>
+          <t>WINCO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>092F  039</t>
+          <t>104I  019</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kakawis</t>
+          <t>Boulder City</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.7</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Silver, Copper, Lead, Gold, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,54 +1089,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3 t</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 15.1g/t</t>
+          <t>Ag 487g/t, Cu 9.85%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
+          <t>chip sample results include maximum values over 1 metre of 9.85 per cent copper and 486.86 grams per tonne silver;</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$307k</t>
+          <t>$3.2M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="P7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
+          <t>Quartz Mountain Resources Ltd., Wyn Development Inc., Horseshoe Gold Mining Inc.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="V7" t="n">
-        <v>49.27111</v>
+        <v>58.78</v>
       </c>
       <c r="W7" t="n">
-        <v>-125.73167</v>
+        <v>-128.12222</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++019</t>
         </is>
       </c>
     </row>
@@ -1146,35 +1146,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WINCO</t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>104I  019</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Boulder City</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>66.40000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Gold, Zinc</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,33 +1185,25 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Ag 487g/t, Cu 9.85%</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>chip sample results include maximum values over 1 metre of 9.85 per cent copper and 486.86 grams per tonne silver;</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$3.2M</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P8" t="n">
-        <v>2025</v>
+        <v>1986</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Quartz Mountain Resources Ltd., Wyn Development Inc., Horseshoe Gold Mining Inc.</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1222,17 +1214,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V8" t="n">
-        <v>58.78</v>
+        <v>49.7075</v>
       </c>
       <c r="W8" t="n">
-        <v>-128.12222</v>
+        <v>-116.00528</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++019</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1242,30 +1234,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>31.5</v>
+        <v>10.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1281,33 +1273,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>2022</v>
+        <v>1987</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1318,17 +1310,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>58.90944</v>
+        <v>50.53139</v>
       </c>
       <c r="W9" t="n">
-        <v>-129.09278</v>
+        <v>-125.2025</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1338,35 +1330,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2.2</v>
+        <v>6.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1377,25 +1369,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+          <t>1.0 Mt</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>1986</v>
+        <v>2018</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -1406,17 +1406,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>49.7075</v>
+        <v>49.73278</v>
       </c>
       <c r="W10" t="n">
-        <v>-116.00528</v>
+        <v>-125.21139</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1426,21 +1426,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.8</v>
+        <v>7.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>1987</v>
+        <v>2012</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U11" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>50.53139</v>
+        <v>54.94444</v>
       </c>
       <c r="W11" t="n">
-        <v>-125.2025</v>
+        <v>-126.15722</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1522,35 +1522,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>MAGNET</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>092L  097</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Nimpkish</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Magnetite, Iron, Copper</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1561,54 +1561,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Cu 15.40%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$780k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="P12" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U12" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>49.73278</v>
+        <v>50.40806</v>
       </c>
       <c r="W12" t="n">
-        <v>-125.21139</v>
+        <v>-126.96167</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
         </is>
       </c>
     </row>
@@ -1618,21 +1618,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>ORMOND 3 (L.353)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092E  012</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7.4</v>
+        <v>2.8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1657,54 +1657,54 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Ag 127g/t, Cu 6.07%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$750k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>2012</v>
+        <v>1988</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Parallax Development Corp.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>275</v>
+        <v>175</v>
       </c>
       <c r="U13" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>54.94444</v>
+        <v>49.29972</v>
       </c>
       <c r="W13" t="n">
-        <v>-126.15722</v>
+        <v>-126.09722</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
         </is>
       </c>
     </row>
@@ -1714,30 +1714,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RED CAP - SLOPE ZONE</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>104K  010</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1758,28 +1758,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$666k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>2007</v>
+        <v>2019</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1793,14 +1793,14 @@
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>58.73611</v>
+        <v>57.94639</v>
       </c>
       <c r="W14" t="n">
-        <v>-133.27</v>
+        <v>-131.66722</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1810,30 +1810,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RED CAP - EAST CIRQUE</t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>104K  141</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>21</v>
+        <v>5.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1854,28 +1854,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 3.7g/t, Ag 26.0g/t</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$208k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>2007</v>
+        <v>2019</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1889,14 +1889,14 @@
         <v>61</v>
       </c>
       <c r="V15" t="n">
-        <v>58.73639</v>
+        <v>50.16611</v>
       </c>
       <c r="W15" t="n">
-        <v>-133.24944</v>
+        <v>-125.39944</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -1906,35 +1906,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6.1</v>
+        <v>37.4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1945,33 +1945,29 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>2023</v>
+        <v>1966</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1982,17 +1978,17 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V16" t="n">
-        <v>50.37417</v>
+        <v>58.88222</v>
       </c>
       <c r="W16" t="n">
-        <v>-116.36167</v>
+        <v>-132.1175</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2002,30 +1998,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t>KATANGA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>092GNE009</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Williams Landing</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5.6</v>
+        <v>9.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2046,28 +2042,28 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Au 62.0g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$4k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>2019</v>
+        <v>1985</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>Black Swan Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -2078,17 +2074,17 @@
         <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="V17" t="n">
-        <v>50.16611</v>
+        <v>49.51111</v>
       </c>
       <c r="W17" t="n">
-        <v>-125.39944</v>
+        <v>-122.57306</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
         </is>
       </c>
     </row>
@@ -2098,35 +2094,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">CORMORANT                     </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>092K  098</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Granite Bay</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>37.4</v>
+        <v>5.3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -2137,50 +2133,44 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>$2k</t>
-        </is>
-      </c>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1966</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T18" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>58.88222</v>
+        <v>50.18694</v>
       </c>
       <c r="W18" t="n">
-        <v>-132.1175</v>
+        <v>-125.28056</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
         </is>
       </c>
     </row>
@@ -2190,30 +2180,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIDNIGHT NAILS 1-2            </t>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>082LSE063</t>
+          <t>092B  056</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cherryville</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.1</v>
+        <v>1.9</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc</t>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2229,54 +2219,44 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 11.1g/t, Ag 76.0g/t, Pb 1.05%</t>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>In 1983, samples from the Cherry shear assayed up to 158 grams per tonne gold and 1251 grams per tonne silver, while a sample of the altered dike or sill assayed 4.2 per cent lead, 1.86 per cent zinc, 42.2 grams per tonne gold and 212.5 grams per tonne silver (Assessment Report 11892). In 1987, a sample (R-7) wall rock adjacent to the vein assayed 75.3 grams per tonne gold, 147 grams per tonne silver and 1.96 per cent lead over 0.6 metre (Assessment Report 17386). In 1988, samples from the vein in the Cherry shear assayed up to 2.16 grams per tonne gold and 0.9 gram per tonne silver over 1 metre, while samples from areas with no quartz veining assayed up to 20 grams per tonne gold, 1.05 per cent lead and 76 grams per tonne silver over 90 metres (Assessment Report 18706). Samples from disco</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>$47k</t>
-        </is>
-      </c>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>9</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2026</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Mohawk Oil Co. Ltd., Howard, Lennie Lee</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T19" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>50.17861</v>
+        <v>48.61472</v>
       </c>
       <c r="W19" t="n">
-        <v>-118.54</v>
+        <v>-123.59222</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082LSE063</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
         </is>
       </c>
     </row>
@@ -2286,30 +2266,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AVON</t>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>092F  350</t>
+          <t>092B  060</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Chetarpe</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>24.6</v>
+        <v>3.6</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead</t>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2325,54 +2305,44 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 47.3g/t, Ag 53.1g/t</t>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>$33k</t>
-        </is>
-      </c>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>4</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U20" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>49.40417</v>
+        <v>48.6075</v>
       </c>
       <c r="W20" t="n">
-        <v>-125.75833</v>
+        <v>-123.57111</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
         </is>
       </c>
     </row>
@@ -2382,30 +2352,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KATANGA</t>
+          <t>KING GEORGE (L.159)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>092GNE009</t>
+          <t>092B  011</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Williams Landing</t>
+          <t>East Sooke</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>9.5</v>
+        <v>0.8</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2421,54 +2391,44 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>13 t</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Au 62.0g/t</t>
+          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>$4k</t>
-        </is>
-      </c>
+          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>2</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1985</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Black Swan Gold Mines Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T21" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U21" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>49.51111</v>
+        <v>48.36806</v>
       </c>
       <c r="W21" t="n">
-        <v>-122.57306</v>
+        <v>-123.69528</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
         </is>
       </c>
     </row>
@@ -2478,30 +2438,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
+          <t xml:space="preserve">ROANAN                        </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>092B  060</t>
+          <t>104B  164</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Premier</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2522,12 +2482,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2547,186 +2507,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>48.6075</v>
+        <v>56.00194</v>
       </c>
       <c r="W22" t="n">
-        <v>-123.57111</v>
+        <v>-130.04972</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>092B  056</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Cliffside</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>13</v>
-      </c>
-      <c r="T23" t="n">
-        <v>325</v>
-      </c>
-      <c r="U23" t="n">
-        <v>55</v>
-      </c>
-      <c r="V23" t="n">
-        <v>48.61472</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-123.59222</v>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SILVER BELL                   </t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>093M  076</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Kispiox</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Zinc, Lead</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Ag 98.8g/t, Au 3.3g/t, Pb 3.88%, Zn 3.95%</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>A 10-centimetre wide channel sample assayed 3.3 grams per tonne gold, 98.8 grams per tonne silver 3.88 per cent lead and 3.95 per cent zinc (Geological Survey of Memoir 223, page 7).</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>13</v>
-      </c>
-      <c r="T24" t="n">
-        <v>325</v>
-      </c>
-      <c r="U24" t="n">
-        <v>55</v>
-      </c>
-      <c r="V24" t="n">
-        <v>55.33556</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-127.69194</v>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093M++076</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:X24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -762,35 +762,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CHARLIE</t>
+          <t>ERICKSEN-ASHBY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>092O  043</t>
+          <t>104K  009</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nemaiah Valley</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36.9</v>
+        <v>5.3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Lead</t>
+          <t>Silver, Lead, Zinc, Gold, Rhodonite</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -801,54 +801,54 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>907 kt</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 16.0g/t, Ag 224g/t</t>
+          <t>Au 0.9g/t, Ag 567g/t, Pb 5.68%, Zn 5.21%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>A chip sample assayed 279.9 grams per tonne silver, 10.6 grams per tonne gold and 13.68 per cent copper (Bulletin 81). The following year, samples from the East vein area assayed up to 0.48 per cent copper, 1.0 gram per tonne gold and 14.3 grams per tonne silver (Assessment Report 12105). In 1987, chip samples from the Charlie vein, taken over a length of 20 metres and width of 20 centimetres, averaged 22.1 grams per tonne gold and 224.0 grams per tonne silver, while a sample (AB 245B) of the DK vein assayed 9.9 grams per tonne gold, 95.8 grams per tonne silver and 0.14 per cent lead (Assessment Report 17038). A 20- centimetre sample of massive sulphide from the Big vein assayed 8.2 grams per tonne gold, 8557 grams per tonne silver and 26.0 per cent copper (Assessment Report 17038). In 199</t>
+          <t>3 intersected 20.2 metres which assayed 567.1 grams per tonne silver, 4.94 per cent lead and 4.22 per cent zinc; 4 intersected 5.1 metres which assayed 627.4 grams per tonne silver, 6.42 per cent lead and 6.2 per cent zinc (Assessment Report 10026). In 1981, a 15.1 metre drill intersection in mineralized cherts in Zone 8 assayed 173.1 grams per tonne silver, 1.2 per cent lead and 1.37 per cent zinc (Assessment Report 10026). Identified over an 8 metre width, some samples yielded high assays of 1203 grams per tonne silver, 23.23 per cent zinc, 20.24 per cent lead and 0.69 gram per tonne gold. Grab samples from the mineralized zone, 5 to 7 metres wide, of fine-grained pyrite, sphalerite, galena and quartz were assayed yielding 1.13 grams per tonne gold, 144.0 grams per tonne silver, 2.14 per</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>$6.3M</t>
+          <t>$286k</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="P4" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Galore Resources Inc., Suncor, Galore Resources Inc.; Zelon Enterprises Ltd.</t>
+          <t>Optima Minerals Inc., Northwind Ventures, Terratest</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
         <v>75</v>
       </c>
       <c r="V4" t="n">
-        <v>51.18028</v>
+        <v>58.65806</v>
       </c>
       <c r="W4" t="n">
-        <v>-123.67083</v>
+        <v>-133.475</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092O++043</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++009</t>
         </is>
       </c>
     </row>
@@ -858,30 +858,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ERICKSEN-ASHBY</t>
+          <t>DRIFTPILE CREEK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>104K  009</t>
+          <t>094K  066</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5.3</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold, Rhodonite</t>
+          <t>Zinc, Lead, Barite</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -897,54 +897,54 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>907 kt</t>
+          <t>18.1 Mt</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Au 0.9g/t, Ag 567g/t, Pb 5.68%, Zn 5.21%</t>
+          <t>Pb 1.18%, Zn 10.00%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3 intersected 20.2 metres which assayed 567.1 grams per tonne silver, 4.94 per cent lead and 4.22 per cent zinc; 4 intersected 5.1 metres which assayed 627.4 grams per tonne silver, 6.42 per cent lead and 6.2 per cent zinc (Assessment Report 10026). In 1981, a 15.1 metre drill intersection in mineralized cherts in Zone 8 assayed 173.1 grams per tonne silver, 1.2 per cent lead and 1.37 per cent zinc (Assessment Report 10026). Identified over an 8 metre width, some samples yielded high assays of 1203 grams per tonne silver, 23.23 per cent zinc, 20.24 per cent lead and 0.69 gram per tonne gold. Grab samples from the mineralized zone, 5 to 7 metres wide, of fine-grained pyrite, sphalerite, galena and quartz were assayed yielding 1.13 grams per tonne gold, 144.0 grams per tonne silver, 2.14 per</t>
+          <t>In 1980, it was reported that shallow drilling in 11 areas indicated reserves of approximately 18,145,000 tonnes averaging 2.38 per cent combined lead-zinc (Canadian Mines Handbook 1980-81, pages 280-281). In 1978, the best drill intersection from the North Trench zone (hole 78-07) was 11.7 metres grading 7.45 per cent combined lead and zinc, whereas drilling on the Ridge zone yielded 3 per cent combined lead and zinc over 26.2 metres and 4.14 per cent zinc over 7.5 metres in drillhole 78-09 (Assessment Report 7149 and 24609). In 1993, drilling on the Main zone intersected a 12-metre zone grading 10 per cent zinc and 1 per cent lead, including a zone of 6.02 metres grading 12.26 per cent zinc and 1.36 per cent lead in hole 93-56 (Assessment Report 23109). Several narrow high-grade intercep</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>$286k</t>
+          <t>$1.4M</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P5" t="n">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Optima Minerals Inc., Northwind Ventures, Terratest</t>
+          <t>Teck Exploration Ltd., Welcome North Mines Limited, Teck Corporation</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U5" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="V5" t="n">
-        <v>58.65806</v>
+        <v>58.06639</v>
       </c>
       <c r="W5" t="n">
-        <v>-133.475</v>
+        <v>-125.90972</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++009</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++066</t>
         </is>
       </c>
     </row>
@@ -954,30 +954,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DRIFTPILE CREEK</t>
+          <t>MAPLE LEAF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>094K  066</t>
+          <t>092F  039</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Kakawis</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>16.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Barite</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -993,54 +993,54 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>18.1 Mt</t>
+          <t>3 t</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Pb 1.18%, Zn 10.00%</t>
+          <t>Au 15.1g/t</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>In 1980, it was reported that shallow drilling in 11 areas indicated reserves of approximately 18,145,000 tonnes averaging 2.38 per cent combined lead-zinc (Canadian Mines Handbook 1980-81, pages 280-281). In 1978, the best drill intersection from the North Trench zone (hole 78-07) was 11.7 metres grading 7.45 per cent combined lead and zinc, whereas drilling on the Ridge zone yielded 3 per cent combined lead and zinc over 26.2 metres and 4.14 per cent zinc over 7.5 metres in drillhole 78-09 (Assessment Report 7149 and 24609). In 1993, drilling on the Main zone intersected a 12-metre zone grading 10 per cent zinc and 1 per cent lead, including a zone of 6.02 metres grading 12.26 per cent zinc and 1.36 per cent lead in hole 93-56 (Assessment Report 23109). Several narrow high-grade intercep</t>
+          <t>A channel sample taken from this vein assayed 15.09 grams per tonne gold and 6.86 grams per tonne silver across a 10 centimetre width (Minister of Mines Annual Report 1946). In 1984, a sample (65179) from the vein, as exposed in the lower adit, assayed up to 3.8 grams per tonne gold over 0.3 metres (Assessment Report 12026). In 1984, sampling of the vein, as exposed in the lower adit, assayed up to 14 grams per tonne gold over 0.45 metres (Assessment Report 12026). A channel sample assayed 16.11 grams per tonne gold over a 10 centimetre width (Minister of Mines Annual Report 1946).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>$1.4M</t>
+          <t>$307k</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Teck Exploration Ltd., Welcome North Mines Limited, Teck Corporation</t>
+          <t>Selkirk Metals Corp. (FMC # 231261), Stetson Resources Management, Arklow Res.; Stetson Resources Management; Strabane Res.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="V6" t="n">
-        <v>58.06639</v>
+        <v>49.27111</v>
       </c>
       <c r="W6" t="n">
-        <v>-125.90972</v>
+        <v>-125.73167</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++066</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++039</t>
         </is>
       </c>
     </row>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WINCO</t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>104I  019</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Boulder City</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>66.40000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Gold, Zinc</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,33 +1089,25 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Ag 487g/t, Cu 9.85%</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>chip sample results include maximum values over 1 metre of 9.85 per cent copper and 486.86 grams per tonne silver;</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$3.2M</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P7" t="n">
-        <v>2025</v>
+        <v>1986</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Quartz Mountain Resources Ltd., Wyn Development Inc., Horseshoe Gold Mining Inc.</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1126,17 +1118,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V7" t="n">
-        <v>58.78</v>
+        <v>49.7075</v>
       </c>
       <c r="W7" t="n">
-        <v>-128.12222</v>
+        <v>-116.00528</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++019</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1146,35 +1138,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.2</v>
+        <v>10.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1185,25 +1177,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+          <t>118 kt (assay)</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1214,17 +1214,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V8" t="n">
-        <v>49.7075</v>
+        <v>50.53139</v>
       </c>
       <c r="W8" t="n">
-        <v>-116.00528</v>
+        <v>-125.2025</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1234,35 +1234,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10.8</v>
+        <v>6.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1273,33 +1273,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>1987</v>
+        <v>2018</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1313,14 +1313,14 @@
         <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>50.53139</v>
+        <v>49.73278</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.2025</v>
+        <v>-125.21139</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1330,35 +1330,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,54 +1369,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>49.73278</v>
+        <v>54.94444</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.21139</v>
+        <v>-126.15722</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1426,35 +1426,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092E  088</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.4</v>
+        <v>1.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Gold, Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$766k</t>
         </is>
       </c>
       <c r="O11" t="n">
         <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2012</v>
+        <v>1988</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T11" t="n">
-        <v>275</v>
+        <v>200</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>54.94444</v>
+        <v>49.29694</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.15722</v>
+        <v>-126.08111</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
         </is>
       </c>
     </row>
@@ -1522,30 +1522,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MAGNET</t>
+          <t>ORMOND 3 (L.353)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>092L  097</t>
+          <t>092E  012</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nimpkish</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8.4</v>
+        <v>2.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Magnetite, Iron, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1566,49 +1566,49 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 15.40%</t>
+          <t>Ag 127g/t, Cu 6.07%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
+          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$780k</t>
+          <t>$750k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2025</v>
+        <v>1988</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
+          <t>Parallax Development Corp.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T12" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="U12" t="n">
         <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>50.40806</v>
+        <v>49.29972</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.96167</v>
+        <v>-126.09722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
         </is>
       </c>
     </row>
@@ -1618,21 +1618,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORMOND 3 (L.353)</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>092E  012</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.8</v>
+        <v>20.1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,49 +1662,49 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ag 127g/t, Cu 6.07%</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$750k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>1988</v>
+        <v>2019</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Parallax Development Corp.</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>49.29972</v>
+        <v>57.94639</v>
       </c>
       <c r="W13" t="n">
-        <v>-126.09722</v>
+        <v>-131.66722</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1714,21 +1714,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>20.1</v>
+        <v>36</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1758,28 +1758,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P14" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1793,14 +1793,14 @@
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>57.94639</v>
+        <v>58.185</v>
       </c>
       <c r="W14" t="n">
-        <v>-131.66722</v>
+        <v>-125.30611</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1810,21 +1810,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5.6</v>
+        <v>39.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1854,28 +1854,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1886,17 +1886,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V15" t="n">
-        <v>50.16611</v>
+        <v>58.15222</v>
       </c>
       <c r="W15" t="n">
-        <v>-125.39944</v>
+        <v>-125.27778</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -1906,35 +1906,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>37.4</v>
+        <v>21</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1945,29 +1945,33 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>1966</v>
+        <v>2007</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1978,17 +1982,17 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V16" t="n">
-        <v>58.88222</v>
+        <v>58.73639</v>
       </c>
       <c r="W16" t="n">
-        <v>-132.1175</v>
+        <v>-133.24944</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -1998,30 +2002,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KATANGA</t>
+          <t xml:space="preserve">DRAGON                        </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>092GNE009</t>
+          <t>082KSE071</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Williams Landing</t>
+          <t>Toby Creek</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9.5</v>
+        <v>6.1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2037,33 +2041,33 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 62.0g/t</t>
+          <t>Ag 15g/t, Cu 13.36%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>In 1926, a grab sample, from the face of a 20.4-metre long adit, assayed 4.2 per cent copper, 51.4 grams per tonne silver, trace zinc and trace gold (Minister of Mines Annual Report 1926, p. In 1968, a diamond drilling hole (No.2), located near the Lower adit, yielded 1.0 gram per tonne gold, 3.4 grams per tonne silver and 0.68 per cent copper over 81 centimetres (Property File - Kennedy Silver Mines Ltd. In 1969, a diamond drill hole (No.6), located near the Upper adit portal, yielded 0.5 gram per tonne gold, 10.9 grams per tonne silver and 0.49 per cent copper over 1.2 metres (Property File - Kennedy Silver Mines Ltd. however, some samples assayed as high as 62 grams per tonne gold (Assessment Report 13090, p. Also at this time, a random grab sample (15617) of mineralization exposed in t</t>
+          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$4k</t>
+          <t>$170k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>1985</v>
+        <v>2023</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Black Swan Gold Mines Ltd.</t>
+          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -2074,17 +2078,17 @@
         <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>49.51111</v>
+        <v>50.37417</v>
       </c>
       <c r="W17" t="n">
-        <v>-122.57306</v>
+        <v>-116.36167</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092GNE009</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
         </is>
       </c>
     </row>
@@ -2094,30 +2098,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORMORANT                     </t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>092K  098</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Granite Bay</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5.3</v>
+        <v>11.4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2133,44 +2137,54 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>$74k</t>
+        </is>
+      </c>
       <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1999</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>50.18694</v>
+        <v>52.85806</v>
       </c>
       <c r="W18" t="n">
-        <v>-125.28056</v>
+        <v>-132.15722</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -2180,35 +2194,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>092B  056</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.9</v>
+        <v>37.4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2219,25 +2233,31 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>$2k</t>
+        </is>
+      </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
         <v>13</v>
@@ -2246,17 +2266,17 @@
         <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="V19" t="n">
-        <v>48.61472</v>
+        <v>58.88222</v>
       </c>
       <c r="W19" t="n">
-        <v>-123.59222</v>
+        <v>-132.1175</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2266,30 +2286,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
+          <t>FISH CREEK</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>092B  060</t>
+          <t>103O  005</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cliffside</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2305,17 +2325,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2335,14 +2355,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>48.6075</v>
+        <v>55.99139</v>
       </c>
       <c r="W20" t="n">
-        <v>-123.57111</v>
+        <v>-130.03694</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
         </is>
       </c>
     </row>
@@ -2352,30 +2372,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KING GEORGE (L.159)</t>
+          <t>SIXMILE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>092B  011</t>
+          <t>103O  002</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>East Sooke</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.8</v>
+        <v>7.1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2391,17 +2411,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>13 t</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2412,23 +2432,23 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T21" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U21" t="n">
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>48.36806</v>
+        <v>55.98833</v>
       </c>
       <c r="W21" t="n">
-        <v>-123.69528</v>
+        <v>-130.06194</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
         </is>
       </c>
     </row>
@@ -2438,30 +2458,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROANAN                        </t>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>104B  164</t>
+          <t>092B  056</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Premier</t>
+          <t>Cliffside</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2482,12 +2502,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2498,23 +2518,195 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T22" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U22" t="n">
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>56.00194</v>
+        <v>48.61472</v>
       </c>
       <c r="W22" t="n">
-        <v>-130.04972</v>
+        <v>-123.59222</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>KING GEORGE (L.159)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>092B  011</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>East Sooke</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>13 t</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>6</v>
+      </c>
+      <c r="T23" t="n">
+        <v>150</v>
+      </c>
+      <c r="U23" t="n">
+        <v>55</v>
+      </c>
+      <c r="V23" t="n">
+        <v>48.36806</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-123.69528</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>092B  060</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Cliffside</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>13</v>
+      </c>
+      <c r="T24" t="n">
+        <v>325</v>
+      </c>
+      <c r="U24" t="n">
+        <v>55</v>
+      </c>
+      <c r="V24" t="n">
+        <v>48.6075</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-123.57111</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:X20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t>WINCO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>104I  019</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Boulder City</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2.2</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Silver, Copper, Lead, Gold, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,25 +1089,33 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Ag 487g/t, Cu 9.85%</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>chip sample results include maximum values over 1 metre of 9.85 per cent copper and 486.86 grams per tonne silver;</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$3.2M</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P7" t="n">
-        <v>1986</v>
+        <v>2013</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>Quartz Mountain Resources Ltd., Wyn Development Inc., Horseshoe Gold Mining Inc.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1118,17 +1126,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V7" t="n">
-        <v>49.7075</v>
+        <v>58.78</v>
       </c>
       <c r="W7" t="n">
-        <v>-116.00528</v>
+        <v>-128.12222</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++019</t>
         </is>
       </c>
     </row>
@@ -1138,30 +1146,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>KEEL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>104I  098</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>McDame</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10.8</v>
+        <v>31.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1177,33 +1185,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$1.3M</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>1987</v>
+        <v>2022</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1214,17 +1222,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V8" t="n">
-        <v>50.53139</v>
+        <v>58.90944</v>
       </c>
       <c r="W8" t="n">
-        <v>-125.2025</v>
+        <v>-129.09278</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
         </is>
       </c>
     </row>
@@ -1234,35 +1242,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6.8</v>
+        <v>2.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1273,33 +1281,25 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P9" t="n">
-        <v>2018</v>
+        <v>1986</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1310,17 +1310,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="V9" t="n">
-        <v>49.73278</v>
+        <v>49.7075</v>
       </c>
       <c r="W9" t="n">
-        <v>-125.21139</v>
+        <v>-116.00528</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1330,21 +1330,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.4</v>
+        <v>10.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,54 +1369,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>2012</v>
+        <v>1987</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V10" t="n">
-        <v>54.94444</v>
+        <v>50.53139</v>
       </c>
       <c r="W10" t="n">
-        <v>-126.15722</v>
+        <v>-125.2025</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1426,21 +1426,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MAIN</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092E  088</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.8</v>
+        <v>6.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Zinc</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.0 Mt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$766k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>1988</v>
+        <v>2018</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V11" t="n">
-        <v>49.29694</v>
+        <v>49.73278</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.08111</v>
+        <v>-125.21139</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1522,21 +1522,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ORMOND 3 (L.353)</t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>092E  012</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.8</v>
+        <v>7.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1561,54 +1561,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ag 127g/t, Cu 6.07%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$750k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>1988</v>
+        <v>2012</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Parallax Development Corp.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T12" t="n">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="U12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V12" t="n">
-        <v>49.29972</v>
+        <v>54.94444</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.09722</v>
+        <v>-126.15722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1618,30 +1618,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VB 20</t>
+          <t>RED CAP - SLOPE ZONE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>104G  081</t>
+          <t>104K  010</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Glenora</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Molybdenum, Copper</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1662,28 +1662,28 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
+          <t>Ag 115g/t, Cu 2.38%, Zn 0.14%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
+          <t>The third mineralized intersection was over 5.30 metres in length and contained about 5 per cent total sulphides. This hole intersected 9.2 metres grading 1.59 per cent copper and 59.65 grams per tonne silver. This rhyolite hosted a 2.15 metre drill section of massive sulphide material assaying 1.84 per cent copper and 96.0 grams per tonne silver. This mineralized interval included a 60 centimetre section grading 3.17 per cent copper, 169.37 grams per tonne silver and 0.14 per cent zinc with the best gold assay of 0.27 gram per tonne. Assays of up to 34.99 grams per tonne gold, 1390 grams per tonne silver, 9.85 per cent lead, 9.33 per cent zinc and 1.71 per cent copper were obtained from rock samples.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>$558k</t>
+          <t>$666k</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P13" t="n">
-        <v>2019</v>
+        <v>2007</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -1697,14 +1697,14 @@
         <v>65</v>
       </c>
       <c r="V13" t="n">
-        <v>57.94639</v>
+        <v>58.73611</v>
       </c>
       <c r="W13" t="n">
-        <v>-131.66722</v>
+        <v>-133.27</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++010</t>
         </is>
       </c>
     </row>
@@ -1810,30 +1810,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BOOK 9-10</t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>094K  052</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>39.3</v>
+        <v>21</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Lead</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1854,28 +1854,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ag 15.7g/t, Cu 11.33%</t>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$412k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>2022</v>
+        <v>2007</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1886,17 +1886,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V15" t="n">
-        <v>58.15222</v>
+        <v>58.73639</v>
       </c>
       <c r="W15" t="n">
-        <v>-125.27778</v>
+        <v>-133.24944</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -1906,30 +1906,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RED CAP - EAST CIRQUE</t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>104K  141</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>21</v>
+        <v>5.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1950,28 +1950,28 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 3.7g/t, Ag 26.0g/t</t>
+          <t>Cu 9.10%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$208k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>2007</v>
+        <v>2019</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1985,14 +1985,14 @@
         <v>61</v>
       </c>
       <c r="V16" t="n">
-        <v>58.73639</v>
+        <v>50.16611</v>
       </c>
       <c r="W16" t="n">
-        <v>-133.24944</v>
+        <v>-125.39944</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -2002,30 +2002,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAGON                        </t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>082KSE071</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Toby Creek</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6.1</v>
+        <v>7.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2046,49 +2046,49 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ag 15g/t, Cu 13.36%</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>A grab sample from a mineralized section of the vein assayed 13.36 per cent copper and 15 grams per tonne silver (Minister of Mines Annual Report 1924).</t>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$170k</t>
+          <t>$64k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>2023</v>
+        <v>1986</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Eagle Plains Resources Ltd., Dragoon Resources Ltd., Strata GeoData Services Ltd.</t>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U17" t="n">
         <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>50.37417</v>
+        <v>49.30889</v>
       </c>
       <c r="W17" t="n">
-        <v>-116.36167</v>
+        <v>-120.00417</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082KSE071</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
         </is>
       </c>
     </row>
@@ -2098,35 +2098,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HAIDA GOLD</t>
+          <t xml:space="preserve">ACE                           </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>103C  002</t>
+          <t>104K  025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sewell Inlet</t>
+          <t>Callison Ranch</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.4</v>
+        <v>37.4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Developed Prospect  </t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -2137,33 +2137,29 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>544 t</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Au 8.7g/t</t>
-        </is>
-      </c>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$74k</t>
+          <t>$2k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>1999</v>
+        <v>1966</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
@@ -2174,17 +2170,17 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V18" t="n">
-        <v>52.85806</v>
+        <v>58.88222</v>
       </c>
       <c r="W18" t="n">
-        <v>-132.15722</v>
+        <v>-132.1175</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
         </is>
       </c>
     </row>
@@ -2194,35 +2190,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t xml:space="preserve">CORMORANT                     </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>092K  098</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Granite Bay</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>37.4</v>
+        <v>5.3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2233,50 +2229,44 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>$2k</t>
-        </is>
-      </c>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1966</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T19" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>58.88222</v>
+        <v>50.18694</v>
       </c>
       <c r="W19" t="n">
-        <v>-132.1175</v>
+        <v>-125.28056</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
         </is>
       </c>
     </row>
@@ -2286,21 +2276,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FISH CREEK</t>
+          <t xml:space="preserve">ROANAN                        </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>103O  005</t>
+          <t>104B  164</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Premier</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2325,17 +2315,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>Assay resource</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2355,358 +2345,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>55.99139</v>
+        <v>56.00194</v>
       </c>
       <c r="W20" t="n">
-        <v>-130.03694</v>
+        <v>-130.04972</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SIXMILE</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>103O  002</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>13</v>
-      </c>
-      <c r="T21" t="n">
-        <v>325</v>
-      </c>
-      <c r="U21" t="n">
-        <v>55</v>
-      </c>
-      <c r="V21" t="n">
-        <v>55.98833</v>
-      </c>
-      <c r="W21" t="n">
-        <v>-130.06194</v>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>092B  056</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Cliffside</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Iron, Magnetite, Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>12</v>
-      </c>
-      <c r="T22" t="n">
-        <v>300</v>
-      </c>
-      <c r="U22" t="n">
-        <v>55</v>
-      </c>
-      <c r="V22" t="n">
-        <v>48.61472</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-123.59222</v>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>KING GEORGE (L.159)</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>092B  011</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>East Sooke</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>13 t</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>6</v>
-      </c>
-      <c r="T23" t="n">
-        <v>150</v>
-      </c>
-      <c r="U23" t="n">
-        <v>55</v>
-      </c>
-      <c r="V23" t="n">
-        <v>48.36806</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-123.69528</v>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STAR (L.19G)                  </t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>092B  060</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Cliffside</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Iron, Magnetite, Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospect            </t>
-        </is>
-      </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Assay resource</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>13</v>
-      </c>
-      <c r="T24" t="n">
-        <v>325</v>
-      </c>
-      <c r="U24" t="n">
-        <v>55</v>
-      </c>
-      <c r="V24" t="n">
-        <v>48.6075</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-123.57111</v>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X20"/>
+  <dimension ref="A1:X29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -1050,35 +1050,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WINCO</t>
+          <t>SULLIVAN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>104I  019</t>
+          <t>082FNE052</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Boulder City</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>66.40000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Silver, Copper, Lead, Gold, Zinc</t>
+          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1089,33 +1089,25 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Ag 487g/t, Cu 9.85%</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>chip sample results include maximum values over 1 metre of 9.85 per cent copper and 486.86 grams per tonne silver;</t>
-        </is>
-      </c>
+          <t>54.0 Mt</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>$3.2M</t>
+          <t>$423k</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P7" t="n">
-        <v>2013</v>
+        <v>1986</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Quartz Mountain Resources Ltd., Wyn Development Inc., Horseshoe Gold Mining Inc.</t>
+          <t>Cominco Ltd.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1126,17 +1118,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V7" t="n">
-        <v>58.78</v>
+        <v>49.7075</v>
       </c>
       <c r="W7" t="n">
-        <v>-128.12222</v>
+        <v>-116.00528</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++019</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
         </is>
       </c>
     </row>
@@ -1146,30 +1138,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KEEL</t>
+          <t xml:space="preserve">COLOSSUS (L.256)              </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>104I  098</t>
+          <t>092K  029</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>McDame</t>
+          <t>Phillips Arm</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>31.5</v>
+        <v>10.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold, Silver, Tungsten</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1185,33 +1177,33 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>118 kt (assay)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 6.2g/t, Ag 189g/t, Zn 1.76%, W 0.02%, Bi 0.06%</t>
+          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Also at this time, a grab sample (83CW930) of quartz-sulphide veins exposed in Hook Creek, north of the West veined zone, assayed 2.47 grams per tonne gold, 188.6 grams per tonne silver and 1.76 per cent zinc, whereas a float sample (83CW885) from the area of the third zone of mineralization, located northeast of the East veined zone, assayed 17.14 grams per tonne gold (Assessment Report 12181). A float sample (530509) of quartz vein hosting arsenopyrite, located approximately 900 kilometres north of the West zone, assayed 0.024 per cent tungsten, 0.060 per cent bismuth and 9.86 grams per tonne gold (Assessment Report 25044). A local float or subcrop sample (BL03G017) from the area of historical hand trenching on the East veined zone assayed 2.06 grams per tonne gold and 24.1 grams per ton</t>
+          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>$1.3M</t>
+          <t>$80k</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>2022</v>
+        <v>1987</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Sutcliffe Resources Ltd., 606896 B.C. Ltd.; Gambier Mining Corp.; Sutcliffe Resources Ltd., Canamax Resources Inc.</t>
+          <t>Sancono Ventures Inc., Gardiner Res.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1222,17 +1214,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="V8" t="n">
-        <v>58.90944</v>
+        <v>50.53139</v>
       </c>
       <c r="W8" t="n">
-        <v>-129.09278</v>
+        <v>-125.2025</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104I++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
         </is>
       </c>
     </row>
@@ -1242,35 +1234,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SULLIVAN</t>
+          <t>IDEAL 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>082FNE052</t>
+          <t>092F  510</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Mount Washington</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2.2</v>
+        <v>6.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Tin, Copper, Gold, Iron, Sulphur</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Showing             </t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1281,25 +1273,33 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>54.0 Mt</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+          <t>1.0 Mt</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Au 4.4g/t, Ag 20.9g/t</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>$423k</t>
+          <t>$52k</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>1986</v>
+        <v>2018</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Cominco Ltd.</t>
+          <t>North Bay Resources Inc. (FMC 204090)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1310,17 +1310,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V9" t="n">
-        <v>49.7075</v>
+        <v>49.73278</v>
       </c>
       <c r="W9" t="n">
-        <v>-116.00528</v>
+        <v>-125.21139</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=082FNE052</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
         </is>
       </c>
     </row>
@@ -1330,21 +1330,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">COLOSSUS (L.256)              </t>
+          <t>GRANISLE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>092K  029</t>
+          <t>093L  146</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Phillips Arm</t>
+          <t>Granisle</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10.8</v>
+        <v>7.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Copper, Silver, Gold, Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospect            </t>
+          <t xml:space="preserve">Past Producer       </t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1369,54 +1369,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>118 kt (assay)</t>
+          <t>119.0 Mt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ag 105.2g/t, Au 0.056g/t, Cu 28.1%, Mo 0.003%</t>
+          <t>Cu 0.43%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A grab sample, from underground working level 2, of chalcopyrite with pyrite and sphalerite, assayed 28.10 per cent copper, 0.003 per cent molybdenum 0.056 gram per tonne gold, 105.2 grams per tonne silver and 0.0959 per cent cobalt (Assessment Report 15919).</t>
+          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>$80k</t>
+          <t>$637k</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>1987</v>
+        <v>2012</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Sancono Ventures Inc., Gardiner Res.</t>
+          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>50.53139</v>
+        <v>54.94444</v>
       </c>
       <c r="W10" t="n">
-        <v>-125.2025</v>
+        <v>-126.15722</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++029</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
         </is>
       </c>
     </row>
@@ -1426,21 +1426,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IDEAL 3</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092F  510</t>
+          <t>092E  088</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mount Washington</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.8</v>
+        <v>1.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Gold, Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing             </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1465,54 +1465,54 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 4.4g/t, Ag 20.9g/t</t>
+          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>A composite of grab samples of the veinlets (1 to 3 centimetres wide) assayed 9.87 grams per tonne gold, 24.6 grams per tonne silver, 0.05 per cent copper, 0.8 per cent lead, 1.2 per cent zinc and 0.4 per cent arsenic (Assessment Report 16412). A sample (Sample 49A) assayed 0.42 per cent copper and 2.43 per cent zinc (Assessment Report 16412). In 1987, they had outlined  approximately 88 859 tonnes drill-indicated at 4.44 grams per tonne gold and 20.9 grams per tonne silver in the Lakeview-West grid and Domineer zones. They drilled one intersection of 15.9 metres of 5.56 grams per tonne gold plus 2.7 metres of 2.5 grams per tonne gold and 3 metres of 3.44 grams per tonne gold (Assessment Report 22975).</t>
+          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$52k</t>
+          <t>$766k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2018</v>
+        <v>1988</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>North Bay Resources Inc. (FMC 204090)</t>
+          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U11" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>49.73278</v>
+        <v>49.29694</v>
       </c>
       <c r="W11" t="n">
-        <v>-125.21139</v>
+        <v>-126.08111</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++510</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
         </is>
       </c>
     </row>
@@ -1522,21 +1522,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GRANISLE</t>
+          <t>ORMOND 3 (L.353)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>093L  146</t>
+          <t>092E  012</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Granisle</t>
+          <t>Ahousat</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7.4</v>
+        <v>2.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Molybdenum</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past Producer       </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1561,54 +1561,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>119.0 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 0.43%</t>
+          <t>Ag 127g/t, Cu 6.07%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>In 1969, a diamond drill program of 10,000 meters in 50 holes increased reserves to 81 million tonnes proven of 0.43 per cent copper.</t>
+          <t>In 1981, a sample assayed 6.07 per cent copper and 126.9 grams per tonne silver (Assessment Report 9658).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>$637k</t>
+          <t>$750k</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2012</v>
+        <v>1988</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Noranda Minerals Inc. (Babine Div.), Xstrata Canada Corporation, Galambos</t>
+          <t>Parallax Development Corp.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>275</v>
+        <v>125</v>
       </c>
       <c r="U12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>54.94444</v>
+        <v>49.29972</v>
       </c>
       <c r="W12" t="n">
-        <v>-126.15722</v>
+        <v>-126.09722</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=093L++146</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++012</t>
         </is>
       </c>
     </row>
@@ -1714,21 +1714,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>VB 20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>094K  027</t>
+          <t>104G  081</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Magnum Mine</t>
+          <t>Glenora</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>36</v>
+        <v>20.1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1758,28 +1758,28 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 5.8g/t, Cu 7.88%</t>
+          <t>Au 1.3g/t, Ag 31.9g/t, Cu 2.29%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
+          <t>assayed 2.64 per cent copper, 59.0 grams per tonne silver and 2.78 grams per tonne gold (Assessment Report 20149). Sulphide zones within skarn are typically 1 to 2 metres wide, up to 5 metres wide, and contain 2-5 per cent chalcopyrite, up to 5 per cent pyrite, up to 3 per cent pyrrhotite, and variable concentrations of magnetite and hematite. Six samples taken over a strike length of 740 metres averaged 1.34 grams per tonne gold, 31.9 grams per tonne silver and 2.29 per cent copper (Pautler, J.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>$446k</t>
+          <t>$558k</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
+          <t>Artemis Gold Inc., Strategic Metals Ltd., Red Tusk Resources</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1793,14 +1793,14 @@
         <v>65</v>
       </c>
       <c r="V14" t="n">
-        <v>58.185</v>
+        <v>57.94639</v>
       </c>
       <c r="W14" t="n">
-        <v>-125.30611</v>
+        <v>-131.66722</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104G++081</t>
         </is>
       </c>
     </row>
@@ -1810,30 +1810,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RED CAP - EAST CIRQUE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>104K  141</t>
+          <t>094K  027</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tulsequah</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1854,28 +1854,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 3.7g/t, Ag 26.0g/t</t>
+          <t>Au 5.8g/t, Cu 7.88%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
+          <t>One 1.5-metre chip sample (418) assayed 17.69 per cent copper and 4.8 grams per tonne silver (Assessment Report 2487). Most of the other chip samples from this cluster of veins assayed greater than 6 per cent copper. A chip sample (403) assayed 29.22 per cent copper and 116 grams per tonne silver over 0.45 metre (Assessment Report 2487). Another sample (402) assayed 5.8 grams per tonne gold (Assessment Report 2487). Quartz-carbonate veins are mineralized with chalcopyrite and bornite, and yield assays that average 7.88 per cent copper over 1.7 metres.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>$208k</t>
+          <t>$446k</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>2007</v>
+        <v>2022</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
+          <t>Fabled Copper Corp., Coppex Synd., Pugh</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1886,17 +1886,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V15" t="n">
-        <v>58.73639</v>
+        <v>58.185</v>
       </c>
       <c r="W15" t="n">
-        <v>-133.24944</v>
+        <v>-125.30611</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++027</t>
         </is>
       </c>
     </row>
@@ -1906,21 +1906,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SUNSET</t>
+          <t>BOOK 9-10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>092K  050</t>
+          <t>094K  052</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bloedel</t>
+          <t>Magnum Mine</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5.6</v>
+        <v>39.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Lead</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1950,28 +1950,28 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Cu 9.10%</t>
+          <t>Ag 15.7g/t, Cu 11.33%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
+          <t>In 2021, a chip sample (D723170) assayed 0.26 per cent copper over 1 metre, whereas five mineralized float samples (D723458, D723161, D723167, D723171, D723172) from the occurrence area yielded from 1.13 to 22.4 per cent copper with up to 15.7 grams per tonne silver (Assessment Report 39912).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>$102k</t>
+          <t>$412k</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P16" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Volatus Capital Corp., Osborne, T.</t>
+          <t>Fabled Copper Corp., Coppex Synd., Bralorne Res.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1982,17 +1982,17 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="V16" t="n">
-        <v>50.16611</v>
+        <v>58.15222</v>
       </c>
       <c r="W16" t="n">
-        <v>-125.39944</v>
+        <v>-125.27778</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=094K++052</t>
         </is>
       </c>
     </row>
@@ -2002,21 +2002,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTORIA (L.2464)             </t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>092HSE058</t>
+          <t>104K  141</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Tulsequah</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7.5</v>
+        <v>21</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2041,54 +2041,54 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ag 10g/t, Au 9.6g/t</t>
+          <t>Au 3.7g/t, Ag 26.0g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+          <t>In hole LJ-98-5B, 3 metres grading 3.7 grams per tonne gold and 26.0 grams per tonne silver were intersected. In RV-98-10, there were two intersections of note: 7.15 metres grading 12.05 grams per tonne gold and 49.50 grams per tonne silver; and a second adjacent 4.73 metre interval grading 2.50 grams per tonne gold and 18.37 grams per tonne silver.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>$64k</t>
+          <t>$208k</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>1986</v>
+        <v>2007</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+          <t>XPlorer Gold Corp., Xplorer Minerals Inc., Omni Resources Incorporated</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
         <v>61</v>
       </c>
       <c r="V17" t="n">
-        <v>49.30889</v>
+        <v>58.73639</v>
       </c>
       <c r="W17" t="n">
-        <v>-120.00417</v>
+        <v>-133.24944</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++141</t>
         </is>
       </c>
     </row>
@@ -2098,35 +2098,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACE                           </t>
+          <t>SUNSET</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>104K  025</t>
+          <t>092K  050</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Callison Ranch</t>
+          <t>Bloedel</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>37.4</v>
+        <v>5.6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developed Prospect  </t>
+          <t xml:space="preserve">Prospect            </t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -2137,29 +2137,33 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>11.8 Mt</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Cu 9.10%</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+          <t>A 2.3 kilogram composite grab sample of mineralized vein quartz assayed 2.69 per cent copper, 14.3976 grams per tonne silver and trace gold (Assessment Report 4179). In 1901 the vein is quoted as assaying an average of 6 per cent copper (Minister of Mines Annual Report 1901, page 1115). A sample (32312) from the upper adit assayed 12.2 per cent copper and 72.0 grams per tonne silver (MacIntyre, D.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>$2k</t>
+          <t>$102k</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>1966</v>
+        <v>2019</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Canadian Johns-Manville Corp. Ltd.</t>
+          <t>Volatus Capital Corp., Osborne, T.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
@@ -2170,17 +2174,17 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V18" t="n">
-        <v>58.88222</v>
+        <v>50.16611</v>
       </c>
       <c r="W18" t="n">
-        <v>-132.1175</v>
+        <v>-125.39944</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++050</t>
         </is>
       </c>
     </row>
@@ -2190,30 +2194,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORMORANT                     </t>
+          <t>HAIDA GOLD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>092K  098</t>
+          <t>103C  002</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Granite Bay</t>
+          <t>Sewell Inlet</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5.3</v>
+        <v>11.4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2229,44 +2233,54 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Assay resource</t>
+          <t>544 t</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+          <t>Au 8.7g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>In 1932, a sample from a 0.3 to 0.4-metre wide quartz vein with minor chalcopyrite exposed in the face of an opencut assayed 21.9 grams per tonne gold and 10.3 grams per tonne silver (Property File - J.T. In 1933, two sets of samples from the no.1 tunnel (C vein) assayed 4.4 and 17.1 grams per tonne gold, respectively, over 0.54 metre for the first 13.5 metres of the tunnel, whereas the average of surface sampling above the tunnel yielded 10.1 grams per tonne gold across 0.725 metre (Property File - C.C. In 1934, detailed sampling in the 85-metre long drift adit (A-1 adit) showed values varying from 0.69 to 48.7 grams per tonne gold, with an average assay value of 7.3 grams per tonne gold across a width of 0.73 metre along the length of the tunnel (Annual Report 1934; In 1979, a chip sampl</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>$74k</t>
+        </is>
+      </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1999</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Cusac Industries Ltd., Richards, Gordon G.</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T19" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U19" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V19" t="n">
-        <v>50.18694</v>
+        <v>52.85806</v>
       </c>
       <c r="W19" t="n">
-        <v>-125.28056</v>
+        <v>-132.15722</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103C++002</t>
         </is>
       </c>
     </row>
@@ -2276,21 +2290,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROANAN                        </t>
+          <t xml:space="preserve">VICTORIA (L.2464)             </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>104B  164</t>
+          <t>092HSE058</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Premier</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2299,7 +2313,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2320,39 +2334,839 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+          <t>Ag 10g/t, Au 9.6g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>A selected sample of arsenopyrite assayed 4.5 grams per tonne gold and 8.6 grams per tonne silver (Minister of Mines Annual Report 1936, page D12). 2 adit, across 66 centimetres of quartz, assayed 9.6 grams per tonne gold and 10 grams per tonne silver (Minister of Mines Annual Report 1936, page D12).</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>$64k</t>
+        </is>
+      </c>
       <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1986</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Mascot Gold Mines Ltd., Brohm Res.</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
+        <v>12</v>
+      </c>
+      <c r="T20" t="n">
+        <v>300</v>
+      </c>
+      <c r="U20" t="n">
+        <v>61</v>
+      </c>
+      <c r="V20" t="n">
+        <v>49.30889</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-120.00417</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092HSE058</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACE                           </t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>104K  025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Callison Ranch</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Asbestos</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Prospect  </t>
+        </is>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>11.8 Mt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>The main fibre zone occurs on the north side of Camp Creek and consists of a continuous zone about 122 by 60 metres, containing greater than 5 per cent chrysotile with fibre lengths averaging about 2 centimetres.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>$2k</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1966</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Canadian Johns-Manville Corp. Ltd.</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
         <v>13</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>325</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
+        <v>60</v>
+      </c>
+      <c r="V21" t="n">
+        <v>58.88222</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-132.1175</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104K++025</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>AVON</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>092F  350</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Chetarpe</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Copper, Lead</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Au 47.3g/t, Ag 53.1g/t</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>A 20 centimetre chip sample taken across the vein assayed 8.91 grams per tonne gold and 65.14 grams per tonne silver (Bulletin 8). One sample assayed 85.71 grams per tonne gold and 41.14 grams per tonne silver (Bulletin 8).</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>$33k</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Bermuda Resources Ltd., Canamco Res., Guppy</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>25</v>
+      </c>
+      <c r="U22" t="n">
+        <v>57</v>
+      </c>
+      <c r="V22" t="n">
+        <v>49.40417</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-125.75833</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092F++350</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROANAN                        </t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>104B  164</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Premier</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Ag 349.74g/t, Au 48.68g/t, WO3 0.05%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>A sample across 1.83 metres in the surface exposure, taken in 1917, assayed 48.68 grams per tonne gold and 349.74 grams per tonne silver (United States Geological Survey, Bulletin 807). In the lower drift, the vein averages 30 centimetres in width and contains sparsely distributed grains of scheelite over a length of 15 metres with an estimated grade of 0.05 per cent scheelite (United States Geological Survey, Bulletin 1024-F).</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>13</v>
+      </c>
+      <c r="T23" t="n">
+        <v>325</v>
+      </c>
+      <c r="U23" t="n">
         <v>55</v>
       </c>
-      <c r="V20" t="n">
+      <c r="V23" t="n">
         <v>56.00194</v>
       </c>
-      <c r="W20" t="n">
+      <c r="W23" t="n">
         <v>-130.04972</v>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=104B++164</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SIXMILE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>103O  002</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 154g/t, Pb 8.70%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>A heavy pyritic quartz stringer assayed 2.05 grams per tonne gold and 20.56 grams per tonne silver; where galena occurs an assay returned 23.31 grams per tonne gold, 287.95 grams per tonne silver and 8.7 per cent lead (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>13</v>
+      </c>
+      <c r="T24" t="n">
+        <v>325</v>
+      </c>
+      <c r="U24" t="n">
+        <v>55</v>
+      </c>
+      <c r="V24" t="n">
+        <v>55.98833</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-130.06194</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++002</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FISH CREEK</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>103O  005</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Lead, Zinc, Copper, Tungsten</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Au 12.7g/t, Ag 832g/t, Cu 7.68%, Pb 32.20%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Eighteen tonnes of sorted ore taken from veins on the Olympia claim assayed 12.68 grams per tonne gold, 10,832.48 grams per tonne silver, 32.2 per cent lead and 7.68 per cent copper (United States Geological Survey Bulletin 807).</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>13</v>
+      </c>
+      <c r="T25" t="n">
+        <v>325</v>
+      </c>
+      <c r="U25" t="n">
+        <v>55</v>
+      </c>
+      <c r="V25" t="n">
+        <v>55.99139</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-130.03694</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=103O++005</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CORMORANT                     </t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>092K  098</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Granite Bay</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Ag 6.86g/t, Au 2.06g/t, Cu 2.7%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>A sample from the surface assayed 2.06 grams per tonne gold, 6.86 grams per tonne silver and 2.7 per cent copper (Minister of Mines Annual Report 1913, page 285).</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>11</v>
+      </c>
+      <c r="T26" t="n">
+        <v>275</v>
+      </c>
+      <c r="U26" t="n">
+        <v>55</v>
+      </c>
+      <c r="V26" t="n">
+        <v>50.18694</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-125.28056</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092K++098</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>KING GEORGE (L.159)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>092B  011</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>East Sooke</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>13 t</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Au 2.1g/t, Ag 10.3g/t, Cu 7.95%, Ni 0.05%</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>In 1948, a sample taken across 1.5 metres assayed 7.95 per cent copper, 2.06 grams per tonne gold, 10.28 grams per tonne silver and not more than 0.05 per cent nickel, cobalt or molybdenum (Minister of Mines Annual Report 1948, page 170).</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>6</v>
+      </c>
+      <c r="T27" t="n">
+        <v>150</v>
+      </c>
+      <c r="U27" t="n">
+        <v>55</v>
+      </c>
+      <c r="V27" t="n">
+        <v>48.36806</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-123.69528</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++011</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STAR (L.19G)                  </t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>092B  060</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Cliffside</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Iron, Magnetite, Gold, Silver, Copper</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Ag 12g/t, Au 4.8g/t, Cu 0.2%</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>A 1.2 metre chip sample assayed 4.80 grams per tonne gold, 12.00 grams per tonne silver and 0.20 per cent copper; a grab sample assayed 56.72 per cent iron and 0.15 per cent copper (Aho, 1961).</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>13</v>
+      </c>
+      <c r="T28" t="n">
+        <v>325</v>
+      </c>
+      <c r="U28" t="n">
+        <v>55</v>
+      </c>
+      <c r="V28" t="n">
+        <v>48.6075</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-123.57111</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++060</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WILLORON 1-3,9,10             </t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>092B  056</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Cliffside</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Iron, Magnetite, Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prospect            </t>
+        </is>
+      </c>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Assay resource</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Ag 24g/t, Au 2.74g/t, Cu 2.38%, Iro 57.33%</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>A sample taken at showing Number 9 assayed 2.74 grams per tonne gold, 24.00 grams per tonne silver, 2.38 per cent copper and 57.33 per cent iron. Most samples taken, however, assayed nil or trace gold and silver and less than 0.5 per cent copper (Property File - Aho, 1961, page 14).</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>13</v>
+      </c>
+      <c r="T29" t="n">
+        <v>325</v>
+      </c>
+      <c r="U29" t="n">
+        <v>55</v>
+      </c>
+      <c r="V29" t="n">
+        <v>48.61472</v>
+      </c>
+      <c r="W29" t="n">
+        <v>-123.59222</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092B++056</t>
         </is>
       </c>
     </row>

--- a/site/bc_leads.xlsx
+++ b/site/bc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X29"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -928,10 +928,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="U5" t="n">
         <v>74</v>
@@ -1426,30 +1426,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MAIN</t>
+          <t>MAGNET</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>092E  088</t>
+          <t>092L  097</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ahousat</t>
+          <t>Nimpkish</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.8</v>
+        <v>8.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Zinc</t>
+          <t>Magnetite, Iron, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1470,49 +1470,49 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 4.3g/t, Ag 120g/t, Cu 2.24%, Zn 0.26%</t>
+          <t>Cu 15.40%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>In 1987, grab samples from the area assayed up to 7.4 grams per tonne gold, 242.1 grams per tonne silver, 7.70 per cent copper and 0.262 per cent zinc (sample 22703; A 2 metre chip sample assayed 120.0 grams per tonne silver, 2.00 per cent copper and 2.52 per cent zinc (Assessment Report 17428). Chip sampling of the former trenches, in the same year, yielded values up to 1.12 grams per tonne gold, 78.2 grams per tonne silver, 2.24 per cent copper and 0.063 per cent zinc over 3.5 metres (sample 23075;</t>
+          <t>In 1972, a chip sample across a 1.5-metre chalcopyrite-pyrite vein assayed 15.4 per cent copper (Assessment Report 4447).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>$766k</t>
+          <t>$780k</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P11" t="n">
-        <v>1988</v>
+        <v>2025</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Parallax Development Corp., Ross Island Min., Au Resources Ltd.</t>
+          <t>Graymont Western Canada Inc. (105327), Industrial Fillers, Homegold Resources Ltd.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T11" t="n">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="U11" t="n">
         <v>65</v>
       </c>
       <c r="V11" t="n">
-        <v>49.29694</v>
+        <v>50.40806</v>
       </c>
       <c r="W11" t="n">
-        <v>-126.08111</v>
+        <v>-126.96167</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092E++088</t>
+          <t>http://minfile.gov.bc.ca/Summary.aspx?minfilno=092L++097</t>
         </is>
       </c>
     </row>
@@ -1522,30 +1522,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ORMOND 3 (L.353)</t>
+          <t>RED CAP - EAST CIRQUE</t>
         </is>
       </c>
 